--- a/AMS/009-Little-Sunflower/Little Sunflower FY 25-26 V2.xlsx
+++ b/AMS/009-Little-Sunflower/Little Sunflower FY 25-26 V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\009-Little-Sunflower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2F6131-CB74-4265-91B3-E9BFA60275FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA87BAC-9667-4A9A-A7BA-97338FC3AB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="862" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="862" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -3024,7 +3024,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3298,72 +3298,9 @@
     <xf numFmtId="166" fontId="0" fillId="38" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="41" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="34" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3394,9 +3331,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3421,15 +3355,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="0" borderId="28" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="39" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3442,30 +3367,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3475,15 +3376,6 @@
     <xf numFmtId="164" fontId="31" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3493,38 +3385,20 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3532,7 +3406,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3541,25 +3415,22 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3568,13 +3439,13 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3586,46 +3457,37 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3634,10 +3496,10 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3646,7 +3508,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3658,41 +3520,26 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3715,9 +3562,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -3750,11 +3595,143 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="0" borderId="28" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="0" borderId="1" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -4130,62 +4107,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="183"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="247"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="248" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="186"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="248" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="186"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="249"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250"/>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="192" t="s">
+      <c r="A4" s="242" t="s">
         <v>369</v>
       </c>
-      <c r="B4" s="193"/>
-      <c r="C4" s="193"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="194"/>
+      <c r="B4" s="243"/>
+      <c r="C4" s="243"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="244"/>
     </row>
     <row r="5" spans="1:12" s="42" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="195"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="197" t="s">
+      <c r="A5" s="159"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="160"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="161" t="s">
         <v>230</v>
       </c>
     </row>
@@ -4193,21 +4170,21 @@
       <c r="A6" s="63" t="s">
         <v>367</v>
       </c>
-      <c r="B6" s="135" t="s">
+      <c r="B6" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="273" t="s">
+      <c r="C6" s="251"/>
+      <c r="D6" s="222" t="s">
         <v>368</v>
       </c>
       <c r="E6" s="125" t="str">
         <f>A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="F6" s="136" t="s">
+      <c r="F6" s="252" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="137"/>
+      <c r="G6" s="253"/>
       <c r="H6" s="63" t="str">
         <f>D6</f>
         <v>Current Year 2025-26</v>
@@ -4215,12 +4192,12 @@
     </row>
     <row r="7" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45"/>
-      <c r="B7" s="274" t="s">
+      <c r="B7" s="66" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="46"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="271"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="220"/>
       <c r="F7" s="66" t="s">
         <v>0</v>
       </c>
@@ -4231,14 +4208,14 @@
       <c r="A8" s="44">
         <v>100000</v>
       </c>
-      <c r="B8" s="276" t="s">
+      <c r="B8" t="s">
         <v>222</v>
       </c>
       <c r="C8" s="46"/>
-      <c r="D8" s="277">
+      <c r="D8" s="224">
         <v>100000</v>
       </c>
-      <c r="E8" s="271">
+      <c r="E8" s="220">
         <v>764</v>
       </c>
       <c r="F8" t="s">
@@ -4251,10 +4228,9 @@
     </row>
     <row r="9" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
-      <c r="B9" s="276"/>
       <c r="C9" s="46"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="271">
+      <c r="D9" s="225"/>
+      <c r="E9" s="220">
         <v>14409</v>
       </c>
       <c r="F9" t="s">
@@ -4269,12 +4245,12 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
-      <c r="B10" s="274" t="s">
+      <c r="B10" s="66" t="s">
         <v>221</v>
       </c>
       <c r="C10" s="46"/>
-      <c r="D10" s="278"/>
-      <c r="E10" s="271">
+      <c r="D10" s="225"/>
+      <c r="E10" s="220">
         <v>5895</v>
       </c>
       <c r="F10" t="s">
@@ -4296,14 +4272,14 @@
       <c r="A11" s="12">
         <v>14000</v>
       </c>
-      <c r="B11" s="276" t="s">
+      <c r="B11" t="s">
         <v>223</v>
       </c>
       <c r="C11" s="46"/>
-      <c r="D11" s="279">
+      <c r="D11" s="226">
         <v>14000</v>
       </c>
-      <c r="E11" s="271">
+      <c r="E11" s="220">
         <v>15608</v>
       </c>
       <c r="F11" t="s">
@@ -4319,10 +4295,9 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
-      <c r="B12" s="276"/>
       <c r="C12" s="46"/>
-      <c r="D12" s="278"/>
-      <c r="E12" s="271">
+      <c r="D12" s="225"/>
+      <c r="E12" s="220">
         <v>236540.74</v>
       </c>
       <c r="F12" t="s">
@@ -4340,12 +4315,12 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
-      <c r="B13" s="274" t="s">
+      <c r="B13" s="66" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="46"/>
-      <c r="D13" s="278"/>
-      <c r="E13" s="271"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="220"/>
       <c r="G13" s="46"/>
       <c r="H13" s="12"/>
       <c r="J13" s="39"/>
@@ -4354,15 +4329,15 @@
       <c r="A14" s="12">
         <v>627286</v>
       </c>
-      <c r="B14" s="276" t="s">
+      <c r="B14" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="46">
         <f>SUM(A14:A17)</f>
         <v>734254</v>
       </c>
-      <c r="D14" s="278"/>
-      <c r="E14" s="271"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="220"/>
       <c r="F14" s="66" t="s">
         <v>226</v>
       </c>
@@ -4374,15 +4349,15 @@
       <c r="A15" s="12">
         <v>23174</v>
       </c>
-      <c r="B15" s="276" t="s">
+      <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="46">
         <f>IE!D46</f>
         <v>10419</v>
       </c>
-      <c r="D15" s="278"/>
-      <c r="E15" s="271">
+      <c r="D15" s="225"/>
+      <c r="E15" s="220">
         <v>500</v>
       </c>
       <c r="F15" t="s">
@@ -4398,14 +4373,14 @@
       <c r="A16" s="12">
         <v>300</v>
       </c>
-      <c r="B16" s="276" t="s">
+      <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="46">
         <v>0</v>
       </c>
-      <c r="D16" s="278"/>
-      <c r="E16" s="271">
+      <c r="D16" s="225"/>
+      <c r="E16" s="220">
         <v>100</v>
       </c>
       <c r="F16" t="s">
@@ -4421,18 +4396,18 @@
       <c r="A17" s="12">
         <v>83494</v>
       </c>
-      <c r="B17" s="276" t="s">
+      <c r="B17" t="s">
         <v>115</v>
       </c>
       <c r="C17" s="77">
         <f>'FD Interest Working'!E117</f>
         <v>95399</v>
       </c>
-      <c r="D17" s="279">
+      <c r="D17" s="226">
         <f>SUM(C14:C17)</f>
         <v>840072</v>
       </c>
-      <c r="E17" s="271">
+      <c r="E17" s="220">
         <v>2500</v>
       </c>
       <c r="F17" t="s">
@@ -4446,10 +4421,9 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
-      <c r="B18" s="276"/>
       <c r="C18" s="46"/>
-      <c r="D18" s="278"/>
-      <c r="E18" s="271">
+      <c r="D18" s="225"/>
+      <c r="E18" s="220">
         <v>8108609</v>
       </c>
       <c r="F18" s="66" t="s">
@@ -4465,12 +4439,12 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="66" t="s">
         <v>175</v>
       </c>
       <c r="C19" s="46"/>
-      <c r="D19" s="278"/>
-      <c r="E19" s="271">
+      <c r="D19" s="225"/>
+      <c r="E19" s="220">
         <v>576281</v>
       </c>
       <c r="F19" t="s">
@@ -4490,15 +4464,15 @@
       <c r="A20" s="12">
         <v>74603</v>
       </c>
-      <c r="B20" s="276" t="s">
+      <c r="B20" t="s">
         <v>176</v>
       </c>
       <c r="C20" s="46">
         <f>SUM(A20:A23)</f>
         <v>96383</v>
       </c>
-      <c r="D20" s="278"/>
-      <c r="E20" s="271"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="220"/>
       <c r="G20" s="46"/>
       <c r="H20" s="12"/>
       <c r="J20" s="39"/>
@@ -4507,14 +4481,14 @@
       <c r="A21" s="12">
         <v>0</v>
       </c>
-      <c r="B21" s="276" t="s">
+      <c r="B21" t="s">
         <v>168</v>
       </c>
       <c r="C21" s="46">
         <v>0</v>
       </c>
-      <c r="D21" s="279"/>
-      <c r="E21" s="271"/>
+      <c r="D21" s="226"/>
+      <c r="E21" s="220"/>
       <c r="F21" s="66" t="s">
         <v>3</v>
       </c>
@@ -4526,14 +4500,14 @@
       <c r="A22" s="12">
         <v>10000</v>
       </c>
-      <c r="B22" s="276" t="s">
+      <c r="B22" t="s">
         <v>325</v>
       </c>
       <c r="C22" s="46">
         <v>0</v>
       </c>
-      <c r="D22" s="279"/>
-      <c r="E22" s="271">
+      <c r="D22" s="226"/>
+      <c r="E22" s="220">
         <v>12131.5</v>
       </c>
       <c r="F22" t="s">
@@ -4549,18 +4523,18 @@
       <c r="A23" s="12">
         <v>11780</v>
       </c>
-      <c r="B23" s="276" t="s">
+      <c r="B23" t="s">
         <v>115</v>
       </c>
       <c r="C23" s="73">
         <f>'FD Interest Working'!E115</f>
         <v>7902</v>
       </c>
-      <c r="D23" s="279">
+      <c r="D23" s="226">
         <f>SUM(C20:C23)</f>
         <v>104285</v>
       </c>
-      <c r="E23" s="271"/>
+      <c r="E23" s="220"/>
       <c r="G23" s="46"/>
       <c r="H23" s="12"/>
       <c r="J23" s="39"/>
@@ -4568,10 +4542,9 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
-      <c r="B24" s="276"/>
       <c r="C24" s="46"/>
-      <c r="D24" s="278"/>
-      <c r="E24" s="271"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="220"/>
       <c r="F24" s="66" t="s">
         <v>4</v>
       </c>
@@ -4581,12 +4554,12 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
-      <c r="B25" s="274" t="s">
+      <c r="B25" s="66" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="46"/>
-      <c r="D25" s="278"/>
-      <c r="E25" s="271">
+      <c r="D25" s="225"/>
+      <c r="E25" s="220">
         <v>35838000</v>
       </c>
       <c r="F25" t="s">
@@ -4602,15 +4575,15 @@
       <c r="A26" s="12">
         <v>1389293</v>
       </c>
-      <c r="B26" s="276" t="s">
+      <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="46">
         <f>SUM(A26:A28)</f>
         <v>1584118</v>
       </c>
-      <c r="D26" s="278"/>
-      <c r="E26" s="271">
+      <c r="D26" s="225"/>
+      <c r="E26" s="220">
         <v>189800</v>
       </c>
       <c r="F26" s="66" t="s">
@@ -4627,14 +4600,14 @@
       <c r="A27" s="12">
         <v>103200</v>
       </c>
-      <c r="B27" s="276" t="s">
+      <c r="B27" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="46">
         <v>54000</v>
       </c>
-      <c r="D27" s="278"/>
-      <c r="E27" s="271"/>
+      <c r="D27" s="225"/>
+      <c r="E27" s="220"/>
       <c r="F27" s="2"/>
       <c r="G27" s="46"/>
       <c r="H27" s="12"/>
@@ -4644,18 +4617,18 @@
       <c r="A28" s="12">
         <v>91625</v>
       </c>
-      <c r="B28" s="276" t="s">
+      <c r="B28" t="s">
         <v>115</v>
       </c>
       <c r="C28" s="73">
         <f>'FD Interest Working'!E114</f>
         <v>112301</v>
       </c>
-      <c r="D28" s="279">
+      <c r="D28" s="226">
         <f>SUM(C26:C28)</f>
         <v>1750419</v>
       </c>
-      <c r="E28" s="271"/>
+      <c r="E28" s="220"/>
       <c r="F28" s="66" t="s">
         <v>5</v>
       </c>
@@ -4665,10 +4638,9 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
-      <c r="B29" s="276"/>
       <c r="C29" s="46"/>
-      <c r="D29" s="278"/>
-      <c r="E29" s="271">
+      <c r="D29" s="225"/>
+      <c r="E29" s="220">
         <v>2870</v>
       </c>
       <c r="F29" t="s">
@@ -4683,12 +4655,12 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="45"/>
-      <c r="B30" s="274" t="s">
+      <c r="B30" s="66" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="278"/>
-      <c r="E30" s="271"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="220"/>
       <c r="G30" s="46"/>
       <c r="H30" s="12"/>
       <c r="J30" s="39"/>
@@ -4697,15 +4669,15 @@
       <c r="A31" s="12">
         <v>1069196</v>
       </c>
-      <c r="B31" s="276" t="s">
+      <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="46">
         <f>SUM(A31:A33)</f>
         <v>1203632</v>
       </c>
-      <c r="D31" s="278"/>
-      <c r="E31" s="271"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="220"/>
       <c r="F31" s="66" t="s">
         <v>228</v>
       </c>
@@ -4717,14 +4689,14 @@
       <c r="A32" s="12">
         <v>58224</v>
       </c>
-      <c r="B32" s="276" t="s">
+      <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" s="46">
         <v>58224</v>
       </c>
-      <c r="D32" s="278"/>
-      <c r="E32" s="271">
+      <c r="D32" s="225"/>
+      <c r="E32" s="220">
         <v>12286</v>
       </c>
       <c r="F32" t="s">
@@ -4740,18 +4712,18 @@
       <c r="A33" s="12">
         <v>76212</v>
       </c>
-      <c r="B33" s="276" t="s">
+      <c r="B33" t="s">
         <v>115</v>
       </c>
       <c r="C33" s="73">
         <f>'FD Interest Working'!E122</f>
         <v>87678</v>
       </c>
-      <c r="D33" s="279">
+      <c r="D33" s="226">
         <f>SUM(C31:C33)</f>
         <v>1349534</v>
       </c>
-      <c r="E33" s="271">
+      <c r="E33" s="220">
         <v>4295</v>
       </c>
       <c r="F33" t="s">
@@ -4768,22 +4740,21 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="12"/>
-      <c r="B34" s="276"/>
       <c r="C34" s="46"/>
-      <c r="D34" s="278"/>
-      <c r="E34" s="271"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="220"/>
       <c r="G34" s="46"/>
       <c r="H34" s="22"/>
       <c r="J34" s="39"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
-      <c r="B35" s="274" t="s">
+      <c r="B35" s="66" t="s">
         <v>40</v>
       </c>
       <c r="C35" s="46"/>
-      <c r="D35" s="278"/>
-      <c r="E35" s="271"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="220"/>
       <c r="G35" s="46"/>
       <c r="H35" s="12"/>
       <c r="J35" s="39"/>
@@ -4792,15 +4763,15 @@
       <c r="A36" s="12">
         <v>4563998</v>
       </c>
-      <c r="B36" s="276" t="s">
+      <c r="B36" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="46">
         <f>SUM(A36:A39)</f>
         <v>3453942</v>
       </c>
-      <c r="D36" s="278"/>
-      <c r="E36" s="271"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="220"/>
       <c r="F36" s="66" t="s">
         <v>229</v>
       </c>
@@ -4812,14 +4783,14 @@
       <c r="A37" s="12">
         <v>175056</v>
       </c>
-      <c r="B37" s="276" t="s">
+      <c r="B37" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="46">
         <v>175056</v>
       </c>
-      <c r="D37" s="278"/>
-      <c r="E37" s="271">
+      <c r="D37" s="225"/>
+      <c r="E37" s="220">
         <v>50131</v>
       </c>
       <c r="F37" t="s">
@@ -4838,15 +4809,15 @@
       <c r="A38" s="12">
         <v>-1489986</v>
       </c>
-      <c r="B38" s="276" t="s">
+      <c r="B38" t="s">
         <v>302</v>
       </c>
       <c r="C38" s="46">
         <f>IE!C20</f>
         <v>-152099</v>
       </c>
-      <c r="D38" s="278"/>
-      <c r="E38" s="271"/>
+      <c r="D38" s="225"/>
+      <c r="E38" s="220"/>
       <c r="G38" s="46"/>
       <c r="H38" s="12"/>
       <c r="J38" s="39"/>
@@ -4856,40 +4827,39 @@
       <c r="A39" s="12">
         <v>204874</v>
       </c>
-      <c r="B39" s="276" t="s">
+      <c r="B39" t="s">
         <v>115</v>
       </c>
       <c r="C39" s="73">
         <f>'FD Interest Working'!E119</f>
         <v>237133</v>
       </c>
-      <c r="D39" s="279">
+      <c r="D39" s="226">
         <f>SUM(C36:C39)</f>
         <v>3714032</v>
       </c>
-      <c r="E39" s="271"/>
+      <c r="E39" s="220"/>
       <c r="G39" s="46"/>
       <c r="H39" s="12"/>
       <c r="J39" s="39"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="45"/>
-      <c r="B40" s="276"/>
       <c r="C40" s="46"/>
-      <c r="D40" s="278"/>
-      <c r="E40" s="271"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="220"/>
       <c r="G40" s="46"/>
       <c r="H40" s="12"/>
       <c r="J40" s="39"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
-      <c r="B41" s="274" t="s">
+      <c r="B41" s="66" t="s">
         <v>116</v>
       </c>
       <c r="C41" s="46"/>
-      <c r="D41" s="278"/>
-      <c r="E41" s="271"/>
+      <c r="D41" s="225"/>
+      <c r="E41" s="220"/>
       <c r="G41" s="46"/>
       <c r="H41" s="12"/>
       <c r="J41" s="39"/>
@@ -4898,15 +4868,15 @@
       <c r="A42" s="12">
         <v>719610</v>
       </c>
-      <c r="B42" s="276" t="s">
+      <c r="B42" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="46">
         <f>SUM(A42:A43)</f>
         <v>767792</v>
       </c>
-      <c r="D42" s="278"/>
-      <c r="E42" s="271"/>
+      <c r="D42" s="225"/>
+      <c r="E42" s="220"/>
       <c r="G42" s="46"/>
       <c r="H42" s="12"/>
       <c r="J42" s="39"/>
@@ -4915,40 +4885,39 @@
       <c r="A43" s="12">
         <v>48182</v>
       </c>
-      <c r="B43" s="276" t="s">
+      <c r="B43" t="s">
         <v>115</v>
       </c>
       <c r="C43" s="73">
         <f>'FD Interest Working'!E116</f>
         <v>55965</v>
       </c>
-      <c r="D43" s="279">
+      <c r="D43" s="226">
         <f>SUM(C42:C43)</f>
         <v>823757</v>
       </c>
-      <c r="E43" s="271"/>
+      <c r="E43" s="220"/>
       <c r="G43" s="46"/>
       <c r="H43" s="12"/>
       <c r="J43" s="39"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="45"/>
-      <c r="B44" s="276"/>
       <c r="C44" s="46"/>
-      <c r="D44" s="278"/>
-      <c r="E44" s="271"/>
+      <c r="D44" s="225"/>
+      <c r="E44" s="220"/>
       <c r="G44" s="46"/>
       <c r="H44" s="12"/>
       <c r="J44" s="39"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
-      <c r="B45" s="274" t="s">
+      <c r="B45" s="66" t="s">
         <v>69</v>
       </c>
       <c r="C45" s="46"/>
-      <c r="D45" s="278"/>
-      <c r="E45" s="271"/>
+      <c r="D45" s="225"/>
+      <c r="E45" s="220"/>
       <c r="G45" s="46"/>
       <c r="H45" s="12"/>
       <c r="J45" s="39"/>
@@ -4957,15 +4926,15 @@
       <c r="A46" s="12">
         <v>19894</v>
       </c>
-      <c r="B46" s="276" t="s">
+      <c r="B46" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="46">
         <f>SUM(A46:A48)</f>
         <v>1103</v>
       </c>
-      <c r="D46" s="278"/>
-      <c r="E46" s="271"/>
+      <c r="D46" s="225"/>
+      <c r="E46" s="220"/>
       <c r="G46" s="46"/>
       <c r="H46" s="12"/>
       <c r="J46" s="39"/>
@@ -4974,14 +4943,14 @@
       <c r="A47" s="12">
         <v>5376</v>
       </c>
-      <c r="B47" s="276" t="s">
+      <c r="B47" t="s">
         <v>14</v>
       </c>
       <c r="C47" s="46">
         <v>5376</v>
       </c>
-      <c r="D47" s="279"/>
-      <c r="E47" s="271"/>
+      <c r="D47" s="226"/>
+      <c r="E47" s="220"/>
       <c r="G47" s="46"/>
       <c r="H47" s="12"/>
       <c r="J47" s="39"/>
@@ -4990,39 +4959,38 @@
       <c r="A48" s="12">
         <v>-24167</v>
       </c>
-      <c r="B48" s="276" t="s">
+      <c r="B48" t="s">
         <v>279</v>
       </c>
       <c r="C48" s="77">
         <v>0</v>
       </c>
-      <c r="D48" s="279">
+      <c r="D48" s="226">
         <f>SUM(C46:C48)</f>
         <v>6479</v>
       </c>
-      <c r="E48" s="271"/>
+      <c r="E48" s="220"/>
       <c r="G48" s="46"/>
       <c r="H48" s="12"/>
       <c r="J48" s="39"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="12"/>
-      <c r="B49" s="276"/>
       <c r="C49" s="46"/>
-      <c r="D49" s="278"/>
-      <c r="E49" s="271"/>
+      <c r="D49" s="225"/>
+      <c r="E49" s="220"/>
       <c r="G49" s="46"/>
       <c r="H49" s="12"/>
       <c r="J49" s="39"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
-      <c r="B50" s="274" t="s">
+      <c r="B50" s="66" t="s">
         <v>234</v>
       </c>
       <c r="C50" s="46"/>
-      <c r="D50" s="278"/>
-      <c r="E50" s="271"/>
+      <c r="D50" s="225"/>
+      <c r="E50" s="220"/>
       <c r="G50" s="46"/>
       <c r="H50" s="12"/>
       <c r="J50" s="39"/>
@@ -5031,15 +4999,15 @@
       <c r="A51" s="12">
         <v>84000</v>
       </c>
-      <c r="B51" s="276" t="s">
+      <c r="B51" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="46">
         <f>'Sch III, IV, V, VI &amp; VII'!D21</f>
         <v>80000</v>
       </c>
-      <c r="D51" s="278"/>
-      <c r="E51" s="271"/>
+      <c r="D51" s="225"/>
+      <c r="E51" s="220"/>
       <c r="G51" s="46"/>
       <c r="H51" s="12"/>
       <c r="J51" s="39"/>
@@ -5048,14 +5016,14 @@
       <c r="A52" s="12">
         <v>0</v>
       </c>
-      <c r="B52" s="276" t="s">
+      <c r="B52" t="s">
         <v>38</v>
       </c>
       <c r="C52" s="46">
         <v>0</v>
       </c>
-      <c r="D52" s="278"/>
-      <c r="E52" s="271"/>
+      <c r="D52" s="225"/>
+      <c r="E52" s="220"/>
       <c r="G52" s="46"/>
       <c r="H52" s="12"/>
       <c r="J52" s="39"/>
@@ -5064,14 +5032,14 @@
       <c r="A53" s="12">
         <v>0</v>
       </c>
-      <c r="B53" s="276" t="s">
+      <c r="B53" t="s">
         <v>177</v>
       </c>
       <c r="C53" s="46">
         <v>0</v>
       </c>
-      <c r="D53" s="279"/>
-      <c r="E53" s="271"/>
+      <c r="D53" s="226"/>
+      <c r="E53" s="220"/>
       <c r="G53" s="46"/>
       <c r="H53" s="12"/>
       <c r="J53" s="39"/>
@@ -5080,27 +5048,26 @@
       <c r="A54" s="12">
         <v>-4000</v>
       </c>
-      <c r="B54" s="276" t="s">
+      <c r="B54" t="s">
         <v>145</v>
       </c>
       <c r="C54" s="73">
         <v>0</v>
       </c>
-      <c r="D54" s="279">
+      <c r="D54" s="226">
         <f>SUM(C51:C54)</f>
         <v>80000</v>
       </c>
-      <c r="E54" s="271"/>
+      <c r="E54" s="220"/>
       <c r="G54" s="46"/>
       <c r="H54" s="12"/>
       <c r="J54" s="39"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="12"/>
-      <c r="B55" s="276"/>
       <c r="C55" s="46"/>
-      <c r="D55" s="278"/>
-      <c r="E55" s="271"/>
+      <c r="D55" s="225"/>
+      <c r="E55" s="220"/>
       <c r="G55" s="46"/>
       <c r="H55" s="12"/>
       <c r="J55" s="39"/>
@@ -5109,14 +5076,14 @@
       <c r="A56" s="12">
         <v>35838000</v>
       </c>
-      <c r="B56" s="276" t="s">
+      <c r="B56" t="s">
         <v>85</v>
       </c>
       <c r="C56" s="46"/>
-      <c r="D56" s="279">
+      <c r="D56" s="226">
         <v>35838000</v>
       </c>
-      <c r="E56" s="271"/>
+      <c r="E56" s="220"/>
       <c r="G56" s="46"/>
       <c r="H56" s="12"/>
       <c r="I56" s="47"/>
@@ -5124,10 +5091,9 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="45"/>
-      <c r="B57" s="276"/>
       <c r="C57" s="46"/>
-      <c r="D57" s="278"/>
-      <c r="E57" s="271"/>
+      <c r="D57" s="225"/>
+      <c r="E57" s="220"/>
       <c r="G57" s="46"/>
       <c r="H57" s="12"/>
       <c r="J57" s="39"/>
@@ -5137,15 +5103,15 @@
       <c r="A58" s="12">
         <v>23558</v>
       </c>
-      <c r="B58" s="274" t="s">
+      <c r="B58" s="66" t="s">
         <v>235</v>
       </c>
       <c r="C58" s="46"/>
-      <c r="D58" s="279">
+      <c r="D58" s="226">
         <f>'Sch III, IV, V, VI &amp; VII'!D31</f>
         <v>31977</v>
       </c>
-      <c r="E58" s="271"/>
+      <c r="E58" s="220"/>
       <c r="F58" s="40"/>
       <c r="G58" s="46"/>
       <c r="H58" s="12"/>
@@ -5153,10 +5119,9 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="12"/>
-      <c r="B59" s="276"/>
       <c r="C59" s="46"/>
-      <c r="D59" s="278"/>
-      <c r="E59" s="271"/>
+      <c r="D59" s="225"/>
+      <c r="E59" s="220"/>
       <c r="G59" s="46"/>
       <c r="H59" s="12"/>
       <c r="I59" s="40"/>
@@ -5164,12 +5129,12 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="12"/>
-      <c r="B60" s="274" t="s">
+      <c r="B60" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="278"/>
-      <c r="E60" s="271"/>
+      <c r="D60" s="225"/>
+      <c r="E60" s="220"/>
       <c r="G60" s="46"/>
       <c r="H60" s="12"/>
       <c r="J60" s="39"/>
@@ -5178,37 +5143,36 @@
       <c r="A61" s="12">
         <v>61831</v>
       </c>
-      <c r="B61" s="274" t="s">
+      <c r="B61" s="66" t="s">
         <v>236</v>
       </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="279">
+      <c r="D61" s="226">
         <f>'Sch III, IV, V, VI &amp; VII'!D48</f>
         <v>45591.520000000004</v>
       </c>
-      <c r="E61" s="271"/>
+      <c r="E61" s="220"/>
       <c r="G61" s="46"/>
       <c r="H61" s="12"/>
       <c r="J61" s="39"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="12"/>
-      <c r="B62" s="276"/>
       <c r="C62" s="46"/>
-      <c r="D62" s="278"/>
-      <c r="E62" s="271"/>
+      <c r="D62" s="225"/>
+      <c r="E62" s="220"/>
       <c r="G62" s="46"/>
       <c r="H62" s="12"/>
       <c r="J62" s="39"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
-      <c r="B63" s="274" t="s">
+      <c r="B63" s="66" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="46"/>
-      <c r="D63" s="278"/>
-      <c r="E63" s="271"/>
+      <c r="D63" s="225"/>
+      <c r="E63" s="220"/>
       <c r="G63" s="46"/>
       <c r="H63" s="12"/>
       <c r="J63" s="39"/>
@@ -5217,15 +5181,15 @@
       <c r="A64" s="12">
         <v>1138986.99</v>
       </c>
-      <c r="B64" s="276" t="s">
+      <c r="B64" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="46">
         <f>SUM(A64:A67)</f>
         <v>1212107.24</v>
       </c>
-      <c r="D64" s="278"/>
-      <c r="E64" s="271"/>
+      <c r="D64" s="225"/>
+      <c r="E64" s="220"/>
       <c r="G64" s="46"/>
       <c r="H64" s="12"/>
       <c r="I64" s="47"/>
@@ -5234,14 +5198,14 @@
       <c r="A65" s="12">
         <v>3600</v>
       </c>
-      <c r="B65" s="274" t="s">
+      <c r="B65" s="66" t="s">
         <v>326</v>
       </c>
       <c r="C65" s="46">
         <v>0</v>
       </c>
-      <c r="D65" s="278"/>
-      <c r="E65" s="271"/>
+      <c r="D65" s="225"/>
+      <c r="E65" s="220"/>
       <c r="G65" s="46"/>
       <c r="H65" s="12"/>
       <c r="I65" s="47"/>
@@ -5250,14 +5214,14 @@
       <c r="A66" s="12">
         <v>0</v>
       </c>
-      <c r="B66" s="274" t="s">
+      <c r="B66" s="66" t="s">
         <v>598</v>
       </c>
       <c r="C66" s="46">
         <v>2366</v>
       </c>
-      <c r="D66" s="278"/>
-      <c r="E66" s="271"/>
+      <c r="D66" s="225"/>
+      <c r="E66" s="220"/>
       <c r="G66" s="46"/>
       <c r="H66" s="12"/>
       <c r="I66" s="47"/>
@@ -5266,18 +5230,18 @@
       <c r="A67" s="41">
         <v>69520.25</v>
       </c>
-      <c r="B67" s="276" t="s">
+      <c r="B67" t="s">
         <v>303</v>
       </c>
       <c r="C67" s="73">
         <f>IE!D47</f>
         <v>31255.589999999967</v>
       </c>
-      <c r="D67" s="279">
+      <c r="D67" s="226">
         <f>SUM(C64:C67)</f>
         <v>1245728.83</v>
       </c>
-      <c r="E67" s="271"/>
+      <c r="E67" s="220"/>
       <c r="G67" s="77"/>
       <c r="H67" s="12"/>
       <c r="I67" s="47"/>
@@ -5287,22 +5251,22 @@
         <f>SUM(A10:A67)</f>
         <v>45070720.240000002</v>
       </c>
-      <c r="B68" s="140" t="s">
+      <c r="B68" s="256" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="141"/>
-      <c r="D68" s="280">
+      <c r="C68" s="257"/>
+      <c r="D68" s="227">
         <f>SUM(D9:D67)</f>
         <v>45843875.350000001</v>
       </c>
-      <c r="E68" s="272">
+      <c r="E68" s="221">
         <f>SUM(E8:E67)</f>
         <v>45070720.240000002</v>
       </c>
-      <c r="F68" s="138" t="s">
+      <c r="F68" s="254" t="s">
         <v>28</v>
       </c>
-      <c r="G68" s="139"/>
+      <c r="G68" s="255"/>
       <c r="H68" s="75">
         <f>SUM(H8:H67)</f>
         <v>45843875.350000001</v>
@@ -5319,75 +5283,75 @@
       <c r="L68" s="94"/>
     </row>
     <row r="69" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="153"/>
+      <c r="A69" s="133"/>
       <c r="B69" s="114"/>
       <c r="C69" s="13"/>
       <c r="D69" s="59"/>
-      <c r="E69" s="154"/>
-      <c r="F69" s="154"/>
-      <c r="G69" s="154"/>
-      <c r="H69" s="155"/>
+      <c r="E69" s="258"/>
+      <c r="F69" s="258"/>
+      <c r="G69" s="258"/>
+      <c r="H69" s="134"/>
       <c r="J69" s="39"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="156" t="s">
+      <c r="A70" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="157"/>
-      <c r="C70" s="157"/>
-      <c r="D70" s="158"/>
-      <c r="E70" s="159"/>
-      <c r="F70" s="157"/>
-      <c r="G70" s="159"/>
-      <c r="H70" s="160"/>
+      <c r="B70" s="136"/>
+      <c r="C70" s="136"/>
+      <c r="D70" s="137"/>
+      <c r="E70" s="138"/>
+      <c r="F70" s="136"/>
+      <c r="G70" s="138"/>
+      <c r="H70" s="139"/>
       <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="161"/>
-      <c r="B71" s="157"/>
-      <c r="C71" s="157"/>
-      <c r="D71" s="162"/>
-      <c r="E71" s="163"/>
-      <c r="F71" s="164" t="s">
+      <c r="A71" s="140"/>
+      <c r="B71" s="136"/>
+      <c r="C71" s="136"/>
+      <c r="D71" s="141"/>
+      <c r="E71" s="142"/>
+      <c r="F71" s="259" t="s">
         <v>618</v>
       </c>
-      <c r="G71" s="164"/>
-      <c r="H71" s="165"/>
+      <c r="G71" s="259"/>
+      <c r="H71" s="260"/>
       <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="161"/>
-      <c r="B72" s="157"/>
-      <c r="C72" s="157"/>
-      <c r="D72" s="162"/>
-      <c r="E72" s="163"/>
-      <c r="F72" s="166"/>
-      <c r="G72" s="163"/>
-      <c r="H72" s="167"/>
+      <c r="A72" s="140"/>
+      <c r="B72" s="136"/>
+      <c r="C72" s="136"/>
+      <c r="D72" s="141"/>
+      <c r="E72" s="142"/>
+      <c r="F72" s="144"/>
+      <c r="G72" s="142"/>
+      <c r="H72" s="145"/>
       <c r="I72" s="47"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="161"/>
-      <c r="B73" s="157"/>
-      <c r="C73" s="157"/>
-      <c r="D73" s="162"/>
-      <c r="E73" s="163"/>
-      <c r="F73" s="166"/>
-      <c r="G73" s="163"/>
-      <c r="H73" s="167"/>
+      <c r="A73" s="140"/>
+      <c r="B73" s="136"/>
+      <c r="C73" s="136"/>
+      <c r="D73" s="141"/>
+      <c r="E73" s="142"/>
+      <c r="F73" s="144"/>
+      <c r="G73" s="142"/>
+      <c r="H73" s="145"/>
       <c r="I73" s="47"/>
     </row>
     <row r="74" spans="1:12" s="76" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="168" t="s">
+      <c r="A74" s="146" t="s">
         <v>619</v>
       </c>
-      <c r="B74" s="169"/>
-      <c r="C74" s="170"/>
-      <c r="D74" s="162"/>
-      <c r="E74" s="163"/>
-      <c r="F74" s="166"/>
-      <c r="G74" s="163"/>
-      <c r="H74" s="167"/>
+      <c r="B74" s="147"/>
+      <c r="C74" s="148"/>
+      <c r="D74" s="141"/>
+      <c r="E74" s="142"/>
+      <c r="F74" s="144"/>
+      <c r="G74" s="142"/>
+      <c r="H74" s="145"/>
       <c r="I74" s="113">
         <f>A68-E68</f>
         <v>0</v>
@@ -5399,46 +5363,46 @@
       <c r="K74" s="94"/>
       <c r="L74" s="94"/>
     </row>
-    <row r="75" spans="1:12" s="157" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="171" t="s">
+    <row r="75" spans="1:12" s="136" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="149" t="s">
         <v>620</v>
       </c>
-      <c r="B75" s="169"/>
-      <c r="C75" s="170"/>
-      <c r="D75" s="162"/>
-      <c r="E75" s="163"/>
-      <c r="F75" s="166"/>
-      <c r="G75" s="163"/>
-      <c r="H75" s="167"/>
-      <c r="J75" s="172"/>
-    </row>
-    <row r="76" spans="1:12" s="157" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="171" t="s">
+      <c r="B75" s="147"/>
+      <c r="C75" s="148"/>
+      <c r="D75" s="141"/>
+      <c r="E75" s="142"/>
+      <c r="F75" s="144"/>
+      <c r="G75" s="142"/>
+      <c r="H75" s="145"/>
+      <c r="J75" s="150"/>
+    </row>
+    <row r="76" spans="1:12" s="136" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="149" t="s">
         <v>621</v>
       </c>
-      <c r="B76" s="169"/>
-      <c r="C76" s="170"/>
-      <c r="D76" s="162"/>
-      <c r="E76" s="163"/>
-      <c r="F76" s="173" t="s">
+      <c r="B76" s="147"/>
+      <c r="C76" s="148"/>
+      <c r="D76" s="141"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="261" t="s">
         <v>622</v>
       </c>
-      <c r="G76" s="173"/>
-      <c r="H76" s="174"/>
-      <c r="J76" s="172"/>
-    </row>
-    <row r="77" spans="1:12" s="157" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="175">
-        <v>46235</v>
-      </c>
-      <c r="B77" s="176"/>
-      <c r="C77" s="176"/>
-      <c r="D77" s="177"/>
-      <c r="E77" s="178"/>
-      <c r="F77" s="179"/>
-      <c r="G77" s="178"/>
-      <c r="H77" s="180"/>
-      <c r="J77" s="172"/>
+      <c r="G76" s="261"/>
+      <c r="H76" s="262"/>
+      <c r="J76" s="150"/>
+    </row>
+    <row r="77" spans="1:12" s="136" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="240">
+        <v>46242</v>
+      </c>
+      <c r="B77" s="241"/>
+      <c r="C77" s="241"/>
+      <c r="D77" s="152"/>
+      <c r="E77" s="153"/>
+      <c r="F77" s="154"/>
+      <c r="G77" s="153"/>
+      <c r="H77" s="155"/>
+      <c r="J77" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5484,63 +5448,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="183"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="247"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="184" t="str">
+      <c r="A2" s="248" t="str">
         <f>BS!A2</f>
         <v>(Regd. No. BOM/HSG/3365/1972)</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="186"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="249"/>
+      <c r="D2" s="249"/>
+      <c r="E2" s="249"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="248" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="186"/>
+      <c r="B3" s="249"/>
+      <c r="C3" s="249"/>
+      <c r="D3" s="249"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="249"/>
+      <c r="G3" s="249"/>
+      <c r="H3" s="250"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="187" t="s">
+      <c r="A4" s="263" t="s">
         <v>370</v>
       </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="188"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="265"/>
     </row>
     <row r="5" spans="1:11" s="16" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="189"/>
-      <c r="B5" s="190"/>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="190"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="191" t="s">
+      <c r="A5" s="156"/>
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="158" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5549,22 +5513,22 @@
         <f>BS!A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="B6" s="143" t="s">
+      <c r="B6" s="266" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="143"/>
-      <c r="D6" s="283" t="str">
+      <c r="C6" s="266"/>
+      <c r="D6" s="230" t="str">
         <f>BS!D6</f>
         <v>Current Year 2025-26</v>
       </c>
-      <c r="E6" s="281" t="str">
+      <c r="E6" s="228" t="str">
         <f>A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="F6" s="143" t="s">
+      <c r="F6" s="266" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="143"/>
+      <c r="G6" s="266"/>
       <c r="H6" s="82" t="str">
         <f>D6</f>
         <v>Current Year 2025-26</v>
@@ -5576,7 +5540,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="78"/>
-      <c r="D7" s="284"/>
+      <c r="D7" s="231"/>
       <c r="E7" s="19"/>
       <c r="F7" s="64" t="s">
         <v>237</v>
@@ -5592,7 +5556,7 @@
         <v>71</v>
       </c>
       <c r="C8" s="25"/>
-      <c r="D8" s="285">
+      <c r="D8" s="232">
         <v>16296</v>
       </c>
       <c r="E8" s="14">
@@ -5610,7 +5574,7 @@
       <c r="A9" s="20"/>
       <c r="B9" s="20"/>
       <c r="C9" s="25"/>
-      <c r="D9" s="286"/>
+      <c r="D9" s="233"/>
       <c r="E9" s="14">
         <v>48000</v>
       </c>
@@ -5632,7 +5596,7 @@
       <c r="C10" s="79">
         <v>179811.41</v>
       </c>
-      <c r="D10" s="286"/>
+      <c r="D10" s="233"/>
       <c r="E10" s="14">
         <v>115200</v>
       </c>
@@ -5655,7 +5619,7 @@
         <f>58680+4000</f>
         <v>62680</v>
       </c>
-      <c r="D11" s="285">
+      <c r="D11" s="232">
         <f>SUM(C10:C11)</f>
         <v>242491.41</v>
       </c>
@@ -5674,7 +5638,7 @@
       <c r="A12" s="20"/>
       <c r="B12" s="20"/>
       <c r="C12" s="25"/>
-      <c r="D12" s="286"/>
+      <c r="D12" s="233"/>
       <c r="E12" s="14">
         <v>18837</v>
       </c>
@@ -5694,7 +5658,7 @@
         <v>243</v>
       </c>
       <c r="C13" s="78"/>
-      <c r="D13" s="284"/>
+      <c r="D13" s="231"/>
       <c r="E13" s="14">
         <v>31550</v>
       </c>
@@ -5717,7 +5681,7 @@
       <c r="C14" s="25">
         <v>41296</v>
       </c>
-      <c r="D14" s="286"/>
+      <c r="D14" s="233"/>
       <c r="E14" s="14">
         <v>2132</v>
       </c>
@@ -5739,7 +5703,7 @@
       <c r="C15" s="26">
         <v>73240</v>
       </c>
-      <c r="D15" s="285">
+      <c r="D15" s="232">
         <f>SUM(C14:C15)</f>
         <v>114536</v>
       </c>
@@ -5758,7 +5722,7 @@
       <c r="A16" s="20"/>
       <c r="B16" s="20"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="287"/>
+      <c r="D16" s="234"/>
       <c r="E16" s="14">
         <v>6000</v>
       </c>
@@ -5776,7 +5740,7 @@
         <v>244</v>
       </c>
       <c r="C17" s="78"/>
-      <c r="D17" s="284"/>
+      <c r="D17" s="231"/>
       <c r="E17" s="14">
         <v>40452</v>
       </c>
@@ -5798,7 +5762,7 @@
       <c r="C18" s="25">
         <v>65400</v>
       </c>
-      <c r="D18" s="286"/>
+      <c r="D18" s="233"/>
       <c r="E18" s="14">
         <v>5000</v>
       </c>
@@ -5823,7 +5787,7 @@
       <c r="C19" s="25">
         <v>158834</v>
       </c>
-      <c r="D19" s="286"/>
+      <c r="D19" s="233"/>
       <c r="E19" s="21"/>
       <c r="F19" s="20"/>
       <c r="G19" s="25"/>
@@ -5839,7 +5803,7 @@
       <c r="C20" s="25">
         <v>-152099</v>
       </c>
-      <c r="D20" s="286"/>
+      <c r="D20" s="233"/>
       <c r="E20" s="21"/>
       <c r="F20" s="20"/>
       <c r="G20" s="25"/>
@@ -5855,7 +5819,7 @@
       <c r="C21" s="25">
         <v>7730</v>
       </c>
-      <c r="D21" s="286"/>
+      <c r="D21" s="233"/>
       <c r="E21" s="24"/>
       <c r="F21" s="64" t="s">
         <v>238</v>
@@ -5873,7 +5837,7 @@
       <c r="C22" s="25">
         <v>1150</v>
       </c>
-      <c r="D22" s="286"/>
+      <c r="D22" s="233"/>
       <c r="E22" s="14">
         <v>9048</v>
       </c>
@@ -5895,7 +5859,7 @@
       <c r="C23" s="25">
         <v>7788</v>
       </c>
-      <c r="D23" s="286"/>
+      <c r="D23" s="233"/>
       <c r="E23" s="21"/>
       <c r="F23" s="20"/>
       <c r="G23" s="25"/>
@@ -5911,7 +5875,7 @@
       <c r="C24" s="26">
         <v>6490</v>
       </c>
-      <c r="D24" s="285">
+      <c r="D24" s="232">
         <f>SUM(C18:C24)</f>
         <v>95293</v>
       </c>
@@ -5927,7 +5891,7 @@
       <c r="A25" s="15"/>
       <c r="B25" s="20"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="286"/>
+      <c r="D25" s="233"/>
       <c r="E25" s="24">
         <v>1402</v>
       </c>
@@ -5945,7 +5909,7 @@
         <v>245</v>
       </c>
       <c r="C26" s="78"/>
-      <c r="D26" s="284"/>
+      <c r="D26" s="231"/>
       <c r="E26" s="14">
         <v>17385</v>
       </c>
@@ -5970,7 +5934,7 @@
       <c r="C27" s="25">
         <v>264000</v>
       </c>
-      <c r="D27" s="286"/>
+      <c r="D27" s="233"/>
       <c r="E27" s="14"/>
       <c r="F27" s="20"/>
       <c r="G27" s="72"/>
@@ -5986,7 +5950,7 @@
       <c r="C28" s="25">
         <v>5216</v>
       </c>
-      <c r="D28" s="286"/>
+      <c r="D28" s="233"/>
       <c r="E28" s="14">
         <v>526740</v>
       </c>
@@ -6009,7 +5973,7 @@
         <f>'Sch II Fixed Asset'!G10</f>
         <v>27751</v>
       </c>
-      <c r="D29" s="286"/>
+      <c r="D29" s="233"/>
       <c r="E29" s="21">
         <v>0</v>
       </c>
@@ -6031,7 +5995,7 @@
       <c r="C30" s="25">
         <v>24180</v>
       </c>
-      <c r="D30" s="286"/>
+      <c r="D30" s="233"/>
       <c r="E30" s="14">
         <v>-91625</v>
       </c>
@@ -6054,7 +6018,7 @@
       <c r="C31" s="25">
         <v>826</v>
       </c>
-      <c r="D31" s="286"/>
+      <c r="D31" s="233"/>
       <c r="E31" s="14">
         <v>-83494</v>
       </c>
@@ -6077,7 +6041,7 @@
       <c r="C32" s="26">
         <v>2800</v>
       </c>
-      <c r="D32" s="285">
+      <c r="D32" s="232">
         <f>SUM(C27:C32)</f>
         <v>324773</v>
       </c>
@@ -6097,7 +6061,7 @@
       <c r="A33" s="20"/>
       <c r="B33" s="20"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="286"/>
+      <c r="D33" s="233"/>
       <c r="E33" s="14">
         <v>-204874</v>
       </c>
@@ -6116,7 +6080,7 @@
         <v>246</v>
       </c>
       <c r="C34" s="78"/>
-      <c r="D34" s="284"/>
+      <c r="D34" s="231"/>
       <c r="E34" s="14">
         <v>-76212</v>
       </c>
@@ -6140,7 +6104,7 @@
         <f>42000+9500</f>
         <v>51500</v>
       </c>
-      <c r="D35" s="286"/>
+      <c r="D35" s="233"/>
       <c r="E35" s="21">
         <v>-11780</v>
       </c>
@@ -6166,7 +6130,7 @@
       <c r="C36" s="25">
         <v>19588</v>
       </c>
-      <c r="D36" s="286"/>
+      <c r="D36" s="233"/>
       <c r="E36" s="21"/>
       <c r="F36" s="20"/>
       <c r="G36" s="25"/>
@@ -6182,7 +6146,7 @@
       <c r="C37" s="25">
         <v>1884</v>
       </c>
-      <c r="D37" s="286"/>
+      <c r="D37" s="233"/>
       <c r="E37" s="21">
         <v>3500</v>
       </c>
@@ -6204,7 +6168,7 @@
       <c r="C38" s="25">
         <v>2570</v>
       </c>
-      <c r="D38" s="286"/>
+      <c r="D38" s="233"/>
       <c r="E38" s="21"/>
       <c r="F38" s="20"/>
       <c r="G38" s="25"/>
@@ -6220,7 +6184,7 @@
       <c r="C39" s="25">
         <v>60</v>
       </c>
-      <c r="D39" s="286"/>
+      <c r="D39" s="233"/>
       <c r="E39" s="21"/>
       <c r="F39" s="20"/>
       <c r="G39" s="25"/>
@@ -6236,7 +6200,7 @@
       <c r="C40" s="25">
         <v>8100</v>
       </c>
-      <c r="D40" s="286"/>
+      <c r="D40" s="233"/>
       <c r="E40" s="21"/>
       <c r="F40" s="20"/>
       <c r="G40" s="25"/>
@@ -6252,7 +6216,7 @@
       <c r="C41" s="25">
         <v>200</v>
       </c>
-      <c r="D41" s="286"/>
+      <c r="D41" s="233"/>
       <c r="E41" s="21"/>
       <c r="F41" s="20"/>
       <c r="G41" s="25"/>
@@ -6268,7 +6232,7 @@
       <c r="C42" s="25">
         <v>25670</v>
       </c>
-      <c r="D42" s="286"/>
+      <c r="D42" s="233"/>
       <c r="E42" s="21"/>
       <c r="F42" s="20"/>
       <c r="G42" s="25"/>
@@ -6284,7 +6248,7 @@
       <c r="C43" s="25">
         <v>250</v>
       </c>
-      <c r="D43" s="286"/>
+      <c r="D43" s="233"/>
       <c r="E43" s="21"/>
       <c r="F43" s="20"/>
       <c r="G43" s="25"/>
@@ -6294,7 +6258,7 @@
       <c r="A44" s="20"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="285">
+      <c r="D44" s="232">
         <f>SUM(C35:C43)</f>
         <v>109822</v>
       </c>
@@ -6309,7 +6273,7 @@
         <v>241</v>
       </c>
       <c r="C45" s="79"/>
-      <c r="D45" s="286"/>
+      <c r="D45" s="233"/>
       <c r="E45" s="21"/>
       <c r="F45" s="20"/>
       <c r="G45" s="25"/>
@@ -6323,7 +6287,7 @@
         <v>170</v>
       </c>
       <c r="C46" s="25"/>
-      <c r="D46" s="288">
+      <c r="D46" s="235">
         <f>ROUND((H48-SUM(D8:D44))*0.25,0)</f>
         <v>10419</v>
       </c>
@@ -6340,7 +6304,7 @@
         <v>143</v>
       </c>
       <c r="C47" s="25"/>
-      <c r="D47" s="289">
+      <c r="D47" s="236">
         <f>H48-SUM(D8:D46)</f>
         <v>31255.589999999967</v>
       </c>
@@ -6354,97 +6318,97 @@
         <f>SUM(A7:A47)</f>
         <v>941527</v>
       </c>
-      <c r="B48" s="144" t="s">
+      <c r="B48" s="267" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="144"/>
-      <c r="D48" s="290">
+      <c r="C48" s="267"/>
+      <c r="D48" s="237">
         <f>SUM(D7:D47)</f>
         <v>944886</v>
       </c>
-      <c r="E48" s="282">
+      <c r="E48" s="229">
         <f>SUM(E8:E47)</f>
         <v>941527</v>
       </c>
-      <c r="F48" s="144" t="s">
+      <c r="F48" s="267" t="s">
         <v>28</v>
       </c>
-      <c r="G48" s="144"/>
+      <c r="G48" s="267"/>
       <c r="H48" s="62">
         <f>SUM(H8:H47)</f>
         <v>944886</v>
       </c>
     </row>
     <row r="49" spans="1:12" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="153"/>
+      <c r="A49" s="133"/>
       <c r="B49" s="114"/>
       <c r="C49" s="13"/>
       <c r="D49" s="59"/>
-      <c r="E49" s="154"/>
-      <c r="F49" s="154"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="155"/>
+      <c r="E49" s="258"/>
+      <c r="F49" s="258"/>
+      <c r="G49" s="258"/>
+      <c r="H49" s="134"/>
       <c r="J49" s="39"/>
     </row>
     <row r="50" spans="1:12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="156" t="s">
+      <c r="A50" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="157"/>
-      <c r="C50" s="157"/>
-      <c r="D50" s="158"/>
-      <c r="E50" s="159"/>
-      <c r="F50" s="157"/>
-      <c r="G50" s="159"/>
-      <c r="H50" s="160"/>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="137"/>
+      <c r="E50" s="138"/>
+      <c r="F50" s="136"/>
+      <c r="G50" s="138"/>
+      <c r="H50" s="139"/>
       <c r="I50" s="47"/>
     </row>
     <row r="51" spans="1:12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="161"/>
-      <c r="B51" s="157"/>
-      <c r="C51" s="157"/>
-      <c r="D51" s="162"/>
-      <c r="E51" s="163"/>
-      <c r="F51" s="164" t="s">
+      <c r="A51" s="140"/>
+      <c r="B51" s="136"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="141"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="259" t="s">
         <v>618</v>
       </c>
-      <c r="G51" s="164"/>
-      <c r="H51" s="165"/>
+      <c r="G51" s="259"/>
+      <c r="H51" s="260"/>
       <c r="I51" s="47"/>
     </row>
     <row r="52" spans="1:12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="161"/>
-      <c r="B52" s="157"/>
-      <c r="C52" s="157"/>
-      <c r="D52" s="162"/>
-      <c r="E52" s="163"/>
-      <c r="F52" s="166"/>
-      <c r="G52" s="163"/>
-      <c r="H52" s="167"/>
+      <c r="A52" s="140"/>
+      <c r="B52" s="136"/>
+      <c r="C52" s="136"/>
+      <c r="D52" s="141"/>
+      <c r="E52" s="142"/>
+      <c r="F52" s="144"/>
+      <c r="G52" s="142"/>
+      <c r="H52" s="145"/>
       <c r="I52" s="47"/>
     </row>
     <row r="53" spans="1:12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="161"/>
-      <c r="B53" s="157"/>
-      <c r="C53" s="157"/>
-      <c r="D53" s="162"/>
-      <c r="E53" s="163"/>
-      <c r="F53" s="166"/>
-      <c r="G53" s="163"/>
-      <c r="H53" s="167"/>
+      <c r="A53" s="140"/>
+      <c r="B53" s="136"/>
+      <c r="C53" s="136"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="142"/>
+      <c r="F53" s="144"/>
+      <c r="G53" s="142"/>
+      <c r="H53" s="145"/>
       <c r="I53" s="47"/>
     </row>
     <row r="54" spans="1:12" s="76" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="168" t="s">
+      <c r="A54" s="146" t="s">
         <v>619</v>
       </c>
-      <c r="B54" s="169"/>
-      <c r="C54" s="170"/>
-      <c r="D54" s="162"/>
-      <c r="E54" s="163"/>
-      <c r="F54" s="166"/>
-      <c r="G54" s="163"/>
-      <c r="H54" s="167"/>
+      <c r="B54" s="147"/>
+      <c r="C54" s="148"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="142"/>
+      <c r="F54" s="144"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="145"/>
       <c r="I54" s="113">
         <f>A48-E48</f>
         <v>0</v>
@@ -6456,46 +6420,46 @@
       <c r="K54" s="94"/>
       <c r="L54" s="94"/>
     </row>
-    <row r="55" spans="1:12" s="157" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="171" t="s">
+    <row r="55" spans="1:12" s="136" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="149" t="s">
         <v>620</v>
       </c>
-      <c r="B55" s="169"/>
-      <c r="C55" s="170"/>
-      <c r="D55" s="162"/>
-      <c r="E55" s="163"/>
-      <c r="F55" s="166"/>
-      <c r="G55" s="163"/>
-      <c r="H55" s="167"/>
-      <c r="J55" s="172"/>
-    </row>
-    <row r="56" spans="1:12" s="157" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="171" t="s">
+      <c r="B55" s="147"/>
+      <c r="C55" s="148"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="142"/>
+      <c r="F55" s="144"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="145"/>
+      <c r="J55" s="150"/>
+    </row>
+    <row r="56" spans="1:12" s="136" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="149" t="s">
         <v>621</v>
       </c>
-      <c r="B56" s="169"/>
-      <c r="C56" s="170"/>
-      <c r="D56" s="162"/>
-      <c r="E56" s="163"/>
-      <c r="F56" s="173" t="s">
+      <c r="B56" s="147"/>
+      <c r="C56" s="148"/>
+      <c r="D56" s="141"/>
+      <c r="E56" s="142"/>
+      <c r="F56" s="261" t="s">
         <v>622</v>
       </c>
-      <c r="G56" s="173"/>
-      <c r="H56" s="174"/>
-      <c r="J56" s="172"/>
-    </row>
-    <row r="57" spans="1:12" s="157" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="175">
-        <v>46235</v>
-      </c>
-      <c r="B57" s="176"/>
-      <c r="C57" s="176"/>
-      <c r="D57" s="177"/>
-      <c r="E57" s="178"/>
-      <c r="F57" s="179"/>
-      <c r="G57" s="178"/>
-      <c r="H57" s="180"/>
-      <c r="J57" s="172"/>
+      <c r="G56" s="261"/>
+      <c r="H56" s="262"/>
+      <c r="J56" s="150"/>
+    </row>
+    <row r="57" spans="1:12" s="136" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="240">
+        <v>46242</v>
+      </c>
+      <c r="B57" s="241"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="152"/>
+      <c r="E57" s="153"/>
+      <c r="F57" s="154"/>
+      <c r="G57" s="153"/>
+      <c r="H57" s="155"/>
+      <c r="J57" s="150"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I58" s="21"/>
@@ -6532,4164 +6496,4163 @@
   <dimension ref="A1:W101"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="204" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" style="202" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="202" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="202" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" style="202" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="202" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="202" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.44140625" style="202" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" style="202" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" style="202" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.21875" style="202" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.44140625" style="204" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" style="204" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.44140625" style="202" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="202"/>
-    <col min="17" max="17" width="31.33203125" style="202" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" style="202" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="10.77734375" style="202" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.109375" style="202"/>
+    <col min="1" max="1" width="3.44140625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="136" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="136" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="136" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="136" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.44140625" style="136" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" style="136" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.21875" style="136" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.44140625" style="151" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" style="151" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" style="136" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="136"/>
+    <col min="17" max="17" width="31.33203125" style="136" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.77734375" style="136" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="136"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="272" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="201"/>
+      <c r="B1" s="273"/>
+      <c r="C1" s="273"/>
+      <c r="D1" s="273"/>
+      <c r="E1" s="273"/>
+      <c r="F1" s="273"/>
+      <c r="G1" s="273"/>
+      <c r="H1" s="273"/>
+      <c r="I1" s="273"/>
+      <c r="J1" s="273"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="273"/>
+      <c r="M1" s="273"/>
+      <c r="N1" s="274"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="203"/>
-      <c r="B2" s="291" t="s">
+      <c r="A2" s="163"/>
+      <c r="B2" s="268" t="s">
         <v>366</v>
       </c>
-      <c r="C2" s="291"/>
-      <c r="D2" s="291"/>
-      <c r="E2" s="291"/>
-      <c r="F2" s="291"/>
-      <c r="G2" s="291"/>
-      <c r="H2" s="291"/>
-      <c r="I2" s="291"/>
-      <c r="J2" s="291"/>
-      <c r="K2" s="291"/>
-      <c r="L2" s="291"/>
-      <c r="M2" s="291"/>
-      <c r="N2" s="292"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
     </row>
     <row r="3" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="198" t="s">
+      <c r="A3" s="162" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="198" t="s">
+      <c r="C3" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="198" t="s">
+      <c r="D3" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="198" t="s">
+      <c r="E3" s="162" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="198" t="s">
+      <c r="F3" s="162" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="198" t="s">
+      <c r="G3" s="162" t="s">
         <v>178</v>
       </c>
-      <c r="H3" s="198" t="s">
+      <c r="H3" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="I3" s="198" t="s">
+      <c r="I3" s="162" t="s">
         <v>327</v>
       </c>
-      <c r="J3" s="198" t="s">
+      <c r="J3" s="162" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="198" t="s">
+      <c r="K3" s="162" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="198" t="s">
+      <c r="L3" s="162" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="198" t="s">
+      <c r="N3" s="162" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="164" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="206">
+      <c r="A5" s="165">
         <v>1</v>
       </c>
-      <c r="B5" s="207">
+      <c r="B5" s="166">
         <v>116280</v>
       </c>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="209">
+      <c r="D5" s="167">
         <v>132475</v>
       </c>
-      <c r="E5" s="209">
-        <v>0</v>
-      </c>
-      <c r="F5" s="209">
-        <v>0</v>
-      </c>
-      <c r="G5" s="209">
-        <v>0</v>
-      </c>
-      <c r="H5" s="209">
+      <c r="E5" s="167">
+        <v>0</v>
+      </c>
+      <c r="F5" s="167">
+        <v>0</v>
+      </c>
+      <c r="G5" s="167">
+        <v>0</v>
+      </c>
+      <c r="H5" s="167">
         <f>8371-838</f>
         <v>7533</v>
       </c>
-      <c r="I5" s="209">
+      <c r="I5" s="167">
         <f>10035-1004</f>
         <v>9031</v>
       </c>
-      <c r="J5" s="209">
+      <c r="J5" s="167">
         <f>SUM(D5:I5)</f>
         <v>149039</v>
       </c>
-      <c r="K5" s="209" t="s">
+      <c r="K5" s="167" t="s">
         <v>288</v>
       </c>
-      <c r="L5" s="209">
+      <c r="L5" s="167">
         <v>163135</v>
       </c>
-      <c r="M5" s="210">
+      <c r="M5" s="168">
         <v>7</v>
       </c>
-      <c r="N5" s="210" t="s">
+      <c r="N5" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="206">
+      <c r="A6" s="165">
         <v>2</v>
       </c>
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="166" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="208" t="s">
+      <c r="C6" s="118" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="209">
+      <c r="D6" s="167">
         <v>123554</v>
       </c>
-      <c r="E6" s="209">
-        <v>0</v>
-      </c>
-      <c r="F6" s="209">
-        <v>0</v>
-      </c>
-      <c r="G6" s="209">
+      <c r="E6" s="167">
+        <v>0</v>
+      </c>
+      <c r="F6" s="167">
+        <v>0</v>
+      </c>
+      <c r="G6" s="167">
         <f>2023-203</f>
         <v>1820</v>
       </c>
-      <c r="H6" s="209">
+      <c r="H6" s="167">
         <f>9314-931</f>
         <v>8383</v>
       </c>
-      <c r="I6" s="209">
+      <c r="I6" s="167">
         <f>9937-993</f>
         <v>8944</v>
       </c>
-      <c r="J6" s="209">
+      <c r="J6" s="167">
         <f t="shared" ref="J6:J21" si="0">SUM(D6:I6)</f>
         <v>142701</v>
       </c>
-      <c r="K6" s="209" t="s">
+      <c r="K6" s="167" t="s">
         <v>210</v>
       </c>
-      <c r="L6" s="209">
+      <c r="L6" s="167">
         <v>153275</v>
       </c>
-      <c r="M6" s="210">
+      <c r="M6" s="168">
         <v>7.25</v>
       </c>
-      <c r="N6" s="210" t="s">
+      <c r="N6" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="206">
+      <c r="A7" s="165">
         <v>3</v>
       </c>
-      <c r="B7" s="207" t="s">
+      <c r="B7" s="166" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="208" t="s">
+      <c r="C7" s="118" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="209">
+      <c r="D7" s="167">
         <v>105722</v>
       </c>
-      <c r="E7" s="209">
-        <v>0</v>
-      </c>
-      <c r="F7" s="209">
-        <v>0</v>
-      </c>
-      <c r="G7" s="209">
+      <c r="E7" s="167">
+        <v>0</v>
+      </c>
+      <c r="F7" s="167">
+        <v>0</v>
+      </c>
+      <c r="G7" s="167">
         <f>5375-540</f>
         <v>4835</v>
       </c>
-      <c r="H7" s="209">
+      <c r="H7" s="167">
         <f>7634-763</f>
         <v>6871</v>
       </c>
-      <c r="I7" s="209">
+      <c r="I7" s="167">
         <f>8109-197-202-204-207</f>
         <v>7299</v>
       </c>
-      <c r="J7" s="209">
+      <c r="J7" s="167">
         <f t="shared" si="0"/>
         <v>124727</v>
       </c>
-      <c r="K7" s="209" t="s">
+      <c r="K7" s="167" t="s">
         <v>207</v>
       </c>
-      <c r="L7" s="209">
+      <c r="L7" s="167">
         <v>129234</v>
       </c>
-      <c r="M7" s="210">
+      <c r="M7" s="168">
         <v>6.75</v>
       </c>
-      <c r="N7" s="210" t="s">
+      <c r="N7" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="206">
+      <c r="A8" s="165">
         <v>4</v>
       </c>
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="166" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="208" t="s">
+      <c r="C8" s="118" t="s">
         <v>157</v>
       </c>
-      <c r="D8" s="209">
+      <c r="D8" s="167">
         <v>101079</v>
       </c>
-      <c r="E8" s="209">
-        <v>0</v>
-      </c>
-      <c r="F8" s="209">
-        <v>0</v>
-      </c>
-      <c r="G8" s="209">
-        <v>0</v>
-      </c>
-      <c r="H8" s="209">
+      <c r="E8" s="167">
+        <v>0</v>
+      </c>
+      <c r="F8" s="167">
+        <v>0</v>
+      </c>
+      <c r="G8" s="167">
+        <v>0</v>
+      </c>
+      <c r="H8" s="167">
         <f>6257-626</f>
         <v>5631</v>
       </c>
-      <c r="I8" s="209">
+      <c r="I8" s="167">
         <f>6811-682</f>
         <v>6129</v>
       </c>
-      <c r="J8" s="209">
+      <c r="J8" s="167">
         <f t="shared" si="0"/>
         <v>112839</v>
       </c>
-      <c r="K8" s="209" t="s">
+      <c r="K8" s="167" t="s">
         <v>287</v>
       </c>
-      <c r="L8" s="209">
+      <c r="L8" s="167">
         <v>121748</v>
       </c>
-      <c r="M8" s="210">
+      <c r="M8" s="168">
         <v>6.25</v>
       </c>
-      <c r="N8" s="210" t="s">
+      <c r="N8" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="206">
+      <c r="A9" s="165">
         <v>5</v>
       </c>
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="169" t="s">
         <v>352</v>
       </c>
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="118" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="209">
+      <c r="D9" s="167">
         <v>79595</v>
       </c>
-      <c r="E9" s="209">
-        <v>0</v>
-      </c>
-      <c r="F9" s="209">
-        <v>0</v>
-      </c>
-      <c r="G9" s="209">
-        <v>0</v>
-      </c>
-      <c r="H9" s="209">
-        <v>0</v>
-      </c>
-      <c r="I9" s="209">
+      <c r="E9" s="167">
+        <v>0</v>
+      </c>
+      <c r="F9" s="167">
+        <v>0</v>
+      </c>
+      <c r="G9" s="167">
+        <v>0</v>
+      </c>
+      <c r="H9" s="167">
+        <v>0</v>
+      </c>
+      <c r="I9" s="167">
         <f>5473-1218</f>
         <v>4255</v>
       </c>
-      <c r="J9" s="209">
+      <c r="J9" s="167">
         <f t="shared" si="0"/>
         <v>83850</v>
       </c>
-      <c r="K9" s="212" t="s">
+      <c r="K9" s="170" t="s">
         <v>363</v>
       </c>
-      <c r="L9" s="212"/>
-      <c r="M9" s="213">
+      <c r="L9" s="170"/>
+      <c r="M9" s="171">
         <v>7</v>
       </c>
-      <c r="N9" s="210" t="s">
+      <c r="N9" s="168" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="206">
+      <c r="A10" s="165">
         <v>6</v>
       </c>
-      <c r="B10" s="207" t="s">
+      <c r="B10" s="166" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="208" t="s">
+      <c r="C10" s="118" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="209">
+      <c r="D10" s="167">
         <v>47366</v>
       </c>
-      <c r="E10" s="209">
-        <v>0</v>
-      </c>
-      <c r="F10" s="209">
-        <v>0</v>
-      </c>
-      <c r="G10" s="209">
-        <v>0</v>
-      </c>
-      <c r="H10" s="209">
-        <v>0</v>
-      </c>
-      <c r="I10" s="209">
+      <c r="E10" s="167">
+        <v>0</v>
+      </c>
+      <c r="F10" s="167">
+        <v>0</v>
+      </c>
+      <c r="G10" s="167">
+        <v>0</v>
+      </c>
+      <c r="H10" s="167">
+        <v>0</v>
+      </c>
+      <c r="I10" s="167">
         <f>1245-125</f>
         <v>1120</v>
       </c>
-      <c r="J10" s="209">
+      <c r="J10" s="167">
         <f t="shared" si="0"/>
         <v>48486</v>
       </c>
-      <c r="K10" s="209" t="s">
+      <c r="K10" s="167" t="s">
         <v>344</v>
       </c>
-      <c r="L10" s="209">
+      <c r="L10" s="167">
         <v>53992</v>
       </c>
-      <c r="M10" s="210">
+      <c r="M10" s="168">
         <v>6.6</v>
       </c>
-      <c r="N10" s="210" t="s">
+      <c r="N10" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="206">
+      <c r="A11" s="165">
         <v>7</v>
       </c>
-      <c r="B11" s="214">
+      <c r="B11" s="172">
         <v>220743</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="118" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="209">
+      <c r="D11" s="167">
         <v>10000</v>
       </c>
-      <c r="E11" s="209">
-        <v>0</v>
-      </c>
-      <c r="F11" s="209">
-        <v>0</v>
-      </c>
-      <c r="G11" s="209">
-        <v>0</v>
-      </c>
-      <c r="H11" s="209">
+      <c r="E11" s="167">
+        <v>0</v>
+      </c>
+      <c r="F11" s="167">
+        <v>0</v>
+      </c>
+      <c r="G11" s="167">
+        <v>0</v>
+      </c>
+      <c r="H11" s="167">
         <f>238-24</f>
         <v>214</v>
       </c>
-      <c r="I11" s="209">
+      <c r="I11" s="167">
         <f>732-74</f>
         <v>658</v>
       </c>
-      <c r="J11" s="209">
+      <c r="J11" s="167">
         <f>SUM(D11:I11)</f>
         <v>10872</v>
       </c>
-      <c r="K11" s="206" t="s">
+      <c r="K11" s="165" t="s">
         <v>283</v>
       </c>
-      <c r="L11" s="209">
+      <c r="L11" s="167">
         <v>14148</v>
       </c>
-      <c r="M11" s="210">
+      <c r="M11" s="168">
         <v>7</v>
       </c>
-      <c r="N11" s="210" t="s">
+      <c r="N11" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="206">
+      <c r="A12" s="165">
         <v>8</v>
       </c>
-      <c r="B12" s="211" t="s">
+      <c r="B12" s="169" t="s">
         <v>342</v>
       </c>
-      <c r="C12" s="208" t="s">
+      <c r="C12" s="118" t="s">
         <v>266</v>
       </c>
-      <c r="D12" s="209">
+      <c r="D12" s="167">
         <v>77337</v>
       </c>
-      <c r="E12" s="209">
-        <v>0</v>
-      </c>
-      <c r="F12" s="209">
-        <v>0</v>
-      </c>
-      <c r="G12" s="209">
-        <v>0</v>
-      </c>
-      <c r="H12" s="209">
-        <v>0</v>
-      </c>
-      <c r="I12" s="209">
+      <c r="E12" s="167">
+        <v>0</v>
+      </c>
+      <c r="F12" s="167">
+        <v>0</v>
+      </c>
+      <c r="G12" s="167">
+        <v>0</v>
+      </c>
+      <c r="H12" s="167">
+        <v>0</v>
+      </c>
+      <c r="I12" s="167">
         <f>1314-132</f>
         <v>1182</v>
       </c>
-      <c r="J12" s="209">
+      <c r="J12" s="167">
         <f t="shared" si="0"/>
         <v>78519</v>
       </c>
-      <c r="K12" s="209" t="s">
+      <c r="K12" s="167" t="s">
         <v>345</v>
       </c>
-      <c r="L12" s="209">
+      <c r="L12" s="167">
         <v>82610</v>
       </c>
-      <c r="M12" s="210">
+      <c r="M12" s="168">
         <v>6.65</v>
       </c>
-      <c r="N12" s="210" t="s">
+      <c r="N12" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="206">
+      <c r="A13" s="165">
         <v>9</v>
       </c>
-      <c r="B13" s="211" t="s">
+      <c r="B13" s="169" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="208" t="s">
+      <c r="C13" s="118" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="209">
+      <c r="D13" s="167">
         <v>43658</v>
       </c>
-      <c r="E13" s="209">
-        <v>0</v>
-      </c>
-      <c r="F13" s="209">
-        <v>0</v>
-      </c>
-      <c r="G13" s="209">
-        <v>0</v>
-      </c>
-      <c r="H13" s="209">
+      <c r="E13" s="167">
+        <v>0</v>
+      </c>
+      <c r="F13" s="167">
+        <v>0</v>
+      </c>
+      <c r="G13" s="167">
+        <v>0</v>
+      </c>
+      <c r="H13" s="167">
         <f>362-36</f>
         <v>326</v>
       </c>
-      <c r="I13" s="209">
+      <c r="I13" s="167">
         <f>3150-315</f>
         <v>2835</v>
       </c>
-      <c r="J13" s="209">
+      <c r="J13" s="167">
         <f t="shared" si="0"/>
         <v>46819</v>
       </c>
-      <c r="K13" s="209" t="s">
+      <c r="K13" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="L13" s="209">
+      <c r="L13" s="167">
         <v>53762</v>
       </c>
-      <c r="M13" s="210">
+      <c r="M13" s="168">
         <v>7</v>
       </c>
-      <c r="N13" s="210" t="s">
+      <c r="N13" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="206">
+      <c r="A14" s="165">
         <v>10</v>
       </c>
-      <c r="B14" s="211" t="s">
+      <c r="B14" s="169" t="s">
         <v>347</v>
       </c>
-      <c r="C14" s="208" t="s">
+      <c r="C14" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="D14" s="209">
+      <c r="D14" s="167">
         <v>89832</v>
       </c>
-      <c r="E14" s="209">
-        <v>0</v>
-      </c>
-      <c r="F14" s="209">
-        <v>0</v>
-      </c>
-      <c r="G14" s="209">
-        <v>0</v>
-      </c>
-      <c r="H14" s="209">
-        <v>0</v>
-      </c>
-      <c r="I14" s="209">
+      <c r="E14" s="167">
+        <v>0</v>
+      </c>
+      <c r="F14" s="167">
+        <v>0</v>
+      </c>
+      <c r="G14" s="167">
+        <v>0</v>
+      </c>
+      <c r="H14" s="167">
+        <v>0</v>
+      </c>
+      <c r="I14" s="167">
         <f>840-84</f>
         <v>756</v>
       </c>
-      <c r="J14" s="209">
+      <c r="J14" s="167">
         <f t="shared" si="0"/>
         <v>90588</v>
       </c>
-      <c r="K14" s="209" t="s">
+      <c r="K14" s="167" t="s">
         <v>340</v>
       </c>
-      <c r="L14" s="209">
+      <c r="L14" s="167">
         <v>95956</v>
       </c>
-      <c r="M14" s="210">
+      <c r="M14" s="168">
         <v>6.65</v>
       </c>
-      <c r="N14" s="210" t="s">
+      <c r="N14" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="206">
+      <c r="A15" s="165">
         <v>11</v>
       </c>
-      <c r="B15" s="211" t="s">
+      <c r="B15" s="169" t="s">
         <v>337</v>
       </c>
-      <c r="C15" s="208" t="s">
+      <c r="C15" s="118" t="s">
         <v>269</v>
       </c>
-      <c r="D15" s="209">
+      <c r="D15" s="167">
         <v>26499</v>
       </c>
-      <c r="E15" s="209">
-        <v>0</v>
-      </c>
-      <c r="F15" s="209">
-        <v>0</v>
-      </c>
-      <c r="G15" s="209">
-        <v>0</v>
-      </c>
-      <c r="H15" s="209">
-        <v>0</v>
-      </c>
-      <c r="I15" s="209">
+      <c r="E15" s="167">
+        <v>0</v>
+      </c>
+      <c r="F15" s="167">
+        <v>0</v>
+      </c>
+      <c r="G15" s="167">
+        <v>0</v>
+      </c>
+      <c r="H15" s="167">
+        <v>0</v>
+      </c>
+      <c r="I15" s="167">
         <f>19-2</f>
         <v>17</v>
       </c>
-      <c r="J15" s="209">
+      <c r="J15" s="167">
         <f t="shared" si="0"/>
         <v>26516</v>
       </c>
-      <c r="K15" s="209" t="s">
+      <c r="K15" s="167" t="s">
         <v>338</v>
       </c>
-      <c r="L15" s="209">
+      <c r="L15" s="167">
         <v>28306</v>
       </c>
-      <c r="M15" s="210">
+      <c r="M15" s="168">
         <v>6.65</v>
       </c>
-      <c r="N15" s="210" t="s">
+      <c r="N15" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="206">
+      <c r="A16" s="165">
         <v>12</v>
       </c>
-      <c r="B16" s="207" t="s">
+      <c r="B16" s="166" t="s">
         <v>263</v>
       </c>
-      <c r="C16" s="208" t="s">
+      <c r="C16" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="209">
+      <c r="D16" s="167">
         <v>67120</v>
       </c>
-      <c r="E16" s="209">
-        <v>0</v>
-      </c>
-      <c r="F16" s="209">
-        <v>0</v>
-      </c>
-      <c r="G16" s="209">
+      <c r="E16" s="167">
+        <v>0</v>
+      </c>
+      <c r="F16" s="167">
+        <v>0</v>
+      </c>
+      <c r="G16" s="167">
         <f>1191-119</f>
         <v>1072</v>
       </c>
-      <c r="H16" s="209">
+      <c r="H16" s="167">
         <f>4958-496</f>
         <v>4462</v>
       </c>
-      <c r="I16" s="209">
+      <c r="I16" s="167">
         <f>5282-528</f>
         <v>4754</v>
       </c>
-      <c r="J16" s="209">
+      <c r="J16" s="167">
         <f t="shared" si="0"/>
         <v>77408</v>
       </c>
-      <c r="K16" s="209" t="s">
+      <c r="K16" s="167" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="209">
+      <c r="L16" s="167">
         <v>82898</v>
       </c>
-      <c r="M16" s="210">
+      <c r="M16" s="168">
         <v>7.25</v>
       </c>
-      <c r="N16" s="210" t="s">
+      <c r="N16" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="206">
+      <c r="A17" s="165">
         <v>13</v>
       </c>
-      <c r="B17" s="211" t="s">
+      <c r="B17" s="169" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="208" t="s">
+      <c r="C17" s="118" t="s">
         <v>164</v>
       </c>
-      <c r="D17" s="215">
+      <c r="D17" s="173">
         <v>58224</v>
       </c>
-      <c r="E17" s="209">
-        <v>0</v>
-      </c>
-      <c r="F17" s="209">
+      <c r="E17" s="167">
+        <v>0</v>
+      </c>
+      <c r="F17" s="167">
         <f>1171-117</f>
         <v>1054</v>
       </c>
-      <c r="G17" s="209">
+      <c r="G17" s="167">
         <f>3845-384</f>
         <v>3461</v>
       </c>
-      <c r="H17" s="209">
+      <c r="H17" s="167">
         <f>4070-408</f>
         <v>3662</v>
       </c>
-      <c r="I17" s="209">
+      <c r="I17" s="167">
         <f>4306-430</f>
         <v>3876</v>
       </c>
-      <c r="J17" s="209">
+      <c r="J17" s="167">
         <f t="shared" si="0"/>
         <v>70277</v>
       </c>
-      <c r="K17" s="209" t="s">
+      <c r="K17" s="167" t="s">
         <v>165</v>
       </c>
-      <c r="L17" s="209">
+      <c r="L17" s="167">
         <v>79782</v>
       </c>
-      <c r="M17" s="210">
+      <c r="M17" s="168">
         <v>6.35</v>
       </c>
-      <c r="N17" s="210" t="s">
+      <c r="N17" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="R17" s="216" t="s">
+      <c r="R17" s="143" t="s">
         <v>304</v>
       </c>
-      <c r="S17" s="216" t="s">
+      <c r="S17" s="143" t="s">
         <v>610</v>
       </c>
-      <c r="T17" s="216" t="s">
+      <c r="T17" s="143" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="206">
+      <c r="A18" s="165">
         <v>14</v>
       </c>
-      <c r="B18" s="217" t="s">
+      <c r="B18" s="174" t="s">
         <v>254</v>
       </c>
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="118" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="215">
+      <c r="D18" s="173">
         <v>67192</v>
       </c>
-      <c r="E18" s="209">
-        <v>0</v>
-      </c>
-      <c r="F18" s="209">
-        <v>0</v>
-      </c>
-      <c r="G18" s="209">
-        <v>0</v>
-      </c>
-      <c r="H18" s="209">
+      <c r="E18" s="167">
+        <v>0</v>
+      </c>
+      <c r="F18" s="167">
+        <v>0</v>
+      </c>
+      <c r="G18" s="167">
+        <v>0</v>
+      </c>
+      <c r="H18" s="167">
         <f>584-58</f>
         <v>526</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="167">
         <f>4851-485</f>
         <v>4366</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="167">
         <f t="shared" si="0"/>
         <v>72084</v>
       </c>
-      <c r="K18" s="209" t="s">
+      <c r="K18" s="167" t="s">
         <v>270</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="167">
         <v>82743</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="168">
         <v>7</v>
       </c>
-      <c r="N18" s="210" t="s">
+      <c r="N18" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="Q18" s="202" t="s">
+      <c r="Q18" s="136" t="s">
         <v>609</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="175">
         <f>BS!D11</f>
         <v>14000</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="175">
         <f>J97</f>
         <v>14000</v>
       </c>
-      <c r="T18" s="218">
+      <c r="T18" s="175">
         <f>R18-S18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="206">
+      <c r="A19" s="165">
         <v>15</v>
       </c>
-      <c r="B19" s="219" t="s">
+      <c r="B19" s="176" t="s">
         <v>348</v>
       </c>
-      <c r="C19" s="208" t="s">
+      <c r="C19" s="118" t="s">
         <v>183</v>
       </c>
-      <c r="D19" s="209">
+      <c r="D19" s="167">
         <v>66916</v>
       </c>
-      <c r="E19" s="215">
-        <v>0</v>
-      </c>
-      <c r="F19" s="215">
-        <v>0</v>
-      </c>
-      <c r="G19" s="215">
-        <v>0</v>
-      </c>
-      <c r="H19" s="215">
-        <v>0</v>
-      </c>
-      <c r="I19" s="215">
+      <c r="E19" s="173">
+        <v>0</v>
+      </c>
+      <c r="F19" s="173">
+        <v>0</v>
+      </c>
+      <c r="G19" s="173">
+        <v>0</v>
+      </c>
+      <c r="H19" s="173">
+        <v>0</v>
+      </c>
+      <c r="I19" s="173">
         <f>1489-149</f>
         <v>1340</v>
       </c>
-      <c r="J19" s="209">
+      <c r="J19" s="167">
         <f t="shared" si="0"/>
         <v>68256</v>
       </c>
-      <c r="K19" s="209" t="s">
+      <c r="K19" s="167" t="s">
         <v>349</v>
       </c>
-      <c r="L19" s="209">
+      <c r="L19" s="167">
         <v>76276</v>
       </c>
-      <c r="M19" s="210">
+      <c r="M19" s="168">
         <v>6.6</v>
       </c>
-      <c r="N19" s="210" t="s">
+      <c r="N19" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="Q19" s="202" t="str">
+      <c r="Q19" s="136" t="str">
         <f>BS!B13</f>
         <v>Reserve and Surplus Fund</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="175">
         <f>BS!D17</f>
         <v>840072</v>
       </c>
-      <c r="S19" s="218">
+      <c r="S19" s="175">
         <f>J47</f>
         <v>1414865</v>
       </c>
-      <c r="T19" s="218">
+      <c r="T19" s="175">
         <f>R19-S19</f>
         <v>-574793</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="206">
+      <c r="A20" s="165">
         <v>16</v>
       </c>
-      <c r="B20" s="219">
+      <c r="B20" s="176">
         <v>6605400015598</v>
       </c>
-      <c r="C20" s="208" t="s">
+      <c r="C20" s="118" t="s">
         <v>264</v>
       </c>
-      <c r="D20" s="209">
+      <c r="D20" s="167">
         <v>58224</v>
       </c>
-      <c r="E20" s="209">
-        <v>0</v>
-      </c>
-      <c r="F20" s="209">
-        <v>0</v>
-      </c>
-      <c r="G20" s="209">
-        <v>0</v>
-      </c>
-      <c r="H20" s="209">
+      <c r="E20" s="167">
+        <v>0</v>
+      </c>
+      <c r="F20" s="167">
+        <v>0</v>
+      </c>
+      <c r="G20" s="167">
+        <v>0</v>
+      </c>
+      <c r="H20" s="167">
         <f>2287-229</f>
         <v>2058</v>
       </c>
-      <c r="I20" s="209">
+      <c r="I20" s="167">
         <f>4794-480</f>
         <v>4314</v>
       </c>
-      <c r="J20" s="209">
+      <c r="J20" s="167">
         <f t="shared" si="0"/>
         <v>64596</v>
       </c>
-      <c r="K20" s="209" t="s">
+      <c r="K20" s="167" t="s">
         <v>265</v>
       </c>
-      <c r="L20" s="209">
+      <c r="L20" s="167">
         <v>67885</v>
       </c>
-      <c r="M20" s="210">
+      <c r="M20" s="168">
         <v>7.75</v>
       </c>
-      <c r="N20" s="210" t="s">
+      <c r="N20" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="Q20" s="202" t="str">
+      <c r="Q20" s="136" t="str">
         <f>BS!B19</f>
         <v>Grotto Fund</v>
       </c>
-      <c r="R20" s="218">
+      <c r="R20" s="175">
         <f>BS!D23</f>
         <v>104285</v>
       </c>
-      <c r="S20" s="218">
+      <c r="S20" s="175">
         <f>J78</f>
         <v>122767</v>
       </c>
-      <c r="T20" s="218">
+      <c r="T20" s="175">
         <f t="shared" ref="T20:T25" si="1">R20-S20</f>
         <v>-18482</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="206">
+      <c r="A21" s="165">
         <v>17</v>
       </c>
-      <c r="B21" s="219">
+      <c r="B21" s="176">
         <v>281691</v>
       </c>
-      <c r="C21" s="208" t="s">
+      <c r="C21" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="D21" s="209">
+      <c r="D21" s="167">
         <v>17030</v>
       </c>
-      <c r="E21" s="209">
-        <v>0</v>
-      </c>
-      <c r="F21" s="209">
-        <v>0</v>
-      </c>
-      <c r="G21" s="209">
-        <v>0</v>
-      </c>
-      <c r="H21" s="209">
+      <c r="E21" s="167">
+        <v>0</v>
+      </c>
+      <c r="F21" s="167">
+        <v>0</v>
+      </c>
+      <c r="G21" s="167">
+        <v>0</v>
+      </c>
+      <c r="H21" s="167">
         <f>48-4</f>
         <v>44</v>
       </c>
-      <c r="I21" s="209">
+      <c r="I21" s="167">
         <f>1224-124</f>
         <v>1100</v>
       </c>
-      <c r="J21" s="209">
+      <c r="J21" s="167">
         <f t="shared" si="0"/>
         <v>18174</v>
       </c>
-      <c r="K21" s="209" t="s">
+      <c r="K21" s="167" t="s">
         <v>281</v>
       </c>
-      <c r="L21" s="209">
+      <c r="L21" s="167">
         <v>24094</v>
       </c>
-      <c r="M21" s="210">
+      <c r="M21" s="168">
         <v>7</v>
       </c>
-      <c r="N21" s="210" t="s">
+      <c r="N21" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="Q21" s="202" t="str">
+      <c r="Q21" s="136" t="str">
         <f>BS!B25</f>
         <v>Contingency Fund</v>
       </c>
-      <c r="R21" s="218">
+      <c r="R21" s="175">
         <f>BS!D28</f>
         <v>1750419</v>
       </c>
-      <c r="S21" s="218">
+      <c r="S21" s="175">
         <f>J68</f>
         <v>1814135</v>
       </c>
-      <c r="T21" s="218">
+      <c r="T21" s="175">
         <f t="shared" si="1"/>
         <v>-63716</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="206">
+      <c r="A22" s="165">
         <v>18</v>
       </c>
-      <c r="B22" s="214">
+      <c r="B22" s="172">
         <v>6605400016067</v>
       </c>
-      <c r="C22" s="220" t="s">
+      <c r="C22" s="177" t="s">
         <v>350</v>
       </c>
-      <c r="D22" s="221">
+      <c r="D22" s="178">
         <v>65324</v>
       </c>
-      <c r="E22" s="221">
-        <v>0</v>
-      </c>
-      <c r="F22" s="221">
-        <v>0</v>
-      </c>
-      <c r="G22" s="221">
-        <v>0</v>
-      </c>
-      <c r="H22" s="221">
-        <v>0</v>
-      </c>
-      <c r="I22" s="221">
+      <c r="E22" s="178">
+        <v>0</v>
+      </c>
+      <c r="F22" s="178">
+        <v>0</v>
+      </c>
+      <c r="G22" s="178">
+        <v>0</v>
+      </c>
+      <c r="H22" s="178">
+        <v>0</v>
+      </c>
+      <c r="I22" s="178">
         <f>499-50</f>
         <v>449</v>
       </c>
-      <c r="J22" s="209">
+      <c r="J22" s="167">
         <f>SUM(D22:I22)</f>
         <v>65773</v>
       </c>
-      <c r="K22" s="222" t="s">
+      <c r="K22" s="179" t="s">
         <v>336</v>
       </c>
-      <c r="L22" s="221">
+      <c r="L22" s="178">
         <v>79852</v>
       </c>
-      <c r="M22" s="210">
+      <c r="M22" s="168">
         <v>6.75</v>
       </c>
-      <c r="N22" s="210" t="s">
+      <c r="N22" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="Q22" s="202" t="str">
+      <c r="Q22" s="136" t="str">
         <f>BS!B30</f>
         <v>Sinking Fund</v>
       </c>
-      <c r="R22" s="218">
+      <c r="R22" s="175">
         <f>BS!D33</f>
         <v>1349534</v>
       </c>
-      <c r="S22" s="218">
+      <c r="S22" s="175">
         <f>J23</f>
         <v>1351524</v>
       </c>
-      <c r="T22" s="218">
+      <c r="T22" s="175">
         <f t="shared" si="1"/>
         <v>-1990</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="223"/>
-      <c r="B23" s="224"/>
-      <c r="C23" s="225"/>
-      <c r="D23" s="226">
+      <c r="A23" s="180"/>
+      <c r="B23" s="181"/>
+      <c r="C23" s="182"/>
+      <c r="D23" s="183">
         <f>SUM(D5:D22)</f>
         <v>1237147</v>
       </c>
-      <c r="E23" s="226">
+      <c r="E23" s="183">
         <f t="shared" ref="E23:J23" si="2">SUM(E5:E22)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="226">
+      <c r="F23" s="183">
         <f t="shared" si="2"/>
         <v>1054</v>
       </c>
-      <c r="G23" s="226">
+      <c r="G23" s="183">
         <f t="shared" si="2"/>
         <v>11188</v>
       </c>
-      <c r="H23" s="226">
+      <c r="H23" s="183">
         <f t="shared" si="2"/>
         <v>39710</v>
       </c>
-      <c r="I23" s="226">
+      <c r="I23" s="183">
         <f t="shared" si="2"/>
         <v>62425</v>
       </c>
-      <c r="J23" s="226">
+      <c r="J23" s="183">
         <f t="shared" si="2"/>
         <v>1351524</v>
       </c>
-      <c r="K23" s="227"/>
-      <c r="L23" s="226">
+      <c r="K23" s="184"/>
+      <c r="L23" s="183">
         <f>SUM(L5:L22)</f>
         <v>1389696</v>
       </c>
-      <c r="M23" s="223"/>
-      <c r="N23" s="228"/>
-      <c r="Q23" s="229" t="str">
+      <c r="M23" s="180"/>
+      <c r="N23" s="185"/>
+      <c r="Q23" s="150" t="str">
         <f>BS!B35</f>
         <v>Repair Fund</v>
       </c>
-      <c r="R23" s="218">
+      <c r="R23" s="175">
         <f>BS!D39</f>
         <v>3714032</v>
       </c>
-      <c r="S23" s="218">
+      <c r="S23" s="175">
         <f>J38</f>
         <v>3798231</v>
       </c>
-      <c r="T23" s="218">
+      <c r="T23" s="175">
         <f t="shared" si="1"/>
         <v>-84199</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="230"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="158"/>
-      <c r="I24" s="158"/>
-      <c r="J24" s="158"/>
-      <c r="K24" s="231"/>
-      <c r="L24" s="231"/>
-      <c r="N24" s="232"/>
-      <c r="Q24" s="202" t="str">
+      <c r="B24" s="144"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="137"/>
+      <c r="K24" s="186"/>
+      <c r="L24" s="186"/>
+      <c r="N24" s="187"/>
+      <c r="Q24" s="136" t="str">
         <f>BS!B41</f>
         <v>Building Painting Fund</v>
       </c>
-      <c r="R24" s="218">
+      <c r="R24" s="175">
         <f>BS!D43</f>
         <v>823757</v>
       </c>
-      <c r="S24" s="218">
+      <c r="S24" s="175">
         <f>J93</f>
         <v>828409</v>
       </c>
-      <c r="T24" s="218">
+      <c r="T24" s="175">
         <f>R24-S24</f>
         <v>-4652</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B25" s="205" t="s">
+      <c r="B25" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="158"/>
-      <c r="H25" s="158"/>
-      <c r="I25" s="158"/>
-      <c r="J25" s="158"/>
-      <c r="K25" s="231"/>
-      <c r="L25" s="231"/>
-      <c r="N25" s="232"/>
-      <c r="Q25" s="202" t="str">
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137"/>
+      <c r="K25" s="186"/>
+      <c r="L25" s="186"/>
+      <c r="N25" s="187"/>
+      <c r="Q25" s="136" t="str">
         <f>BS!B50</f>
         <v>Refundable Deposit - ( As per Sch IV )</v>
       </c>
-      <c r="R25" s="218">
+      <c r="R25" s="175">
         <f>BS!D54</f>
         <v>80000</v>
       </c>
-      <c r="S25" s="218">
+      <c r="S25" s="175">
         <f>J85</f>
         <v>128730</v>
       </c>
-      <c r="T25" s="218">
+      <c r="T25" s="175">
         <f t="shared" si="1"/>
         <v>-48730</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="206">
+      <c r="A26" s="165">
         <v>19</v>
       </c>
-      <c r="B26" s="207">
+      <c r="B26" s="166">
         <v>116286</v>
       </c>
-      <c r="C26" s="208" t="s">
+      <c r="C26" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="233">
+      <c r="D26" s="188">
         <v>397435</v>
       </c>
-      <c r="E26" s="209">
-        <v>0</v>
-      </c>
-      <c r="F26" s="209">
-        <v>0</v>
-      </c>
-      <c r="G26" s="209">
-        <v>0</v>
-      </c>
-      <c r="H26" s="209">
+      <c r="E26" s="167">
+        <v>0</v>
+      </c>
+      <c r="F26" s="167">
+        <v>0</v>
+      </c>
+      <c r="G26" s="167">
+        <v>0</v>
+      </c>
+      <c r="H26" s="167">
         <f>25114-2510</f>
         <v>22604</v>
       </c>
-      <c r="I26" s="209">
+      <c r="I26" s="167">
         <f>30105-3012</f>
         <v>27093</v>
       </c>
-      <c r="J26" s="209">
+      <c r="J26" s="167">
         <f>SUM(D26:I26)</f>
         <v>447132</v>
       </c>
-      <c r="K26" s="209" t="s">
+      <c r="K26" s="167" t="s">
         <v>288</v>
       </c>
-      <c r="L26" s="209">
+      <c r="L26" s="167">
         <v>498417</v>
       </c>
-      <c r="M26" s="210">
+      <c r="M26" s="168">
         <v>7</v>
       </c>
-      <c r="N26" s="210" t="s">
+      <c r="N26" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="R26" s="218"/>
-      <c r="S26" s="218"/>
-      <c r="T26" s="218"/>
+      <c r="R26" s="175"/>
+      <c r="S26" s="175"/>
+      <c r="T26" s="175"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="206">
+      <c r="A27" s="165">
         <v>20</v>
       </c>
-      <c r="B27" s="207" t="s">
+      <c r="B27" s="166" t="s">
         <v>187</v>
       </c>
-      <c r="C27" s="208" t="s">
+      <c r="C27" s="118" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="233">
+      <c r="D27" s="188">
         <v>317235</v>
       </c>
-      <c r="E27" s="209">
-        <v>0</v>
-      </c>
-      <c r="F27" s="209">
-        <v>0</v>
-      </c>
-      <c r="G27" s="209">
+      <c r="E27" s="167">
+        <v>0</v>
+      </c>
+      <c r="F27" s="167">
+        <v>0</v>
+      </c>
+      <c r="G27" s="167">
         <f>16127-1611</f>
         <v>14516</v>
       </c>
-      <c r="H27" s="209">
+      <c r="H27" s="167">
         <f>22909-2291</f>
         <v>20618</v>
       </c>
-      <c r="I27" s="209">
+      <c r="I27" s="167">
         <f>24332-2434</f>
         <v>21898</v>
       </c>
-      <c r="J27" s="209">
+      <c r="J27" s="167">
         <f t="shared" ref="J27:J37" si="3">SUM(D27:I27)</f>
         <v>374267</v>
       </c>
-      <c r="K27" s="209" t="s">
+      <c r="K27" s="167" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="209">
+      <c r="L27" s="167">
         <v>387786</v>
       </c>
-      <c r="M27" s="210">
+      <c r="M27" s="168">
         <v>6.75</v>
       </c>
-      <c r="N27" s="210" t="s">
+      <c r="N27" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="R27" s="234">
+      <c r="R27" s="189">
         <f>SUM(R18:R26)</f>
         <v>8676099</v>
       </c>
-      <c r="S27" s="234">
+      <c r="S27" s="189">
         <f>SUM(S18:S26)</f>
         <v>9472661</v>
       </c>
-      <c r="T27" s="234">
+      <c r="T27" s="189">
         <f>SUM(T18:T26)</f>
         <v>-796562</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="206">
+      <c r="A28" s="165">
         <v>21</v>
       </c>
-      <c r="B28" s="207" t="s">
+      <c r="B28" s="166" t="s">
         <v>334</v>
       </c>
-      <c r="C28" s="208" t="s">
+      <c r="C28" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="233">
+      <c r="D28" s="188">
         <v>486439</v>
       </c>
-      <c r="E28" s="209">
-        <v>0</v>
-      </c>
-      <c r="F28" s="209">
-        <v>0</v>
-      </c>
-      <c r="G28" s="209">
-        <v>0</v>
-      </c>
-      <c r="H28" s="209">
-        <v>0</v>
-      </c>
-      <c r="I28" s="209">
+      <c r="E28" s="167">
+        <v>0</v>
+      </c>
+      <c r="F28" s="167">
+        <v>0</v>
+      </c>
+      <c r="G28" s="167">
+        <v>0</v>
+      </c>
+      <c r="H28" s="167">
+        <v>0</v>
+      </c>
+      <c r="I28" s="167">
         <f>7283+8627+8804+1+8902-728-863-880-890</f>
         <v>30256</v>
       </c>
-      <c r="J28" s="209">
+      <c r="J28" s="167">
         <f t="shared" si="3"/>
         <v>516695</v>
       </c>
-      <c r="K28" s="209" t="s">
+      <c r="K28" s="167" t="s">
         <v>289</v>
       </c>
-      <c r="L28" s="209">
+      <c r="L28" s="167">
         <v>562121</v>
       </c>
-      <c r="M28" s="210">
+      <c r="M28" s="168">
         <v>7</v>
       </c>
-      <c r="N28" s="210" t="s">
+      <c r="N28" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="206">
+      <c r="A29" s="165">
         <v>22</v>
       </c>
-      <c r="B29" s="207" t="s">
+      <c r="B29" s="166" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="208" t="s">
+      <c r="C29" s="118" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="233">
+      <c r="D29" s="188">
         <v>376597</v>
       </c>
-      <c r="E29" s="209">
-        <v>0</v>
-      </c>
-      <c r="F29" s="209">
-        <v>0</v>
-      </c>
-      <c r="G29" s="209">
-        <v>0</v>
-      </c>
-      <c r="H29" s="209">
+      <c r="E29" s="167">
+        <v>0</v>
+      </c>
+      <c r="F29" s="167">
+        <v>0</v>
+      </c>
+      <c r="G29" s="167">
+        <v>0</v>
+      </c>
+      <c r="H29" s="167">
         <f>3756-375</f>
         <v>3381</v>
       </c>
-      <c r="I29" s="209">
+      <c r="I29" s="167">
         <f>27234-2723</f>
         <v>24511</v>
       </c>
-      <c r="J29" s="209">
+      <c r="J29" s="167">
         <f t="shared" si="3"/>
         <v>404489</v>
       </c>
-      <c r="K29" s="209" t="s">
+      <c r="K29" s="167" t="s">
         <v>284</v>
       </c>
-      <c r="L29" s="209">
+      <c r="L29" s="167">
         <v>463756</v>
       </c>
-      <c r="M29" s="210">
+      <c r="M29" s="168">
         <v>7</v>
       </c>
-      <c r="N29" s="210" t="s">
+      <c r="N29" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="R29" s="202" t="s">
+      <c r="R29" s="136" t="s">
         <v>612</v>
       </c>
-      <c r="S29" s="202" t="s">
+      <c r="S29" s="136" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A30" s="206">
+      <c r="A30" s="165">
         <v>23</v>
       </c>
-      <c r="B30" s="207">
+      <c r="B30" s="166">
         <v>42907</v>
       </c>
-      <c r="C30" s="208" t="s">
+      <c r="C30" s="118" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="233">
+      <c r="D30" s="188">
         <v>175056</v>
       </c>
-      <c r="E30" s="209">
+      <c r="E30" s="167">
         <f>1185-119</f>
         <v>1066</v>
       </c>
-      <c r="F30" s="209">
+      <c r="F30" s="167">
         <f>10326-1034</f>
         <v>9292</v>
       </c>
-      <c r="G30" s="209">
+      <c r="G30" s="167">
         <f>10935-1094</f>
         <v>9841</v>
       </c>
-      <c r="H30" s="209">
+      <c r="H30" s="167">
         <f>11447-1143</f>
         <v>10304</v>
       </c>
-      <c r="I30" s="209">
+      <c r="I30" s="167">
         <f>12051-1205</f>
         <v>10846</v>
       </c>
-      <c r="J30" s="209">
+      <c r="J30" s="167">
         <f t="shared" si="3"/>
         <v>216405</v>
       </c>
-      <c r="K30" s="209" t="s">
+      <c r="K30" s="167" t="s">
         <v>150</v>
       </c>
-      <c r="L30" s="209">
+      <c r="L30" s="167">
         <v>232888</v>
       </c>
-      <c r="M30" s="210">
+      <c r="M30" s="168">
         <v>5.75</v>
       </c>
-      <c r="N30" s="210" t="s">
+      <c r="N30" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="R30" s="202" t="s">
+      <c r="R30" s="136" t="s">
         <v>94</v>
       </c>
-      <c r="S30" s="202" t="s">
+      <c r="S30" s="136" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="206">
+      <c r="A31" s="165">
         <v>24</v>
       </c>
-      <c r="B31" s="207">
+      <c r="B31" s="166">
         <v>43583</v>
       </c>
-      <c r="C31" s="208" t="s">
+      <c r="C31" s="118" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="233">
+      <c r="D31" s="188">
         <v>175056</v>
       </c>
-      <c r="E31" s="209">
-        <v>0</v>
-      </c>
-      <c r="F31" s="209">
+      <c r="E31" s="167">
+        <v>0</v>
+      </c>
+      <c r="F31" s="167">
         <f>3767-378</f>
         <v>3389</v>
       </c>
-      <c r="G31" s="209">
+      <c r="G31" s="167">
         <f>12349-1235</f>
         <v>11114</v>
       </c>
-      <c r="H31" s="209">
+      <c r="H31" s="167">
         <f>13090-1311</f>
         <v>11779</v>
       </c>
-      <c r="I31" s="209">
+      <c r="I31" s="167">
         <f>13903-1390</f>
         <v>12513</v>
       </c>
-      <c r="J31" s="209">
+      <c r="J31" s="167">
         <f t="shared" si="3"/>
         <v>213851</v>
       </c>
-      <c r="K31" s="209" t="s">
+      <c r="K31" s="167" t="s">
         <v>166</v>
       </c>
-      <c r="L31" s="209">
+      <c r="L31" s="167">
         <v>244641</v>
       </c>
-      <c r="M31" s="210">
+      <c r="M31" s="168">
         <v>6.75</v>
       </c>
-      <c r="N31" s="210" t="s">
+      <c r="N31" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="R31" s="202" t="s">
+      <c r="R31" s="136" t="s">
         <v>94</v>
       </c>
-      <c r="S31" s="202" t="s">
+      <c r="S31" s="136" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" s="206">
+      <c r="A32" s="165">
         <v>25</v>
       </c>
-      <c r="B32" s="207" t="s">
+      <c r="B32" s="166" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="235" t="s">
+      <c r="C32" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="236">
+      <c r="D32" s="190">
         <v>262486</v>
       </c>
-      <c r="E32" s="212">
-        <v>0</v>
-      </c>
-      <c r="F32" s="212">
-        <v>0</v>
-      </c>
-      <c r="G32" s="212">
-        <v>0</v>
-      </c>
-      <c r="H32" s="212">
+      <c r="E32" s="170">
+        <v>0</v>
+      </c>
+      <c r="F32" s="170">
+        <v>0</v>
+      </c>
+      <c r="G32" s="170">
+        <v>0</v>
+      </c>
+      <c r="H32" s="170">
         <f>2185-219</f>
         <v>1966</v>
       </c>
-      <c r="I32" s="212">
+      <c r="I32" s="170">
         <f>18951-1895</f>
         <v>17056</v>
       </c>
-      <c r="J32" s="209">
+      <c r="J32" s="167">
         <f t="shared" si="3"/>
         <v>281508</v>
       </c>
-      <c r="K32" s="209" t="s">
+      <c r="K32" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="L32" s="209">
+      <c r="L32" s="167">
         <v>323236</v>
       </c>
-      <c r="M32" s="210">
+      <c r="M32" s="168">
         <v>7</v>
       </c>
-      <c r="N32" s="213" t="s">
+      <c r="N32" s="171" t="s">
         <v>56</v>
       </c>
-      <c r="R32" s="202" t="s">
+      <c r="R32" s="136" t="s">
         <v>323</v>
       </c>
-      <c r="S32" s="202" t="s">
+      <c r="S32" s="136" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="206">
+      <c r="A33" s="165">
         <v>26</v>
       </c>
-      <c r="B33" s="207" t="s">
+      <c r="B33" s="166" t="s">
         <v>329</v>
       </c>
-      <c r="C33" s="208" t="s">
+      <c r="C33" s="118" t="s">
         <v>213</v>
       </c>
-      <c r="D33" s="233">
+      <c r="D33" s="188">
         <v>282129</v>
       </c>
-      <c r="E33" s="209">
-        <v>0</v>
-      </c>
-      <c r="F33" s="209">
-        <v>0</v>
-      </c>
-      <c r="G33" s="209">
-        <v>0</v>
-      </c>
-      <c r="H33" s="209">
-        <v>0</v>
-      </c>
-      <c r="I33" s="209">
+      <c r="E33" s="167">
+        <v>0</v>
+      </c>
+      <c r="F33" s="167">
+        <v>0</v>
+      </c>
+      <c r="G33" s="167">
+        <v>0</v>
+      </c>
+      <c r="H33" s="167">
+        <v>0</v>
+      </c>
+      <c r="I33" s="167">
         <f>6629-663</f>
         <v>5966</v>
       </c>
-      <c r="J33" s="209">
+      <c r="J33" s="167">
         <f t="shared" si="3"/>
         <v>288095</v>
       </c>
-      <c r="K33" s="209" t="s">
+      <c r="K33" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="L33" s="209">
+      <c r="L33" s="167">
         <v>322836</v>
       </c>
-      <c r="M33" s="210">
+      <c r="M33" s="168">
         <v>6.8</v>
       </c>
-      <c r="N33" s="210" t="s">
+      <c r="N33" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="206">
+      <c r="A34" s="165">
         <v>27</v>
       </c>
-      <c r="B34" s="207" t="s">
+      <c r="B34" s="166" t="s">
         <v>333</v>
       </c>
-      <c r="C34" s="208" t="s">
+      <c r="C34" s="118" t="s">
         <v>360</v>
       </c>
-      <c r="D34" s="233">
+      <c r="D34" s="188">
         <v>463557</v>
       </c>
-      <c r="E34" s="209">
-        <v>0</v>
-      </c>
-      <c r="F34" s="209">
-        <v>0</v>
-      </c>
-      <c r="G34" s="209">
-        <v>0</v>
-      </c>
-      <c r="H34" s="209">
-        <v>0</v>
-      </c>
-      <c r="I34" s="209">
+      <c r="E34" s="167">
+        <v>0</v>
+      </c>
+      <c r="F34" s="167">
+        <v>0</v>
+      </c>
+      <c r="G34" s="167">
+        <v>0</v>
+      </c>
+      <c r="H34" s="167">
+        <v>0</v>
+      </c>
+      <c r="I34" s="167">
         <f>7118-712</f>
         <v>6406</v>
       </c>
-      <c r="J34" s="209">
+      <c r="J34" s="167">
         <f t="shared" si="3"/>
         <v>469963</v>
       </c>
-      <c r="K34" s="209" t="s">
+      <c r="K34" s="167" t="s">
         <v>361</v>
       </c>
-      <c r="L34" s="209">
+      <c r="L34" s="167">
         <v>530482</v>
       </c>
-      <c r="M34" s="210">
+      <c r="M34" s="168">
         <v>6.8</v>
       </c>
-      <c r="N34" s="210" t="s">
+      <c r="N34" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="206">
+      <c r="A35" s="165">
         <v>28</v>
       </c>
-      <c r="B35" s="217">
+      <c r="B35" s="174">
         <v>21086</v>
       </c>
-      <c r="C35" s="208" t="s">
+      <c r="C35" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="D35" s="233">
+      <c r="D35" s="188">
         <v>175056</v>
       </c>
-      <c r="E35" s="209">
-        <v>0</v>
-      </c>
-      <c r="F35" s="209">
-        <v>0</v>
-      </c>
-      <c r="G35" s="209">
+      <c r="E35" s="167">
+        <v>0</v>
+      </c>
+      <c r="F35" s="167">
+        <v>0</v>
+      </c>
+      <c r="G35" s="167">
         <f>5908-591</f>
         <v>5317</v>
       </c>
-      <c r="H35" s="209">
+      <c r="H35" s="167">
         <f>12927-663</f>
         <v>12264</v>
       </c>
-      <c r="I35" s="209">
+      <c r="I35" s="167">
         <f>13761-1377</f>
         <v>12384</v>
       </c>
-      <c r="J35" s="209">
+      <c r="J35" s="167">
         <f t="shared" si="3"/>
         <v>205021</v>
       </c>
-      <c r="K35" s="209" t="s">
+      <c r="K35" s="167" t="s">
         <v>211</v>
       </c>
-      <c r="L35" s="209">
+      <c r="L35" s="167">
         <v>215571</v>
       </c>
-      <c r="M35" s="210">
+      <c r="M35" s="168">
         <v>7</v>
       </c>
-      <c r="N35" s="210" t="s">
+      <c r="N35" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="206">
+      <c r="A36" s="165">
         <v>29</v>
       </c>
-      <c r="B36" s="217">
+      <c r="B36" s="174">
         <v>281673</v>
       </c>
-      <c r="C36" s="208" t="s">
+      <c r="C36" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="D36" s="233">
+      <c r="D36" s="188">
         <v>122568</v>
       </c>
-      <c r="E36" s="209">
-        <v>0</v>
-      </c>
-      <c r="F36" s="209">
-        <v>0</v>
-      </c>
-      <c r="G36" s="209">
-        <v>0</v>
-      </c>
-      <c r="H36" s="209">
+      <c r="E36" s="167">
+        <v>0</v>
+      </c>
+      <c r="F36" s="167">
+        <v>0</v>
+      </c>
+      <c r="G36" s="167">
+        <v>0</v>
+      </c>
+      <c r="H36" s="167">
         <f>346-34</f>
         <v>312</v>
       </c>
-      <c r="I36" s="209">
+      <c r="I36" s="167">
         <f>8807-882</f>
         <v>7925</v>
       </c>
-      <c r="J36" s="209">
+      <c r="J36" s="167">
         <f t="shared" si="3"/>
         <v>130805</v>
       </c>
-      <c r="K36" s="209" t="s">
+      <c r="K36" s="167" t="s">
         <v>281</v>
       </c>
-      <c r="L36" s="209">
+      <c r="L36" s="167">
         <v>173407</v>
       </c>
-      <c r="M36" s="210">
+      <c r="M36" s="168">
         <v>7</v>
       </c>
-      <c r="N36" s="210" t="s">
+      <c r="N36" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="206">
+      <c r="A37" s="165">
         <v>30</v>
       </c>
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="191" t="s">
         <v>355</v>
       </c>
-      <c r="C37" s="220" t="s">
+      <c r="C37" s="177" t="s">
         <v>335</v>
       </c>
-      <c r="D37" s="238">
+      <c r="D37" s="192">
         <v>250000</v>
       </c>
-      <c r="E37" s="221">
-        <v>0</v>
-      </c>
-      <c r="F37" s="221">
-        <v>0</v>
-      </c>
-      <c r="G37" s="221">
-        <v>0</v>
-      </c>
-      <c r="H37" s="221">
-        <v>0</v>
-      </c>
-      <c r="I37" s="221">
-        <v>0</v>
-      </c>
-      <c r="J37" s="209">
+      <c r="E37" s="178">
+        <v>0</v>
+      </c>
+      <c r="F37" s="178">
+        <v>0</v>
+      </c>
+      <c r="G37" s="178">
+        <v>0</v>
+      </c>
+      <c r="H37" s="178">
+        <v>0</v>
+      </c>
+      <c r="I37" s="178">
+        <v>0</v>
+      </c>
+      <c r="J37" s="167">
         <f t="shared" si="3"/>
         <v>250000</v>
       </c>
-      <c r="K37" s="222" t="s">
+      <c r="K37" s="179" t="s">
         <v>356</v>
       </c>
-      <c r="L37" s="209">
+      <c r="L37" s="167">
         <v>250000</v>
       </c>
-      <c r="M37" s="210">
+      <c r="M37" s="168">
         <v>6.8</v>
       </c>
-      <c r="N37" s="210" t="s">
+      <c r="N37" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="223"/>
-      <c r="B38" s="224"/>
-      <c r="C38" s="225"/>
-      <c r="D38" s="226">
+      <c r="A38" s="180"/>
+      <c r="B38" s="181"/>
+      <c r="C38" s="182"/>
+      <c r="D38" s="183">
         <f>SUM(D26:D37)</f>
         <v>3483614</v>
       </c>
-      <c r="E38" s="226">
+      <c r="E38" s="183">
         <f>SUM(E26:E37)</f>
         <v>1066</v>
       </c>
-      <c r="F38" s="226">
+      <c r="F38" s="183">
         <f t="shared" ref="F38" si="4">SUM(F26:F37)</f>
         <v>12681</v>
       </c>
-      <c r="G38" s="226">
+      <c r="G38" s="183">
         <f>SUM(G26:G37)</f>
         <v>40788</v>
       </c>
-      <c r="H38" s="226">
+      <c r="H38" s="183">
         <f>SUM(H26:H37)</f>
         <v>83228</v>
       </c>
-      <c r="I38" s="226">
+      <c r="I38" s="183">
         <f>SUM(I26:I37)</f>
         <v>176854</v>
       </c>
-      <c r="J38" s="226">
+      <c r="J38" s="183">
         <f>SUM(J26:J37)</f>
         <v>3798231</v>
       </c>
-      <c r="K38" s="227"/>
-      <c r="L38" s="226">
+      <c r="K38" s="184"/>
+      <c r="L38" s="183">
         <f>SUM(L26:L37)</f>
         <v>4205141</v>
       </c>
-      <c r="M38" s="223"/>
-      <c r="N38" s="228"/>
-      <c r="O38" s="239"/>
+      <c r="M38" s="180"/>
+      <c r="N38" s="185"/>
+      <c r="O38" s="193"/>
     </row>
     <row r="39" spans="1:18" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="230"/>
-      <c r="D39" s="158"/>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="158"/>
-      <c r="H39" s="158"/>
-      <c r="I39" s="158"/>
-      <c r="J39" s="158"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="N39" s="232"/>
+      <c r="B39" s="144"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="137"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="137"/>
+      <c r="K39" s="186"/>
+      <c r="L39" s="186"/>
+      <c r="N39" s="187"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B40" s="205" t="s">
+      <c r="B40" s="164" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="240"/>
+      <c r="D40" s="194"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" s="206">
+      <c r="A41" s="165">
         <v>31</v>
       </c>
-      <c r="B41" s="211" t="s">
+      <c r="B41" s="169" t="s">
         <v>339</v>
       </c>
-      <c r="C41" s="208" t="s">
+      <c r="C41" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="D41" s="209">
+      <c r="D41" s="167">
         <v>26872</v>
       </c>
-      <c r="E41" s="209">
-        <v>0</v>
-      </c>
-      <c r="F41" s="209">
-        <v>0</v>
-      </c>
-      <c r="G41" s="209">
-        <v>0</v>
-      </c>
-      <c r="H41" s="209">
-        <v>0</v>
-      </c>
-      <c r="I41" s="209">
+      <c r="E41" s="167">
+        <v>0</v>
+      </c>
+      <c r="F41" s="167">
+        <v>0</v>
+      </c>
+      <c r="G41" s="167">
+        <v>0</v>
+      </c>
+      <c r="H41" s="167">
+        <v>0</v>
+      </c>
+      <c r="I41" s="167">
         <f>250-25</f>
         <v>225</v>
       </c>
-      <c r="J41" s="209">
+      <c r="J41" s="167">
         <f>SUM(D41:I41)</f>
         <v>27097</v>
       </c>
-      <c r="K41" s="209" t="s">
+      <c r="K41" s="167" t="s">
         <v>340</v>
       </c>
-      <c r="L41" s="209">
+      <c r="L41" s="167">
         <v>28704</v>
       </c>
-      <c r="M41" s="210">
+      <c r="M41" s="168">
         <v>6.65</v>
       </c>
-      <c r="N41" s="210" t="s">
+      <c r="N41" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" s="206">
+      <c r="A42" s="165">
         <v>32</v>
       </c>
-      <c r="B42" s="207" t="s">
+      <c r="B42" s="166" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="208" t="s">
+      <c r="C42" s="118" t="s">
         <v>213</v>
       </c>
-      <c r="D42" s="209">
+      <c r="D42" s="167">
         <v>28075</v>
       </c>
-      <c r="E42" s="209">
-        <v>0</v>
-      </c>
-      <c r="F42" s="209">
-        <v>0</v>
-      </c>
-      <c r="G42" s="209">
-        <v>0</v>
-      </c>
-      <c r="H42" s="209">
-        <v>0</v>
-      </c>
-      <c r="I42" s="209">
+      <c r="E42" s="167">
+        <v>0</v>
+      </c>
+      <c r="F42" s="167">
+        <v>0</v>
+      </c>
+      <c r="G42" s="167">
+        <v>0</v>
+      </c>
+      <c r="H42" s="167">
+        <v>0</v>
+      </c>
+      <c r="I42" s="167">
         <f>660-66</f>
         <v>594</v>
       </c>
-      <c r="J42" s="209">
+      <c r="J42" s="167">
         <f t="shared" ref="J42:J45" si="5">SUM(D42:I42)</f>
         <v>28669</v>
       </c>
-      <c r="K42" s="209" t="s">
+      <c r="K42" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="L42" s="209">
+      <c r="L42" s="167">
         <v>32126</v>
       </c>
-      <c r="M42" s="210">
+      <c r="M42" s="168">
         <v>6.8</v>
       </c>
-      <c r="N42" s="210" t="s">
+      <c r="N42" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" s="206">
+      <c r="A43" s="165">
         <v>33</v>
       </c>
-      <c r="B43" s="207" t="s">
+      <c r="B43" s="166" t="s">
         <v>200</v>
       </c>
-      <c r="C43" s="208" t="s">
+      <c r="C43" s="118" t="s">
         <v>130</v>
       </c>
-      <c r="D43" s="209">
+      <c r="D43" s="167">
         <v>13585</v>
       </c>
-      <c r="E43" s="209">
-        <v>0</v>
-      </c>
-      <c r="F43" s="209">
-        <v>0</v>
-      </c>
-      <c r="G43" s="209">
+      <c r="E43" s="167">
+        <v>0</v>
+      </c>
+      <c r="F43" s="167">
+        <v>0</v>
+      </c>
+      <c r="G43" s="167">
         <f>811-81</f>
         <v>730</v>
       </c>
-      <c r="H43" s="209">
+      <c r="H43" s="167">
         <f>1026-103</f>
         <v>923</v>
       </c>
-      <c r="I43" s="209">
+      <c r="I43" s="167">
         <f>1091-27-27-27-28</f>
         <v>982</v>
       </c>
-      <c r="J43" s="209">
+      <c r="J43" s="167">
         <f t="shared" si="5"/>
         <v>16220</v>
       </c>
-      <c r="K43" s="209" t="s">
+      <c r="K43" s="167" t="s">
         <v>208</v>
       </c>
-      <c r="L43" s="209">
+      <c r="L43" s="167">
         <v>16729</v>
       </c>
-      <c r="M43" s="210">
+      <c r="M43" s="168">
         <v>7</v>
       </c>
-      <c r="N43" s="210" t="s">
+      <c r="N43" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" s="206">
+      <c r="A44" s="165">
         <v>34</v>
       </c>
-      <c r="B44" s="241" t="s">
+      <c r="B44" s="195" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="242" t="s">
+      <c r="C44" s="196" t="s">
         <v>142</v>
       </c>
-      <c r="D44" s="243">
+      <c r="D44" s="197">
         <v>299931</v>
       </c>
-      <c r="E44" s="243">
-        <v>0</v>
-      </c>
-      <c r="F44" s="243">
-        <v>0</v>
-      </c>
-      <c r="G44" s="243">
-        <v>0</v>
-      </c>
-      <c r="H44" s="243">
+      <c r="E44" s="197">
+        <v>0</v>
+      </c>
+      <c r="F44" s="197">
+        <v>0</v>
+      </c>
+      <c r="G44" s="197">
+        <v>0</v>
+      </c>
+      <c r="H44" s="197">
         <f>2496-250</f>
         <v>2246</v>
       </c>
-      <c r="I44" s="243">
+      <c r="I44" s="197">
         <f>21655-2166</f>
         <v>19489</v>
       </c>
-      <c r="J44" s="209">
+      <c r="J44" s="167">
         <f t="shared" si="5"/>
         <v>321666</v>
       </c>
-      <c r="K44" s="221" t="s">
+      <c r="K44" s="178" t="s">
         <v>267</v>
       </c>
-      <c r="L44" s="243">
+      <c r="L44" s="197">
         <v>369347</v>
       </c>
-      <c r="M44" s="244">
+      <c r="M44" s="198">
         <v>7</v>
       </c>
-      <c r="N44" s="244" t="s">
+      <c r="N44" s="198" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="206">
+      <c r="A45" s="165">
         <v>36</v>
       </c>
-      <c r="B45" s="219">
+      <c r="B45" s="176">
         <v>116861</v>
       </c>
-      <c r="C45" s="235" t="s">
+      <c r="C45" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="D45" s="212">
+      <c r="D45" s="170">
         <v>453931</v>
       </c>
-      <c r="E45" s="212">
-        <v>0</v>
-      </c>
-      <c r="F45" s="212">
-        <v>0</v>
-      </c>
-      <c r="G45" s="212">
-        <v>0</v>
-      </c>
-      <c r="H45" s="212">
+      <c r="E45" s="170">
+        <v>0</v>
+      </c>
+      <c r="F45" s="170">
+        <v>0</v>
+      </c>
+      <c r="G45" s="170">
+        <v>0</v>
+      </c>
+      <c r="H45" s="170">
         <f>28595-2860</f>
         <v>25735</v>
       </c>
-      <c r="I45" s="212">
+      <c r="I45" s="170">
         <f>34378-3437</f>
         <v>30941</v>
       </c>
-      <c r="J45" s="209">
+      <c r="J45" s="167">
         <f t="shared" si="5"/>
         <v>510607</v>
       </c>
-      <c r="K45" s="209" t="s">
+      <c r="K45" s="167" t="s">
         <v>289</v>
       </c>
-      <c r="L45" s="212">
+      <c r="L45" s="170">
         <v>558988</v>
       </c>
-      <c r="M45" s="213">
+      <c r="M45" s="171">
         <v>7</v>
       </c>
-      <c r="N45" s="213" t="s">
+      <c r="N45" s="171" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" s="206">
+      <c r="A46" s="165">
         <v>37</v>
       </c>
-      <c r="B46" s="219">
+      <c r="B46" s="176">
         <v>116845</v>
       </c>
-      <c r="C46" s="235" t="s">
+      <c r="C46" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="D46" s="212">
+      <c r="D46" s="170">
         <v>453931</v>
       </c>
-      <c r="E46" s="212">
-        <v>0</v>
-      </c>
-      <c r="F46" s="212">
-        <v>0</v>
-      </c>
-      <c r="G46" s="212">
-        <v>0</v>
-      </c>
-      <c r="H46" s="212">
+      <c r="E46" s="170">
+        <v>0</v>
+      </c>
+      <c r="F46" s="170">
+        <v>0</v>
+      </c>
+      <c r="G46" s="170">
+        <v>0</v>
+      </c>
+      <c r="H46" s="170">
         <f>28595-2860</f>
         <v>25735</v>
       </c>
-      <c r="I46" s="212">
+      <c r="I46" s="170">
         <f>34378-3438</f>
         <v>30940</v>
       </c>
-      <c r="J46" s="209">
+      <c r="J46" s="167">
         <f>SUM(D46:I46)</f>
         <v>510606</v>
       </c>
-      <c r="K46" s="209" t="s">
+      <c r="K46" s="167" t="s">
         <v>289</v>
       </c>
-      <c r="L46" s="212">
+      <c r="L46" s="170">
         <v>558988</v>
       </c>
-      <c r="M46" s="213">
+      <c r="M46" s="171">
         <v>7</v>
       </c>
-      <c r="N46" s="213" t="s">
+      <c r="N46" s="171" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="223"/>
-      <c r="B47" s="224"/>
-      <c r="C47" s="225"/>
-      <c r="D47" s="226">
+      <c r="A47" s="180"/>
+      <c r="B47" s="181"/>
+      <c r="C47" s="182"/>
+      <c r="D47" s="183">
         <f>SUM(D41:D46)</f>
         <v>1276325</v>
       </c>
-      <c r="E47" s="226">
+      <c r="E47" s="183">
         <f t="shared" ref="E47:J47" si="6">SUM(E41:E46)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="226">
+      <c r="F47" s="183">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G47" s="226">
+      <c r="G47" s="183">
         <f t="shared" si="6"/>
         <v>730</v>
       </c>
-      <c r="H47" s="226">
+      <c r="H47" s="183">
         <f t="shared" si="6"/>
         <v>54639</v>
       </c>
-      <c r="I47" s="226">
+      <c r="I47" s="183">
         <f t="shared" si="6"/>
         <v>83171</v>
       </c>
-      <c r="J47" s="226">
+      <c r="J47" s="183">
         <f t="shared" si="6"/>
         <v>1414865</v>
       </c>
-      <c r="K47" s="227"/>
-      <c r="L47" s="226">
+      <c r="K47" s="184"/>
+      <c r="L47" s="183">
         <f>SUM(L41:L46)</f>
         <v>1564882</v>
       </c>
-      <c r="M47" s="228"/>
-      <c r="N47" s="228"/>
-      <c r="R47" s="229"/>
+      <c r="M47" s="185"/>
+      <c r="N47" s="185"/>
+      <c r="R47" s="150"/>
     </row>
     <row r="48" spans="1:18" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="230"/>
-      <c r="D48" s="158"/>
-      <c r="E48" s="158"/>
-      <c r="F48" s="158"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="158"/>
-      <c r="I48" s="158"/>
-      <c r="J48" s="158"/>
-      <c r="K48" s="231"/>
-      <c r="L48" s="231"/>
-      <c r="N48" s="232"/>
-      <c r="O48" s="239"/>
-      <c r="Q48" s="229"/>
+      <c r="B48" s="144"/>
+      <c r="D48" s="137"/>
+      <c r="E48" s="137"/>
+      <c r="F48" s="137"/>
+      <c r="G48" s="137"/>
+      <c r="H48" s="137"/>
+      <c r="I48" s="137"/>
+      <c r="J48" s="137"/>
+      <c r="K48" s="186"/>
+      <c r="L48" s="186"/>
+      <c r="N48" s="187"/>
+      <c r="O48" s="193"/>
+      <c r="Q48" s="150"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B49" s="205" t="s">
+      <c r="B49" s="164" t="s">
         <v>39</v>
       </c>
-      <c r="D49" s="158"/>
-      <c r="E49" s="158"/>
-      <c r="F49" s="158"/>
-      <c r="G49" s="158"/>
-      <c r="H49" s="158"/>
-      <c r="I49" s="158"/>
-      <c r="J49" s="158"/>
-      <c r="K49" s="231"/>
-      <c r="L49" s="231"/>
-      <c r="N49" s="232"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="186"/>
+      <c r="L49" s="186"/>
+      <c r="N49" s="187"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" s="206">
+      <c r="A50" s="165">
         <v>38</v>
       </c>
-      <c r="B50" s="211" t="s">
+      <c r="B50" s="169" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="208" t="s">
+      <c r="C50" s="118" t="s">
         <v>268</v>
       </c>
-      <c r="D50" s="209">
+      <c r="D50" s="167">
         <v>140715</v>
       </c>
-      <c r="E50" s="209">
-        <v>0</v>
-      </c>
-      <c r="F50" s="209">
-        <v>0</v>
-      </c>
-      <c r="G50" s="209">
-        <v>0</v>
-      </c>
-      <c r="H50" s="209">
-        <v>0</v>
-      </c>
-      <c r="I50" s="209">
+      <c r="E50" s="167">
+        <v>0</v>
+      </c>
+      <c r="F50" s="167">
+        <v>0</v>
+      </c>
+      <c r="G50" s="167">
+        <v>0</v>
+      </c>
+      <c r="H50" s="167">
+        <v>0</v>
+      </c>
+      <c r="I50" s="167">
         <f>1317-132</f>
         <v>1185</v>
       </c>
-      <c r="J50" s="209">
+      <c r="J50" s="167">
         <f>SUM(D50:I50)</f>
         <v>141900</v>
       </c>
-      <c r="K50" s="209" t="s">
+      <c r="K50" s="167" t="s">
         <v>340</v>
       </c>
-      <c r="L50" s="209">
+      <c r="L50" s="167">
         <v>150309</v>
       </c>
-      <c r="M50" s="210">
+      <c r="M50" s="168">
         <v>6.65</v>
       </c>
-      <c r="N50" s="210" t="s">
+      <c r="N50" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" s="206">
+      <c r="A51" s="165">
         <v>39</v>
       </c>
-      <c r="B51" s="207" t="s">
+      <c r="B51" s="166" t="s">
         <v>330</v>
       </c>
-      <c r="C51" s="208" t="s">
+      <c r="C51" s="118" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="209">
+      <c r="D51" s="167">
         <v>35505</v>
       </c>
-      <c r="E51" s="209">
-        <v>0</v>
-      </c>
-      <c r="F51" s="209">
-        <v>0</v>
-      </c>
-      <c r="G51" s="209">
-        <v>0</v>
-      </c>
-      <c r="H51" s="209">
-        <v>0</v>
-      </c>
-      <c r="I51" s="209">
+      <c r="E51" s="167">
+        <v>0</v>
+      </c>
+      <c r="F51" s="167">
+        <v>0</v>
+      </c>
+      <c r="G51" s="167">
+        <v>0</v>
+      </c>
+      <c r="H51" s="167">
+        <v>0</v>
+      </c>
+      <c r="I51" s="167">
         <f>834-84</f>
         <v>750</v>
       </c>
-      <c r="J51" s="209">
+      <c r="J51" s="167">
         <f>SUM(D51:I51)</f>
         <v>36255</v>
       </c>
-      <c r="K51" s="209" t="s">
+      <c r="K51" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="L51" s="209">
+      <c r="L51" s="167">
         <v>40628</v>
       </c>
-      <c r="M51" s="210">
+      <c r="M51" s="168">
         <v>6.8</v>
       </c>
-      <c r="N51" s="210" t="s">
+      <c r="N51" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="206">
+      <c r="A52" s="165">
         <v>40</v>
       </c>
-      <c r="B52" s="207" t="s">
+      <c r="B52" s="166" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="208" t="s">
+      <c r="C52" s="118" t="s">
         <v>130</v>
       </c>
-      <c r="D52" s="209">
+      <c r="D52" s="167">
         <v>13585</v>
       </c>
-      <c r="E52" s="209">
-        <v>0</v>
-      </c>
-      <c r="F52" s="209">
-        <v>0</v>
-      </c>
-      <c r="G52" s="209">
+      <c r="E52" s="167">
+        <v>0</v>
+      </c>
+      <c r="F52" s="167">
+        <v>0</v>
+      </c>
+      <c r="G52" s="167">
         <f>811-80</f>
         <v>731</v>
       </c>
-      <c r="H52" s="209">
+      <c r="H52" s="167">
         <f>1026-103</f>
         <v>923</v>
       </c>
-      <c r="I52" s="209">
+      <c r="I52" s="167">
         <f>266+271+275+279-26-27-28-27</f>
         <v>983</v>
       </c>
-      <c r="J52" s="209">
+      <c r="J52" s="167">
         <f>SUM(D52:I52)</f>
         <v>16222</v>
       </c>
-      <c r="K52" s="209" t="s">
+      <c r="K52" s="167" t="s">
         <v>208</v>
       </c>
-      <c r="L52" s="209">
+      <c r="L52" s="167">
         <v>16729</v>
       </c>
-      <c r="M52" s="210">
+      <c r="M52" s="168">
         <v>7</v>
       </c>
-      <c r="N52" s="210" t="s">
+      <c r="N52" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="206">
+      <c r="A53" s="165">
         <v>41</v>
       </c>
-      <c r="B53" s="214">
+      <c r="B53" s="172">
         <v>6605500001645</v>
       </c>
-      <c r="C53" s="245" t="s">
+      <c r="C53" s="199" t="s">
         <v>335</v>
       </c>
-      <c r="D53" s="243">
+      <c r="D53" s="197">
         <v>23174</v>
       </c>
-      <c r="E53" s="243">
-        <v>0</v>
-      </c>
-      <c r="F53" s="243">
-        <v>0</v>
-      </c>
-      <c r="G53" s="243">
-        <v>0</v>
-      </c>
-      <c r="H53" s="243">
-        <v>0</v>
-      </c>
-      <c r="I53" s="243">
+      <c r="E53" s="197">
+        <v>0</v>
+      </c>
+      <c r="F53" s="197">
+        <v>0</v>
+      </c>
+      <c r="G53" s="197">
+        <v>0</v>
+      </c>
+      <c r="H53" s="197">
+        <v>0</v>
+      </c>
+      <c r="I53" s="197">
         <f>177-18</f>
         <v>159</v>
       </c>
-      <c r="J53" s="209">
+      <c r="J53" s="167">
         <f>SUM(D53:I53)</f>
         <v>23333</v>
       </c>
-      <c r="K53" s="222" t="s">
+      <c r="K53" s="179" t="s">
         <v>336</v>
       </c>
-      <c r="L53" s="212">
+      <c r="L53" s="170">
         <v>28328</v>
       </c>
-      <c r="M53" s="213">
+      <c r="M53" s="171">
         <v>6.75</v>
       </c>
-      <c r="N53" s="213" t="s">
+      <c r="N53" s="171" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="206">
+      <c r="A54" s="165">
         <v>42</v>
       </c>
-      <c r="B54" s="246" t="s">
+      <c r="B54" s="200" t="s">
         <v>253</v>
       </c>
-      <c r="C54" s="235" t="s">
+      <c r="C54" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="212">
+      <c r="D54" s="170">
         <v>64785</v>
       </c>
-      <c r="E54" s="212">
-        <v>0</v>
-      </c>
-      <c r="F54" s="212">
-        <v>0</v>
-      </c>
-      <c r="G54" s="212">
-        <v>0</v>
-      </c>
-      <c r="H54" s="212">
+      <c r="E54" s="170">
+        <v>0</v>
+      </c>
+      <c r="F54" s="170">
+        <v>0</v>
+      </c>
+      <c r="G54" s="170">
+        <v>0</v>
+      </c>
+      <c r="H54" s="170">
         <f>538-54</f>
         <v>484</v>
       </c>
-      <c r="I54" s="212">
+      <c r="I54" s="170">
         <f>4677-468</f>
         <v>4209</v>
       </c>
-      <c r="J54" s="209">
+      <c r="J54" s="167">
         <f t="shared" ref="J54:J66" si="7">SUM(D54:I54)</f>
         <v>69478</v>
       </c>
-      <c r="K54" s="209" t="s">
+      <c r="K54" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="L54" s="209">
+      <c r="L54" s="167">
         <v>79779</v>
       </c>
-      <c r="M54" s="210">
+      <c r="M54" s="168">
         <v>7</v>
       </c>
-      <c r="N54" s="213" t="s">
+      <c r="N54" s="171" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="206">
+      <c r="A55" s="165">
         <v>43</v>
       </c>
-      <c r="B55" s="211" t="s">
+      <c r="B55" s="169" t="s">
         <v>341</v>
       </c>
-      <c r="C55" s="208" t="s">
+      <c r="C55" s="118" t="s">
         <v>269</v>
       </c>
-      <c r="D55" s="209">
+      <c r="D55" s="167">
         <v>37105</v>
       </c>
-      <c r="E55" s="209">
-        <v>0</v>
-      </c>
-      <c r="F55" s="209">
-        <v>0</v>
-      </c>
-      <c r="G55" s="209">
-        <v>0</v>
-      </c>
-      <c r="H55" s="209">
-        <v>0</v>
-      </c>
-      <c r="I55" s="209">
+      <c r="E55" s="167">
+        <v>0</v>
+      </c>
+      <c r="F55" s="167">
+        <v>0</v>
+      </c>
+      <c r="G55" s="167">
+        <v>0</v>
+      </c>
+      <c r="H55" s="167">
+        <v>0</v>
+      </c>
+      <c r="I55" s="167">
         <f>27-3</f>
         <v>24</v>
       </c>
-      <c r="J55" s="209">
+      <c r="J55" s="167">
         <f>SUM(D55:I55)</f>
         <v>37129</v>
       </c>
-      <c r="K55" s="209" t="s">
+      <c r="K55" s="167" t="s">
         <v>338</v>
       </c>
-      <c r="L55" s="209">
+      <c r="L55" s="167">
         <v>39635</v>
       </c>
-      <c r="M55" s="210">
+      <c r="M55" s="168">
         <v>6.65</v>
       </c>
-      <c r="N55" s="210" t="s">
+      <c r="N55" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" s="206">
+      <c r="A56" s="165">
         <v>44</v>
       </c>
-      <c r="B56" s="207" t="s">
+      <c r="B56" s="166" t="s">
         <v>258</v>
       </c>
-      <c r="C56" s="208" t="s">
+      <c r="C56" s="118" t="s">
         <v>157</v>
       </c>
-      <c r="D56" s="209">
+      <c r="D56" s="167">
         <v>104165</v>
       </c>
-      <c r="E56" s="209">
-        <v>0</v>
-      </c>
-      <c r="F56" s="209">
-        <v>0</v>
-      </c>
-      <c r="G56" s="209">
-        <v>0</v>
-      </c>
-      <c r="H56" s="209">
+      <c r="E56" s="167">
+        <v>0</v>
+      </c>
+      <c r="F56" s="167">
+        <v>0</v>
+      </c>
+      <c r="G56" s="167">
+        <v>0</v>
+      </c>
+      <c r="H56" s="167">
         <f>6448-644</f>
         <v>5804</v>
       </c>
-      <c r="I56" s="209">
+      <c r="I56" s="167">
         <f>7020-704</f>
         <v>6316</v>
       </c>
-      <c r="J56" s="209">
+      <c r="J56" s="167">
         <f t="shared" si="7"/>
         <v>116285</v>
       </c>
-      <c r="K56" s="209" t="s">
+      <c r="K56" s="167" t="s">
         <v>287</v>
       </c>
-      <c r="L56" s="209">
+      <c r="L56" s="167">
         <v>125456</v>
       </c>
-      <c r="M56" s="210">
+      <c r="M56" s="168">
         <v>6.25</v>
       </c>
-      <c r="N56" s="210" t="s">
+      <c r="N56" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" s="206">
+      <c r="A57" s="165">
         <v>45</v>
       </c>
-      <c r="B57" s="207">
+      <c r="B57" s="166">
         <v>42392</v>
       </c>
-      <c r="C57" s="208" t="s">
+      <c r="C57" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="209">
+      <c r="D57" s="167">
         <v>253640</v>
       </c>
-      <c r="E57" s="209">
+      <c r="E57" s="167">
         <f>8363-838</f>
         <v>7525</v>
       </c>
-      <c r="F57" s="209">
+      <c r="F57" s="167">
         <f>14903-1492</f>
         <v>13411</v>
       </c>
-      <c r="G57" s="209">
+      <c r="G57" s="167">
         <f>15712-1571</f>
         <v>14141</v>
       </c>
-      <c r="H57" s="209">
+      <c r="H57" s="167">
         <f>16476-1648</f>
         <v>14828</v>
       </c>
-      <c r="I57" s="209">
+      <c r="I57" s="167">
         <f>17322-1732</f>
         <v>15590</v>
       </c>
-      <c r="J57" s="209">
+      <c r="J57" s="167">
         <f t="shared" si="7"/>
         <v>319135</v>
       </c>
-      <c r="K57" s="209" t="s">
+      <c r="K57" s="167" t="s">
         <v>151</v>
       </c>
-      <c r="L57" s="209">
+      <c r="L57" s="167">
         <v>334948</v>
       </c>
-      <c r="M57" s="210">
+      <c r="M57" s="168">
         <v>5.6</v>
       </c>
-      <c r="N57" s="210" t="s">
+      <c r="N57" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="206">
+      <c r="A58" s="165">
         <v>46</v>
       </c>
-      <c r="B58" s="207" t="s">
+      <c r="B58" s="166" t="s">
         <v>189</v>
       </c>
-      <c r="C58" s="208" t="s">
+      <c r="C58" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="D58" s="209">
+      <c r="D58" s="167">
         <v>124632</v>
       </c>
-      <c r="E58" s="209">
-        <v>0</v>
-      </c>
-      <c r="F58" s="209">
-        <v>0</v>
-      </c>
-      <c r="G58" s="209">
+      <c r="E58" s="167">
+        <v>0</v>
+      </c>
+      <c r="F58" s="167">
+        <v>0</v>
+      </c>
+      <c r="G58" s="167">
         <f>1287-128</f>
         <v>1159</v>
       </c>
-      <c r="H58" s="209">
+      <c r="H58" s="167">
         <f>9346-934</f>
         <v>8412</v>
       </c>
-      <c r="I58" s="209">
+      <c r="I58" s="167">
         <f>9970-997</f>
         <v>8973</v>
       </c>
-      <c r="J58" s="209">
+      <c r="J58" s="167">
         <f t="shared" si="7"/>
         <v>143176</v>
       </c>
-      <c r="K58" s="209" t="s">
+      <c r="K58" s="167" t="s">
         <v>206</v>
       </c>
-      <c r="L58" s="209">
+      <c r="L58" s="167">
         <v>154612</v>
       </c>
-      <c r="M58" s="210">
+      <c r="M58" s="168">
         <v>5.75</v>
       </c>
-      <c r="N58" s="210" t="s">
+      <c r="N58" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" s="206">
+      <c r="A59" s="165">
         <v>47</v>
       </c>
-      <c r="B59" s="207" t="s">
+      <c r="B59" s="166" t="s">
         <v>191</v>
       </c>
-      <c r="C59" s="208" t="s">
+      <c r="C59" s="118" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="209">
+      <c r="D59" s="167">
         <v>10230</v>
       </c>
-      <c r="E59" s="209">
-        <v>0</v>
-      </c>
-      <c r="F59" s="209">
-        <v>0</v>
-      </c>
-      <c r="G59" s="209">
+      <c r="E59" s="167">
+        <v>0</v>
+      </c>
+      <c r="F59" s="167">
+        <v>0</v>
+      </c>
+      <c r="G59" s="167">
         <f>12-1</f>
         <v>11</v>
       </c>
-      <c r="H59" s="209">
+      <c r="H59" s="167">
         <f>761-77</f>
         <v>684</v>
       </c>
-      <c r="I59" s="209">
+      <c r="I59" s="167">
         <f>196+202+206+207-20-20-21-20</f>
         <v>730</v>
       </c>
-      <c r="J59" s="209">
+      <c r="J59" s="167">
         <f t="shared" si="7"/>
         <v>11655</v>
       </c>
-      <c r="K59" s="209" t="s">
+      <c r="K59" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="L59" s="209">
+      <c r="L59" s="167">
         <v>12691</v>
       </c>
-      <c r="M59" s="210">
+      <c r="M59" s="168">
         <v>7.25</v>
       </c>
-      <c r="N59" s="210" t="s">
+      <c r="N59" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="O59" s="229"/>
+      <c r="O59" s="150"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="206">
+      <c r="A60" s="165">
         <v>48</v>
       </c>
-      <c r="B60" s="207" t="s">
+      <c r="B60" s="166" t="s">
         <v>272</v>
       </c>
-      <c r="C60" s="208" t="s">
+      <c r="C60" s="118" t="s">
         <v>155</v>
       </c>
-      <c r="D60" s="209">
+      <c r="D60" s="167">
         <v>108481</v>
       </c>
-      <c r="E60" s="209">
-        <v>0</v>
-      </c>
-      <c r="F60" s="209">
-        <v>0</v>
-      </c>
-      <c r="G60" s="209">
-        <v>0</v>
-      </c>
-      <c r="H60" s="209">
+      <c r="E60" s="167">
+        <v>0</v>
+      </c>
+      <c r="F60" s="167">
+        <v>0</v>
+      </c>
+      <c r="G60" s="167">
+        <v>0</v>
+      </c>
+      <c r="H60" s="167">
         <f>1061-107</f>
         <v>954</v>
       </c>
-      <c r="I60" s="209">
+      <c r="I60" s="167">
         <f>7844-784</f>
         <v>7060</v>
       </c>
-      <c r="J60" s="209">
+      <c r="J60" s="167">
         <f t="shared" si="7"/>
         <v>116495</v>
       </c>
-      <c r="K60" s="209" t="s">
+      <c r="K60" s="167" t="s">
         <v>285</v>
       </c>
-      <c r="L60" s="209">
+      <c r="L60" s="167">
         <v>135588</v>
       </c>
-      <c r="M60" s="210">
+      <c r="M60" s="168">
         <v>7</v>
       </c>
-      <c r="N60" s="210" t="s">
+      <c r="N60" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="O60" s="229"/>
+      <c r="O60" s="150"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="206">
+      <c r="A61" s="165">
         <v>49</v>
       </c>
-      <c r="B61" s="207">
+      <c r="B61" s="166">
         <v>43584</v>
       </c>
-      <c r="C61" s="208" t="s">
+      <c r="C61" s="118" t="s">
         <v>162</v>
       </c>
-      <c r="D61" s="209">
+      <c r="D61" s="167">
         <v>100800</v>
       </c>
-      <c r="E61" s="209">
-        <v>0</v>
-      </c>
-      <c r="F61" s="209">
+      <c r="E61" s="167">
+        <v>0</v>
+      </c>
+      <c r="F61" s="167">
         <f>2169-218</f>
         <v>1951</v>
       </c>
-      <c r="G61" s="209">
+      <c r="G61" s="167">
         <f>7111-711</f>
         <v>6400</v>
       </c>
-      <c r="H61" s="209">
+      <c r="H61" s="167">
         <f>7537-754</f>
         <v>6783</v>
       </c>
-      <c r="I61" s="209">
+      <c r="I61" s="167">
         <f>8006-800</f>
         <v>7206</v>
       </c>
-      <c r="J61" s="209">
+      <c r="J61" s="167">
         <f t="shared" si="7"/>
         <v>123140</v>
       </c>
-      <c r="K61" s="209" t="s">
+      <c r="K61" s="167" t="s">
         <v>166</v>
       </c>
-      <c r="L61" s="209">
+      <c r="L61" s="167">
         <v>140868</v>
       </c>
-      <c r="M61" s="210">
+      <c r="M61" s="168">
         <v>6.75</v>
       </c>
-      <c r="N61" s="210" t="s">
+      <c r="N61" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" s="206">
+      <c r="A62" s="165">
         <v>50</v>
       </c>
-      <c r="B62" s="207" t="s">
+      <c r="B62" s="166" t="s">
         <v>331</v>
       </c>
-      <c r="C62" s="208" t="s">
+      <c r="C62" s="118" t="s">
         <v>213</v>
       </c>
-      <c r="D62" s="209">
+      <c r="D62" s="167">
         <v>77374</v>
       </c>
-      <c r="E62" s="209">
-        <v>0</v>
-      </c>
-      <c r="F62" s="209">
-        <v>0</v>
-      </c>
-      <c r="G62" s="209">
-        <v>0</v>
-      </c>
-      <c r="H62" s="209">
-        <v>0</v>
-      </c>
-      <c r="I62" s="209">
+      <c r="E62" s="167">
+        <v>0</v>
+      </c>
+      <c r="F62" s="167">
+        <v>0</v>
+      </c>
+      <c r="G62" s="167">
+        <v>0</v>
+      </c>
+      <c r="H62" s="167">
+        <v>0</v>
+      </c>
+      <c r="I62" s="167">
         <f>1818-182</f>
         <v>1636</v>
       </c>
-      <c r="J62" s="209">
+      <c r="J62" s="167">
         <f t="shared" si="7"/>
         <v>79010</v>
       </c>
-      <c r="K62" s="209" t="s">
+      <c r="K62" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="L62" s="209">
+      <c r="L62" s="167">
         <v>88538</v>
       </c>
-      <c r="M62" s="210">
+      <c r="M62" s="168">
         <v>6.8</v>
       </c>
-      <c r="N62" s="210" t="s">
+      <c r="N62" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A63" s="206">
+      <c r="A63" s="165">
         <v>51</v>
       </c>
-      <c r="B63" s="211" t="s">
+      <c r="B63" s="169" t="s">
         <v>351</v>
       </c>
-      <c r="C63" s="209" t="s">
+      <c r="C63" s="167" t="s">
         <v>214</v>
       </c>
-      <c r="D63" s="209">
+      <c r="D63" s="167">
         <v>154203</v>
       </c>
-      <c r="E63" s="209">
-        <v>0</v>
-      </c>
-      <c r="F63" s="209">
-        <v>0</v>
-      </c>
-      <c r="G63" s="209">
-        <v>0</v>
-      </c>
-      <c r="H63" s="209">
-        <v>0</v>
-      </c>
-      <c r="I63" s="209">
+      <c r="E63" s="167">
+        <v>0</v>
+      </c>
+      <c r="F63" s="167">
+        <v>0</v>
+      </c>
+      <c r="G63" s="167">
+        <v>0</v>
+      </c>
+      <c r="H63" s="167">
+        <v>0</v>
+      </c>
+      <c r="I63" s="167">
         <v>8245</v>
       </c>
-      <c r="J63" s="209">
+      <c r="J63" s="167">
         <f t="shared" si="7"/>
         <v>162448</v>
       </c>
-      <c r="K63" s="209" t="s">
+      <c r="K63" s="167" t="s">
         <v>363</v>
       </c>
-      <c r="L63" s="209"/>
-      <c r="M63" s="210">
+      <c r="L63" s="167"/>
+      <c r="M63" s="168">
         <v>7</v>
       </c>
-      <c r="N63" s="210" t="s">
+      <c r="N63" s="168" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A64" s="206">
+      <c r="A64" s="165">
         <v>52</v>
       </c>
-      <c r="B64" s="211" t="s">
+      <c r="B64" s="169" t="s">
         <v>354</v>
       </c>
-      <c r="C64" s="208" t="s">
+      <c r="C64" s="118" t="s">
         <v>292</v>
       </c>
-      <c r="D64" s="209">
+      <c r="D64" s="167">
         <v>97472</v>
       </c>
-      <c r="E64" s="209">
-        <v>0</v>
-      </c>
-      <c r="F64" s="209">
-        <v>0</v>
-      </c>
-      <c r="G64" s="209">
-        <v>0</v>
-      </c>
-      <c r="H64" s="209">
-        <v>0</v>
-      </c>
-      <c r="I64" s="209">
+      <c r="E64" s="167">
+        <v>0</v>
+      </c>
+      <c r="F64" s="167">
+        <v>0</v>
+      </c>
+      <c r="G64" s="167">
+        <v>0</v>
+      </c>
+      <c r="H64" s="167">
+        <v>0</v>
+      </c>
+      <c r="I64" s="167">
         <f>6393-2878</f>
         <v>3515</v>
       </c>
-      <c r="J64" s="209">
+      <c r="J64" s="167">
         <f t="shared" si="7"/>
         <v>100987</v>
       </c>
-      <c r="K64" s="209" t="s">
+      <c r="K64" s="167" t="s">
         <v>365</v>
       </c>
-      <c r="L64" s="209">
+      <c r="L64" s="167">
         <v>106151</v>
       </c>
-      <c r="M64" s="210">
+      <c r="M64" s="168">
         <v>6.5</v>
       </c>
-      <c r="N64" s="210" t="s">
+      <c r="N64" s="168" t="s">
         <v>107</v>
       </c>
-      <c r="Q64" s="229"/>
-      <c r="R64" s="229"/>
+      <c r="Q64" s="150"/>
+      <c r="R64" s="150"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="206">
+      <c r="A65" s="165">
         <v>53</v>
       </c>
-      <c r="B65" s="217">
+      <c r="B65" s="174">
         <v>21103</v>
       </c>
-      <c r="C65" s="208" t="s">
+      <c r="C65" s="118" t="s">
         <v>193</v>
       </c>
-      <c r="D65" s="209">
+      <c r="D65" s="167">
         <v>104400</v>
       </c>
-      <c r="E65" s="209">
-        <v>0</v>
-      </c>
-      <c r="F65" s="209">
-        <v>0</v>
-      </c>
-      <c r="G65" s="209">
+      <c r="E65" s="167">
+        <v>0</v>
+      </c>
+      <c r="F65" s="167">
+        <v>0</v>
+      </c>
+      <c r="G65" s="167">
         <f>3523-353</f>
         <v>3170</v>
       </c>
-      <c r="H65" s="209">
+      <c r="H65" s="167">
         <f>7710-772</f>
         <v>6938</v>
       </c>
-      <c r="I65" s="209">
+      <c r="I65" s="167">
         <f>8207-820</f>
         <v>7387</v>
       </c>
-      <c r="J65" s="209">
+      <c r="J65" s="167">
         <f t="shared" si="7"/>
         <v>121895</v>
       </c>
-      <c r="K65" s="209" t="s">
+      <c r="K65" s="167" t="s">
         <v>211</v>
       </c>
-      <c r="L65" s="209">
+      <c r="L65" s="167">
         <v>128562</v>
       </c>
-      <c r="M65" s="210">
+      <c r="M65" s="168">
         <v>7</v>
       </c>
-      <c r="N65" s="210" t="s">
+      <c r="N65" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="206">
+      <c r="A66" s="165">
         <v>54</v>
       </c>
-      <c r="B66" s="237">
+      <c r="B66" s="191">
         <v>281681</v>
       </c>
-      <c r="C66" s="220" t="s">
+      <c r="C66" s="177" t="s">
         <v>280</v>
       </c>
-      <c r="D66" s="221">
+      <c r="D66" s="178">
         <v>123938</v>
       </c>
-      <c r="E66" s="221">
-        <v>0</v>
-      </c>
-      <c r="F66" s="221">
-        <v>0</v>
-      </c>
-      <c r="G66" s="221">
-        <v>0</v>
-      </c>
-      <c r="H66" s="221">
+      <c r="E66" s="178">
+        <v>0</v>
+      </c>
+      <c r="F66" s="178">
+        <v>0</v>
+      </c>
+      <c r="G66" s="178">
+        <v>0</v>
+      </c>
+      <c r="H66" s="178">
         <f>350-35</f>
         <v>315</v>
       </c>
-      <c r="I66" s="221">
+      <c r="I66" s="178">
         <f>8905-890</f>
         <v>8015</v>
       </c>
-      <c r="J66" s="209">
+      <c r="J66" s="167">
         <f t="shared" si="7"/>
         <v>132268</v>
       </c>
-      <c r="K66" s="222" t="s">
+      <c r="K66" s="179" t="s">
         <v>281</v>
       </c>
-      <c r="L66" s="221">
+      <c r="L66" s="178">
         <v>175345</v>
       </c>
-      <c r="M66" s="210">
+      <c r="M66" s="168">
         <v>7</v>
       </c>
-      <c r="N66" s="210" t="s">
+      <c r="N66" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="206">
+      <c r="A67" s="165">
         <v>55</v>
       </c>
-      <c r="B67" s="237" t="s">
+      <c r="B67" s="191" t="s">
         <v>357</v>
       </c>
-      <c r="C67" s="220" t="s">
+      <c r="C67" s="177" t="s">
         <v>358</v>
       </c>
-      <c r="D67" s="221">
+      <c r="D67" s="178">
         <v>63324</v>
       </c>
-      <c r="E67" s="221">
-        <v>0</v>
-      </c>
-      <c r="F67" s="221">
-        <v>0</v>
-      </c>
-      <c r="G67" s="221">
-        <v>0</v>
-      </c>
-      <c r="H67" s="221">
-        <v>0</v>
-      </c>
-      <c r="I67" s="221">
-        <v>0</v>
-      </c>
-      <c r="J67" s="209">
+      <c r="E67" s="178">
+        <v>0</v>
+      </c>
+      <c r="F67" s="178">
+        <v>0</v>
+      </c>
+      <c r="G67" s="178">
+        <v>0</v>
+      </c>
+      <c r="H67" s="178">
+        <v>0</v>
+      </c>
+      <c r="I67" s="178">
+        <v>0</v>
+      </c>
+      <c r="J67" s="167">
         <f>SUM(D67:I67)</f>
         <v>63324</v>
       </c>
-      <c r="K67" s="222" t="s">
+      <c r="K67" s="179" t="s">
         <v>359</v>
       </c>
-      <c r="L67" s="221">
+      <c r="L67" s="178">
         <v>63324</v>
       </c>
-      <c r="M67" s="210">
+      <c r="M67" s="168">
         <v>6.8</v>
       </c>
-      <c r="N67" s="210" t="s">
+      <c r="N67" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="223"/>
-      <c r="B68" s="224"/>
-      <c r="C68" s="225"/>
-      <c r="D68" s="226">
+      <c r="A68" s="180"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="182"/>
+      <c r="D68" s="183">
         <f>SUM(D50:D67)</f>
         <v>1637528</v>
       </c>
-      <c r="E68" s="226">
+      <c r="E68" s="183">
         <f t="shared" ref="E68:H68" si="8">SUM(E50:E67)</f>
         <v>7525</v>
       </c>
-      <c r="F68" s="226">
+      <c r="F68" s="183">
         <f t="shared" si="8"/>
         <v>15362</v>
       </c>
-      <c r="G68" s="226">
+      <c r="G68" s="183">
         <f t="shared" si="8"/>
         <v>25612</v>
       </c>
-      <c r="H68" s="226">
+      <c r="H68" s="183">
         <f t="shared" si="8"/>
         <v>46125</v>
       </c>
-      <c r="I68" s="226">
+      <c r="I68" s="183">
         <f>SUM(I50:I67)</f>
         <v>81983</v>
       </c>
-      <c r="J68" s="226">
+      <c r="J68" s="183">
         <f>SUM(J50:J67)</f>
         <v>1814135</v>
       </c>
-      <c r="K68" s="227"/>
-      <c r="L68" s="226">
+      <c r="K68" s="184"/>
+      <c r="L68" s="183">
         <f>SUM(L50:L67)</f>
         <v>1821491</v>
       </c>
-      <c r="M68" s="223"/>
-      <c r="N68" s="228"/>
-      <c r="O68" s="239"/>
+      <c r="M68" s="180"/>
+      <c r="N68" s="185"/>
+      <c r="O68" s="193"/>
     </row>
     <row r="69" spans="1:15" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="K69" s="231"/>
-      <c r="L69" s="231"/>
+      <c r="K69" s="186"/>
+      <c r="L69" s="186"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B70" s="205" t="s">
+      <c r="B70" s="164" t="s">
         <v>175</v>
       </c>
-      <c r="K70" s="231"/>
-      <c r="L70" s="231"/>
+      <c r="K70" s="186"/>
+      <c r="L70" s="186"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="206">
+      <c r="A71" s="165">
         <v>56</v>
       </c>
-      <c r="B71" s="207">
+      <c r="B71" s="166">
         <v>42886</v>
       </c>
-      <c r="C71" s="208" t="s">
+      <c r="C71" s="118" t="s">
         <v>139</v>
       </c>
-      <c r="D71" s="209">
+      <c r="D71" s="167">
         <v>10000</v>
       </c>
-      <c r="E71" s="209">
+      <c r="E71" s="167">
         <f>77-8</f>
         <v>69</v>
       </c>
-      <c r="F71" s="209">
+      <c r="F71" s="167">
         <f>591-61</f>
         <v>530</v>
       </c>
-      <c r="G71" s="209">
+      <c r="G71" s="167">
         <f>624-63</f>
         <v>561</v>
       </c>
-      <c r="H71" s="209">
+      <c r="H71" s="167">
         <f>655-67</f>
         <v>588</v>
       </c>
-      <c r="I71" s="209">
+      <c r="I71" s="167">
         <f>688-68</f>
         <v>620</v>
       </c>
-      <c r="J71" s="209">
+      <c r="J71" s="167">
         <f>SUM(D71:I71)</f>
         <v>12368</v>
       </c>
-      <c r="K71" s="209" t="s">
+      <c r="K71" s="167" t="s">
         <v>149</v>
       </c>
-      <c r="L71" s="209">
+      <c r="L71" s="167">
         <v>13304</v>
       </c>
-      <c r="M71" s="210">
+      <c r="M71" s="168">
         <v>5.75</v>
       </c>
-      <c r="N71" s="210" t="s">
+      <c r="N71" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="206">
+      <c r="A72" s="165">
         <v>57</v>
       </c>
-      <c r="B72" s="207" t="s">
+      <c r="B72" s="166" t="s">
         <v>184</v>
       </c>
-      <c r="C72" s="208" t="s">
+      <c r="C72" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="D72" s="209">
+      <c r="D72" s="167">
         <v>18320</v>
       </c>
-      <c r="E72" s="247">
-        <v>0</v>
-      </c>
-      <c r="F72" s="247">
-        <v>0</v>
-      </c>
-      <c r="G72" s="247">
+      <c r="E72" s="201">
+        <v>0</v>
+      </c>
+      <c r="F72" s="201">
+        <v>0</v>
+      </c>
+      <c r="G72" s="201">
         <f>1140-115</f>
         <v>1025</v>
       </c>
-      <c r="H72" s="247">
+      <c r="H72" s="201">
         <f>1386-138</f>
         <v>1248</v>
       </c>
-      <c r="I72" s="247">
+      <c r="I72" s="201">
         <f>1476-148</f>
         <v>1328</v>
       </c>
-      <c r="J72" s="209">
+      <c r="J72" s="167">
         <f t="shared" ref="J72:J77" si="9">SUM(D72:I72)</f>
         <v>21921</v>
       </c>
-      <c r="K72" s="209" t="s">
+      <c r="K72" s="167" t="s">
         <v>209</v>
       </c>
-      <c r="L72" s="209">
+      <c r="L72" s="167">
         <v>22560</v>
       </c>
-      <c r="M72" s="210">
+      <c r="M72" s="168">
         <v>7</v>
       </c>
-      <c r="N72" s="210" t="s">
+      <c r="N72" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="206">
+      <c r="A73" s="165">
         <v>58</v>
       </c>
-      <c r="B73" s="207">
+      <c r="B73" s="166">
         <v>42391</v>
       </c>
-      <c r="C73" s="208" t="s">
+      <c r="C73" s="118" t="s">
         <v>101</v>
       </c>
-      <c r="D73" s="209">
+      <c r="D73" s="167">
         <v>13202</v>
       </c>
-      <c r="E73" s="209">
+      <c r="E73" s="167">
         <f>435-45</f>
         <v>390</v>
       </c>
-      <c r="F73" s="209">
+      <c r="F73" s="167">
         <f>775-79</f>
         <v>696</v>
       </c>
-      <c r="G73" s="209">
+      <c r="G73" s="167">
         <f>819-82</f>
         <v>737</v>
       </c>
-      <c r="H73" s="209">
+      <c r="H73" s="167">
         <f>857-85</f>
         <v>772</v>
       </c>
-      <c r="I73" s="209">
+      <c r="I73" s="167">
         <f>901-90</f>
         <v>811</v>
       </c>
-      <c r="J73" s="209">
+      <c r="J73" s="167">
         <f t="shared" si="9"/>
         <v>16608</v>
       </c>
-      <c r="K73" s="209" t="s">
+      <c r="K73" s="167" t="s">
         <v>151</v>
       </c>
-      <c r="L73" s="209">
+      <c r="L73" s="167">
         <v>17434</v>
       </c>
-      <c r="M73" s="210">
+      <c r="M73" s="168">
         <v>5.6</v>
       </c>
-      <c r="N73" s="210" t="s">
+      <c r="N73" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="206">
+      <c r="A74" s="165">
         <v>59</v>
       </c>
-      <c r="B74" s="207" t="s">
+      <c r="B74" s="166" t="s">
         <v>271</v>
       </c>
-      <c r="C74" s="208" t="s">
+      <c r="C74" s="118" t="s">
         <v>152</v>
       </c>
-      <c r="D74" s="209">
+      <c r="D74" s="167">
         <v>19837</v>
       </c>
-      <c r="E74" s="209">
-        <v>0</v>
-      </c>
-      <c r="F74" s="209">
-        <v>0</v>
-      </c>
-      <c r="G74" s="209">
-        <v>0</v>
-      </c>
-      <c r="H74" s="209">
+      <c r="E74" s="167">
+        <v>0</v>
+      </c>
+      <c r="F74" s="167">
+        <v>0</v>
+      </c>
+      <c r="G74" s="167">
+        <v>0</v>
+      </c>
+      <c r="H74" s="167">
         <f>202-21</f>
         <v>181</v>
       </c>
-      <c r="I74" s="209">
+      <c r="I74" s="167">
         <f>1435-143</f>
         <v>1292</v>
       </c>
-      <c r="J74" s="209">
+      <c r="J74" s="167">
         <f t="shared" si="9"/>
         <v>21310</v>
       </c>
-      <c r="K74" s="209" t="s">
+      <c r="K74" s="167" t="s">
         <v>286</v>
       </c>
-      <c r="L74" s="209">
+      <c r="L74" s="167">
         <v>24428</v>
       </c>
-      <c r="M74" s="210">
+      <c r="M74" s="168">
         <v>7</v>
       </c>
-      <c r="N74" s="210" t="s">
+      <c r="N74" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="206">
+      <c r="A75" s="165">
         <v>60</v>
       </c>
-      <c r="B75" s="211" t="s">
+      <c r="B75" s="169" t="s">
         <v>273</v>
       </c>
-      <c r="C75" s="208" t="s">
+      <c r="C75" s="118" t="s">
         <v>142</v>
       </c>
-      <c r="D75" s="209">
+      <c r="D75" s="167">
         <v>26118</v>
       </c>
-      <c r="E75" s="209">
-        <v>0</v>
-      </c>
-      <c r="F75" s="209">
-        <v>0</v>
-      </c>
-      <c r="G75" s="209">
-        <v>0</v>
-      </c>
-      <c r="H75" s="209">
+      <c r="E75" s="167">
+        <v>0</v>
+      </c>
+      <c r="F75" s="167">
+        <v>0</v>
+      </c>
+      <c r="G75" s="167">
+        <v>0</v>
+      </c>
+      <c r="H75" s="167">
         <f>217-22</f>
         <v>195</v>
       </c>
-      <c r="I75" s="209">
+      <c r="I75" s="167">
         <f>1884-189</f>
         <v>1695</v>
       </c>
-      <c r="J75" s="209">
+      <c r="J75" s="167">
         <f>SUM(D75:I75)</f>
         <v>28008</v>
       </c>
-      <c r="K75" s="209" t="s">
+      <c r="K75" s="167" t="s">
         <v>267</v>
       </c>
-      <c r="L75" s="209">
+      <c r="L75" s="167">
         <v>32163</v>
       </c>
-      <c r="M75" s="210">
+      <c r="M75" s="168">
         <v>7</v>
       </c>
-      <c r="N75" s="210" t="s">
+      <c r="N75" s="168" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="206">
+      <c r="A76" s="165">
         <v>61</v>
       </c>
-      <c r="B76" s="219">
+      <c r="B76" s="176">
         <v>21123</v>
       </c>
-      <c r="C76" s="208" t="s">
+      <c r="C76" s="118" t="s">
         <v>218</v>
       </c>
-      <c r="D76" s="209">
+      <c r="D76" s="167">
         <v>10000</v>
       </c>
-      <c r="E76" s="209">
-        <v>0</v>
-      </c>
-      <c r="F76" s="209">
-        <v>0</v>
-      </c>
-      <c r="G76" s="209">
+      <c r="E76" s="167">
+        <v>0</v>
+      </c>
+      <c r="F76" s="167">
+        <v>0</v>
+      </c>
+      <c r="G76" s="167">
         <f>338-33</f>
         <v>305</v>
       </c>
-      <c r="H76" s="209">
+      <c r="H76" s="167">
         <f>738-73</f>
         <v>665</v>
       </c>
-      <c r="I76" s="209">
+      <c r="I76" s="167">
         <f>786-77</f>
         <v>709</v>
       </c>
-      <c r="J76" s="209">
+      <c r="J76" s="167">
         <f t="shared" si="9"/>
         <v>11679</v>
       </c>
-      <c r="K76" s="209" t="s">
+      <c r="K76" s="167" t="s">
         <v>211</v>
       </c>
-      <c r="L76" s="209">
+      <c r="L76" s="167">
         <v>12314</v>
       </c>
-      <c r="M76" s="210">
+      <c r="M76" s="168">
         <v>7</v>
       </c>
-      <c r="N76" s="210" t="s">
+      <c r="N76" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="206">
+      <c r="A77" s="165">
         <v>62</v>
       </c>
-      <c r="B77" s="214">
+      <c r="B77" s="172">
         <v>220754</v>
       </c>
-      <c r="C77" s="220" t="s">
+      <c r="C77" s="177" t="s">
         <v>282</v>
       </c>
-      <c r="D77" s="221">
+      <c r="D77" s="178">
         <v>10000</v>
       </c>
-      <c r="E77" s="221">
-        <v>0</v>
-      </c>
-      <c r="F77" s="221">
-        <v>0</v>
-      </c>
-      <c r="G77" s="221">
-        <v>0</v>
-      </c>
-      <c r="H77" s="221">
+      <c r="E77" s="178">
+        <v>0</v>
+      </c>
+      <c r="F77" s="178">
+        <v>0</v>
+      </c>
+      <c r="G77" s="178">
+        <v>0</v>
+      </c>
+      <c r="H77" s="178">
         <f>238-24</f>
         <v>214</v>
       </c>
-      <c r="I77" s="221">
+      <c r="I77" s="178">
         <f>732-73</f>
         <v>659</v>
       </c>
-      <c r="J77" s="209">
+      <c r="J77" s="167">
         <f t="shared" si="9"/>
         <v>10873</v>
       </c>
-      <c r="K77" s="222" t="s">
+      <c r="K77" s="179" t="s">
         <v>283</v>
       </c>
-      <c r="L77" s="221">
+      <c r="L77" s="178">
         <v>14148</v>
       </c>
-      <c r="M77" s="210">
+      <c r="M77" s="168">
         <v>7</v>
       </c>
-      <c r="N77" s="210" t="s">
+      <c r="N77" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="223"/>
-      <c r="B78" s="225"/>
-      <c r="C78" s="225"/>
-      <c r="D78" s="226">
+      <c r="A78" s="180"/>
+      <c r="B78" s="182"/>
+      <c r="C78" s="182"/>
+      <c r="D78" s="183">
         <f>SUM(D71:D77)</f>
         <v>107477</v>
       </c>
-      <c r="E78" s="226">
+      <c r="E78" s="183">
         <f t="shared" ref="E78:J78" si="10">SUM(E71:E77)</f>
         <v>459</v>
       </c>
-      <c r="F78" s="226">
+      <c r="F78" s="183">
         <f t="shared" si="10"/>
         <v>1226</v>
       </c>
-      <c r="G78" s="226">
+      <c r="G78" s="183">
         <f t="shared" si="10"/>
         <v>2628</v>
       </c>
-      <c r="H78" s="226">
+      <c r="H78" s="183">
         <f t="shared" si="10"/>
         <v>3863</v>
       </c>
-      <c r="I78" s="226">
+      <c r="I78" s="183">
         <f t="shared" si="10"/>
         <v>7114</v>
       </c>
-      <c r="J78" s="226">
+      <c r="J78" s="183">
         <f t="shared" si="10"/>
         <v>122767</v>
       </c>
-      <c r="K78" s="227"/>
-      <c r="L78" s="226">
+      <c r="K78" s="184"/>
+      <c r="L78" s="183">
         <f>SUM(L71:L77)</f>
         <v>136351</v>
       </c>
-      <c r="M78" s="223"/>
-      <c r="N78" s="223"/>
-      <c r="O78" s="239"/>
+      <c r="M78" s="180"/>
+      <c r="N78" s="180"/>
+      <c r="O78" s="193"/>
     </row>
     <row r="79" spans="1:15" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D79" s="248"/>
-      <c r="E79" s="229"/>
-      <c r="K79" s="231"/>
-      <c r="L79" s="231"/>
+      <c r="D79" s="202"/>
+      <c r="E79" s="150"/>
+      <c r="K79" s="186"/>
+      <c r="L79" s="186"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B80" s="249" t="s">
+      <c r="B80" s="203" t="s">
         <v>98</v>
       </c>
-      <c r="K80" s="231"/>
-      <c r="L80" s="231"/>
+      <c r="K80" s="186"/>
+      <c r="L80" s="186"/>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A81" s="206">
+      <c r="A81" s="165">
         <v>63</v>
       </c>
-      <c r="B81" s="207" t="s">
+      <c r="B81" s="166" t="s">
         <v>260</v>
       </c>
-      <c r="C81" s="208" t="s">
+      <c r="C81" s="118" t="s">
         <v>154</v>
       </c>
-      <c r="D81" s="209">
+      <c r="D81" s="167">
         <v>14225</v>
       </c>
-      <c r="E81" s="209">
-        <v>0</v>
-      </c>
-      <c r="F81" s="209">
-        <v>0</v>
-      </c>
-      <c r="G81" s="209">
-        <v>0</v>
-      </c>
-      <c r="H81" s="209">
+      <c r="E81" s="167">
+        <v>0</v>
+      </c>
+      <c r="F81" s="167">
+        <v>0</v>
+      </c>
+      <c r="G81" s="167">
+        <v>0</v>
+      </c>
+      <c r="H81" s="167">
         <f>801-81</f>
         <v>720</v>
       </c>
-      <c r="I81" s="209">
+      <c r="I81" s="167">
         <f>1071-108</f>
         <v>963</v>
       </c>
-      <c r="J81" s="209">
+      <c r="J81" s="167">
         <f>SUM(D81:I81)</f>
         <v>15908</v>
       </c>
-      <c r="K81" s="206" t="s">
+      <c r="K81" s="165" t="s">
         <v>291</v>
       </c>
-      <c r="L81" s="209">
+      <c r="L81" s="167">
         <v>17618</v>
       </c>
-      <c r="M81" s="210">
+      <c r="M81" s="168">
         <v>7</v>
       </c>
-      <c r="N81" s="210" t="s">
+      <c r="N81" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A82" s="206">
+      <c r="A82" s="165">
         <v>64</v>
       </c>
-      <c r="B82" s="207" t="s">
+      <c r="B82" s="166" t="s">
         <v>261</v>
       </c>
-      <c r="C82" s="208" t="s">
+      <c r="C82" s="118" t="s">
         <v>152</v>
       </c>
-      <c r="D82" s="209">
+      <c r="D82" s="167">
         <v>59518</v>
       </c>
-      <c r="E82" s="209">
-        <v>0</v>
-      </c>
-      <c r="F82" s="209">
-        <v>0</v>
-      </c>
-      <c r="G82" s="209">
-        <v>0</v>
-      </c>
-      <c r="H82" s="209">
+      <c r="E82" s="167">
+        <v>0</v>
+      </c>
+      <c r="F82" s="167">
+        <v>0</v>
+      </c>
+      <c r="G82" s="167">
+        <v>0</v>
+      </c>
+      <c r="H82" s="167">
         <f>605-61</f>
         <v>544</v>
       </c>
-      <c r="I82" s="209">
+      <c r="I82" s="167">
         <f>4305-430</f>
         <v>3875</v>
       </c>
-      <c r="J82" s="209">
+      <c r="J82" s="167">
         <f t="shared" ref="J82:J84" si="11">SUM(D82:I82)</f>
         <v>63937</v>
       </c>
-      <c r="K82" s="206" t="s">
+      <c r="K82" s="165" t="s">
         <v>286</v>
       </c>
-      <c r="L82" s="209">
+      <c r="L82" s="167">
         <v>73293</v>
       </c>
-      <c r="M82" s="210">
+      <c r="M82" s="168">
         <v>7</v>
       </c>
-      <c r="N82" s="210" t="s">
+      <c r="N82" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A83" s="206">
+      <c r="A83" s="165">
         <v>65</v>
       </c>
-      <c r="B83" s="207" t="s">
+      <c r="B83" s="166" t="s">
         <v>190</v>
       </c>
-      <c r="C83" s="208" t="s">
+      <c r="C83" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="D83" s="209">
+      <c r="D83" s="167">
         <v>11667</v>
       </c>
-      <c r="E83" s="209">
-        <v>0</v>
-      </c>
-      <c r="F83" s="209">
-        <v>0</v>
-      </c>
-      <c r="G83" s="209">
+      <c r="E83" s="167">
+        <v>0</v>
+      </c>
+      <c r="F83" s="167">
+        <v>0</v>
+      </c>
+      <c r="G83" s="167">
         <f>121-12</f>
         <v>109</v>
       </c>
-      <c r="H83" s="209">
+      <c r="H83" s="167">
         <f>874-88</f>
         <v>786</v>
       </c>
-      <c r="I83" s="209">
+      <c r="I83" s="167">
         <f>934-94</f>
         <v>840</v>
       </c>
-      <c r="J83" s="209">
+      <c r="J83" s="167">
         <f t="shared" si="11"/>
         <v>13402</v>
       </c>
-      <c r="K83" s="206" t="s">
+      <c r="K83" s="165" t="s">
         <v>206</v>
       </c>
-      <c r="L83" s="209">
+      <c r="L83" s="167">
         <v>14473</v>
       </c>
-      <c r="M83" s="210">
+      <c r="M83" s="168">
         <v>7.25</v>
       </c>
-      <c r="N83" s="210" t="s">
+      <c r="N83" s="168" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A84" s="206">
+      <c r="A84" s="165">
         <v>66</v>
       </c>
-      <c r="B84" s="211" t="s">
+      <c r="B84" s="169" t="s">
         <v>353</v>
       </c>
-      <c r="C84" s="208" t="s">
+      <c r="C84" s="118" t="s">
         <v>217</v>
       </c>
-      <c r="D84" s="209">
+      <c r="D84" s="167">
         <v>33842</v>
       </c>
-      <c r="E84" s="209">
-        <v>0</v>
-      </c>
-      <c r="F84" s="209">
-        <v>0</v>
-      </c>
-      <c r="G84" s="209">
-        <v>0</v>
-      </c>
-      <c r="H84" s="209">
-        <v>0</v>
-      </c>
-      <c r="I84" s="209">
+      <c r="E84" s="167">
+        <v>0</v>
+      </c>
+      <c r="F84" s="167">
+        <v>0</v>
+      </c>
+      <c r="G84" s="167">
+        <v>0</v>
+      </c>
+      <c r="H84" s="167">
+        <v>0</v>
+      </c>
+      <c r="I84" s="167">
         <f>2219-578</f>
         <v>1641</v>
       </c>
-      <c r="J84" s="209">
+      <c r="J84" s="167">
         <f t="shared" si="11"/>
         <v>35483</v>
       </c>
-      <c r="K84" s="206" t="s">
+      <c r="K84" s="165" t="s">
         <v>364</v>
       </c>
-      <c r="L84" s="209">
+      <c r="L84" s="167">
         <v>36902</v>
       </c>
-      <c r="M84" s="210">
+      <c r="M84" s="168">
         <v>6.6</v>
       </c>
-      <c r="N84" s="210" t="s">
+      <c r="N84" s="168" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="223"/>
-      <c r="B85" s="225"/>
-      <c r="C85" s="225"/>
-      <c r="D85" s="226">
+      <c r="A85" s="180"/>
+      <c r="B85" s="182"/>
+      <c r="C85" s="182"/>
+      <c r="D85" s="183">
         <f>SUM(D81:D84)</f>
         <v>119252</v>
       </c>
-      <c r="E85" s="226">
+      <c r="E85" s="183">
         <f t="shared" ref="E85" si="12">SUM(E81:E84)</f>
         <v>0</v>
       </c>
-      <c r="F85" s="226">
+      <c r="F85" s="183">
         <f t="shared" ref="F85" si="13">SUM(F81:F84)</f>
         <v>0</v>
       </c>
-      <c r="G85" s="226">
+      <c r="G85" s="183">
         <f t="shared" ref="G85" si="14">SUM(G81:G84)</f>
         <v>109</v>
       </c>
-      <c r="H85" s="226">
+      <c r="H85" s="183">
         <f t="shared" ref="H85" si="15">SUM(H81:H84)</f>
         <v>2050</v>
       </c>
-      <c r="I85" s="226">
+      <c r="I85" s="183">
         <f t="shared" ref="I85" si="16">SUM(I81:I84)</f>
         <v>7319</v>
       </c>
-      <c r="J85" s="226">
+      <c r="J85" s="183">
         <f t="shared" ref="J85" si="17">SUM(J81:J84)</f>
         <v>128730</v>
       </c>
-      <c r="K85" s="250"/>
-      <c r="L85" s="226">
+      <c r="K85" s="204"/>
+      <c r="L85" s="183">
         <f>SUM(L81:L84)</f>
         <v>142286</v>
       </c>
-      <c r="M85" s="223"/>
-      <c r="N85" s="223"/>
-      <c r="O85" s="239"/>
+      <c r="M85" s="180"/>
+      <c r="N85" s="180"/>
+      <c r="O85" s="193"/>
     </row>
     <row r="86" spans="1:23" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="158"/>
-      <c r="I86" s="158"/>
-      <c r="J86" s="158"/>
-      <c r="K86" s="251"/>
-      <c r="L86" s="158"/>
+      <c r="D86" s="137"/>
+      <c r="E86" s="137"/>
+      <c r="F86" s="137"/>
+      <c r="G86" s="137"/>
+      <c r="H86" s="137"/>
+      <c r="I86" s="137"/>
+      <c r="J86" s="137"/>
+      <c r="K86" s="205"/>
+      <c r="L86" s="137"/>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B87" s="249" t="s">
+      <c r="B87" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="158"/>
-      <c r="H87" s="158"/>
-      <c r="I87" s="158"/>
-      <c r="J87" s="158"/>
-      <c r="K87" s="251"/>
-      <c r="L87" s="158"/>
+      <c r="D87" s="137"/>
+      <c r="E87" s="137"/>
+      <c r="F87" s="137"/>
+      <c r="G87" s="137"/>
+      <c r="H87" s="137"/>
+      <c r="I87" s="137"/>
+      <c r="J87" s="137"/>
+      <c r="K87" s="205"/>
+      <c r="L87" s="137"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A88" s="206">
+      <c r="A88" s="165">
         <v>67</v>
       </c>
-      <c r="B88" s="207" t="s">
+      <c r="B88" s="166" t="s">
         <v>332</v>
       </c>
-      <c r="C88" s="208" t="s">
+      <c r="C88" s="118" t="s">
         <v>159</v>
       </c>
-      <c r="D88" s="209">
+      <c r="D88" s="167">
         <v>248538</v>
       </c>
-      <c r="E88" s="209">
-        <v>0</v>
-      </c>
-      <c r="F88" s="209">
-        <v>0</v>
-      </c>
-      <c r="G88" s="209">
-        <v>0</v>
-      </c>
-      <c r="H88" s="209">
-        <v>0</v>
-      </c>
-      <c r="I88" s="209">
+      <c r="E88" s="167">
+        <v>0</v>
+      </c>
+      <c r="F88" s="167">
+        <v>0</v>
+      </c>
+      <c r="G88" s="167">
+        <v>0</v>
+      </c>
+      <c r="H88" s="167">
+        <v>0</v>
+      </c>
+      <c r="I88" s="167">
         <f>5840-584</f>
         <v>5256</v>
       </c>
-      <c r="J88" s="209">
+      <c r="J88" s="167">
         <f>SUM(D88:I88)</f>
         <v>253794</v>
       </c>
-      <c r="K88" s="209" t="s">
+      <c r="K88" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="L88" s="209">
+      <c r="L88" s="167">
         <v>284398</v>
       </c>
-      <c r="M88" s="210">
+      <c r="M88" s="168">
         <v>6.8</v>
       </c>
-      <c r="N88" s="210" t="s">
+      <c r="N88" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A89" s="206">
+      <c r="A89" s="165">
         <v>68</v>
       </c>
-      <c r="B89" s="219">
+      <c r="B89" s="176">
         <v>101043011000368</v>
       </c>
-      <c r="C89" s="208" t="s">
+      <c r="C89" s="118" t="s">
         <v>199</v>
       </c>
-      <c r="D89" s="209">
+      <c r="D89" s="167">
         <v>25000</v>
       </c>
-      <c r="E89" s="209">
-        <v>0</v>
-      </c>
-      <c r="F89" s="209">
-        <v>0</v>
-      </c>
-      <c r="G89" s="209">
-        <v>0</v>
-      </c>
-      <c r="H89" s="209">
-        <v>0</v>
-      </c>
-      <c r="I89" s="209">
-        <v>0</v>
-      </c>
-      <c r="J89" s="209">
+      <c r="E89" s="167">
+        <v>0</v>
+      </c>
+      <c r="F89" s="167">
+        <v>0</v>
+      </c>
+      <c r="G89" s="167">
+        <v>0</v>
+      </c>
+      <c r="H89" s="167">
+        <v>0</v>
+      </c>
+      <c r="I89" s="167">
+        <v>0</v>
+      </c>
+      <c r="J89" s="167">
         <f>SUM(D89:I89)</f>
         <v>25000</v>
       </c>
-      <c r="K89" s="209" t="s">
+      <c r="K89" s="167" t="s">
         <v>205</v>
       </c>
-      <c r="L89" s="209">
+      <c r="L89" s="167">
         <v>25000</v>
       </c>
-      <c r="M89" s="210">
+      <c r="M89" s="168">
         <v>7</v>
       </c>
-      <c r="N89" s="210" t="s">
+      <c r="N89" s="168" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A90" s="206">
+      <c r="A90" s="165">
         <v>35</v>
       </c>
-      <c r="B90" s="219">
+      <c r="B90" s="176">
         <v>220738</v>
       </c>
-      <c r="C90" s="235" t="s">
+      <c r="C90" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="D90" s="212">
+      <c r="D90" s="170">
         <v>5051</v>
       </c>
-      <c r="E90" s="212">
-        <v>0</v>
-      </c>
-      <c r="F90" s="212">
-        <v>0</v>
-      </c>
-      <c r="G90" s="212">
-        <v>0</v>
-      </c>
-      <c r="H90" s="212">
+      <c r="E90" s="170">
+        <v>0</v>
+      </c>
+      <c r="F90" s="170">
+        <v>0</v>
+      </c>
+      <c r="G90" s="170">
+        <v>0</v>
+      </c>
+      <c r="H90" s="170">
         <f>120-11</f>
         <v>109</v>
       </c>
-      <c r="I90" s="212">
+      <c r="I90" s="170">
         <f>370-37</f>
         <v>333</v>
       </c>
-      <c r="J90" s="209">
+      <c r="J90" s="167">
         <f>SUM(D90:I90)</f>
         <v>5493</v>
       </c>
-      <c r="K90" s="209" t="s">
+      <c r="K90" s="167" t="s">
         <v>283</v>
       </c>
-      <c r="L90" s="212">
+      <c r="L90" s="170">
         <v>7146</v>
       </c>
-      <c r="M90" s="213">
+      <c r="M90" s="171">
         <v>7</v>
       </c>
-      <c r="N90" s="213" t="s">
+      <c r="N90" s="171" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A91" s="206">
+      <c r="A91" s="165">
         <v>69</v>
       </c>
-      <c r="B91" s="208" t="s">
+      <c r="B91" s="118" t="s">
         <v>179</v>
       </c>
-      <c r="C91" s="208" t="s">
+      <c r="C91" s="118" t="s">
         <v>126</v>
       </c>
-      <c r="D91" s="209">
+      <c r="D91" s="167">
         <v>187833</v>
       </c>
-      <c r="E91" s="209">
-        <v>0</v>
-      </c>
-      <c r="F91" s="209">
-        <v>0</v>
-      </c>
-      <c r="G91" s="209">
+      <c r="E91" s="167">
+        <v>0</v>
+      </c>
+      <c r="F91" s="167">
+        <v>0</v>
+      </c>
+      <c r="G91" s="167">
         <f>12418-1242</f>
         <v>11176</v>
       </c>
-      <c r="H91" s="209">
+      <c r="H91" s="167">
         <f>14472-1448</f>
         <v>13024</v>
       </c>
-      <c r="I91" s="209">
+      <c r="I91" s="167">
         <f>15337-1532</f>
         <v>13805</v>
       </c>
-      <c r="J91" s="209">
+      <c r="J91" s="167">
         <f t="shared" ref="J91:J92" si="18">SUM(D91:I91)</f>
         <v>225838</v>
       </c>
-      <c r="K91" s="209" t="s">
+      <c r="K91" s="167" t="s">
         <v>212</v>
       </c>
-      <c r="L91" s="209">
+      <c r="L91" s="167">
         <v>230558</v>
       </c>
-      <c r="M91" s="210">
+      <c r="M91" s="168">
         <v>7.1</v>
       </c>
-      <c r="N91" s="210" t="s">
+      <c r="N91" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A92" s="206">
+      <c r="A92" s="165">
         <v>70</v>
       </c>
-      <c r="B92" s="208" t="s">
+      <c r="B92" s="118" t="s">
         <v>257</v>
       </c>
-      <c r="C92" s="208" t="s">
+      <c r="C92" s="118" t="s">
         <v>294</v>
       </c>
-      <c r="D92" s="209">
+      <c r="D92" s="167">
         <v>285636</v>
       </c>
-      <c r="E92" s="209">
-        <v>0</v>
-      </c>
-      <c r="F92" s="209">
-        <v>0</v>
-      </c>
-      <c r="G92" s="209">
-        <v>0</v>
-      </c>
-      <c r="H92" s="209">
+      <c r="E92" s="167">
+        <v>0</v>
+      </c>
+      <c r="F92" s="167">
+        <v>0</v>
+      </c>
+      <c r="G92" s="167">
+        <v>0</v>
+      </c>
+      <c r="H92" s="167">
         <f>14845-1484</f>
         <v>13361</v>
       </c>
-      <c r="I92" s="209">
+      <c r="I92" s="167">
         <f>21429-2142</f>
         <v>19287</v>
       </c>
-      <c r="J92" s="209">
+      <c r="J92" s="167">
         <f t="shared" si="18"/>
         <v>318284</v>
       </c>
-      <c r="K92" s="209" t="s">
+      <c r="K92" s="167" t="s">
         <v>293</v>
       </c>
-      <c r="L92" s="209">
+      <c r="L92" s="167">
         <v>351743</v>
       </c>
-      <c r="M92" s="210">
+      <c r="M92" s="168">
         <v>7</v>
       </c>
-      <c r="N92" s="210" t="s">
+      <c r="N92" s="168" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="223"/>
-      <c r="B93" s="225"/>
-      <c r="C93" s="225"/>
-      <c r="D93" s="226">
+      <c r="A93" s="180"/>
+      <c r="B93" s="182"/>
+      <c r="C93" s="182"/>
+      <c r="D93" s="183">
         <f t="shared" ref="D93:J93" si="19">SUM(D88:D92)</f>
         <v>752058</v>
       </c>
-      <c r="E93" s="226">
+      <c r="E93" s="183">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="F93" s="226">
+      <c r="F93" s="183">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="G93" s="226">
+      <c r="G93" s="183">
         <f t="shared" si="19"/>
         <v>11176</v>
       </c>
-      <c r="H93" s="226">
+      <c r="H93" s="183">
         <f t="shared" si="19"/>
         <v>26494</v>
       </c>
-      <c r="I93" s="226">
+      <c r="I93" s="183">
         <f t="shared" si="19"/>
         <v>38681</v>
       </c>
-      <c r="J93" s="226">
+      <c r="J93" s="183">
         <f t="shared" si="19"/>
         <v>828409</v>
       </c>
-      <c r="K93" s="250"/>
-      <c r="L93" s="226">
+      <c r="K93" s="204"/>
+      <c r="L93" s="183">
         <f t="shared" ref="L93" si="20">SUM(L88:L92)</f>
         <v>898845</v>
       </c>
-      <c r="M93" s="223"/>
-      <c r="N93" s="223"/>
-      <c r="O93" s="239"/>
+      <c r="M93" s="180"/>
+      <c r="N93" s="180"/>
+      <c r="O93" s="193"/>
     </row>
     <row r="94" spans="1:23" ht="7.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="K94" s="231"/>
-      <c r="L94" s="231"/>
+      <c r="K94" s="186"/>
+      <c r="L94" s="186"/>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B95" s="249" t="s">
+      <c r="B95" s="203" t="s">
         <v>99</v>
       </c>
-      <c r="K95" s="231"/>
-      <c r="L95" s="231"/>
-    </row>
-    <row r="96" spans="1:23" s="249" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="206">
+      <c r="K95" s="186"/>
+      <c r="L95" s="186"/>
+    </row>
+    <row r="96" spans="1:23" s="203" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="165">
         <v>71</v>
       </c>
-      <c r="B96" s="208" t="s">
+      <c r="B96" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="C96" s="208" t="s">
+      <c r="C96" s="118" t="s">
         <v>192</v>
       </c>
-      <c r="D96" s="209">
+      <c r="D96" s="167">
         <v>14000</v>
       </c>
-      <c r="E96" s="209">
-        <v>0</v>
-      </c>
-      <c r="F96" s="209">
-        <v>0</v>
-      </c>
-      <c r="G96" s="209">
-        <v>0</v>
-      </c>
-      <c r="H96" s="209">
-        <v>0</v>
-      </c>
-      <c r="I96" s="209">
-        <v>0</v>
-      </c>
-      <c r="J96" s="209">
+      <c r="E96" s="167">
+        <v>0</v>
+      </c>
+      <c r="F96" s="167">
+        <v>0</v>
+      </c>
+      <c r="G96" s="167">
+        <v>0</v>
+      </c>
+      <c r="H96" s="167">
+        <v>0</v>
+      </c>
+      <c r="I96" s="167">
+        <v>0</v>
+      </c>
+      <c r="J96" s="167">
         <f>SUM(D96:I96)</f>
         <v>14000</v>
       </c>
-      <c r="K96" s="209" t="s">
+      <c r="K96" s="167" t="s">
         <v>216</v>
       </c>
-      <c r="L96" s="209">
+      <c r="L96" s="167">
         <v>14000</v>
       </c>
-      <c r="M96" s="206">
+      <c r="M96" s="165">
         <v>7.25</v>
       </c>
-      <c r="N96" s="210" t="s">
+      <c r="N96" s="168" t="s">
         <v>127</v>
       </c>
-      <c r="Q96" s="202"/>
-      <c r="R96" s="202"/>
-      <c r="S96" s="202"/>
-      <c r="T96" s="202"/>
-      <c r="U96" s="202"/>
-      <c r="V96" s="202"/>
-      <c r="W96" s="202"/>
+      <c r="Q96" s="136"/>
+      <c r="R96" s="136"/>
+      <c r="S96" s="136"/>
+      <c r="T96" s="136"/>
+      <c r="U96" s="136"/>
+      <c r="V96" s="136"/>
+      <c r="W96" s="136"/>
     </row>
     <row r="97" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="223"/>
-      <c r="B97" s="225"/>
-      <c r="C97" s="225"/>
-      <c r="D97" s="226">
+      <c r="A97" s="180"/>
+      <c r="B97" s="182"/>
+      <c r="C97" s="182"/>
+      <c r="D97" s="183">
         <f>SUM(D96:D96)</f>
         <v>14000</v>
       </c>
-      <c r="E97" s="226">
+      <c r="E97" s="183">
         <f t="shared" ref="E97:G97" si="21">SUM(E96:E96)</f>
         <v>0</v>
       </c>
-      <c r="F97" s="226">
+      <c r="F97" s="183">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G97" s="226">
+      <c r="G97" s="183">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H97" s="252">
-        <v>0</v>
-      </c>
-      <c r="I97" s="252">
-        <v>0</v>
-      </c>
-      <c r="J97" s="226">
+      <c r="H97" s="206">
+        <v>0</v>
+      </c>
+      <c r="I97" s="206">
+        <v>0</v>
+      </c>
+      <c r="J97" s="183">
         <f t="shared" ref="J97" si="22">SUM(J96:J96)</f>
         <v>14000</v>
       </c>
-      <c r="K97" s="250"/>
-      <c r="L97" s="226">
+      <c r="K97" s="204"/>
+      <c r="L97" s="183">
         <f>SUM(L96:L96)</f>
         <v>14000</v>
       </c>
-      <c r="M97" s="253"/>
-      <c r="N97" s="254"/>
-      <c r="O97" s="239"/>
-      <c r="Q97" s="249"/>
-      <c r="R97" s="249"/>
-      <c r="S97" s="249"/>
-      <c r="T97" s="249"/>
+      <c r="M97" s="207"/>
+      <c r="N97" s="208"/>
+      <c r="O97" s="193"/>
+      <c r="Q97" s="203"/>
+      <c r="R97" s="203"/>
+      <c r="S97" s="203"/>
+      <c r="T97" s="203"/>
     </row>
     <row r="98" spans="1:23" ht="7.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K98" s="231"/>
-      <c r="L98" s="231"/>
-      <c r="O98" s="239"/>
-      <c r="U98" s="249"/>
-      <c r="V98" s="249"/>
-      <c r="W98" s="249"/>
+      <c r="K98" s="186"/>
+      <c r="L98" s="186"/>
+      <c r="O98" s="193"/>
+      <c r="U98" s="203"/>
+      <c r="V98" s="203"/>
+      <c r="W98" s="203"/>
     </row>
     <row r="99" spans="1:23" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="223"/>
-      <c r="B99" s="255" t="s">
+      <c r="A99" s="180"/>
+      <c r="B99" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="C99" s="256"/>
-      <c r="D99" s="257">
+      <c r="C99" s="271"/>
+      <c r="D99" s="209">
         <f t="shared" ref="D99:J99" si="23">D23+D38+D47+D68+D78+D85+D93+D97</f>
         <v>8627401</v>
       </c>
-      <c r="E99" s="257">
+      <c r="E99" s="209">
         <f t="shared" si="23"/>
         <v>9050</v>
       </c>
-      <c r="F99" s="257">
+      <c r="F99" s="209">
         <f t="shared" si="23"/>
         <v>30323</v>
       </c>
-      <c r="G99" s="257">
+      <c r="G99" s="209">
         <f t="shared" si="23"/>
         <v>92231</v>
       </c>
-      <c r="H99" s="257">
+      <c r="H99" s="209">
         <f t="shared" si="23"/>
         <v>256109</v>
       </c>
-      <c r="I99" s="257">
+      <c r="I99" s="209">
         <f t="shared" si="23"/>
         <v>457547</v>
       </c>
-      <c r="J99" s="257">
+      <c r="J99" s="209">
         <f t="shared" si="23"/>
         <v>9472661</v>
       </c>
-      <c r="K99" s="258"/>
-      <c r="L99" s="257">
+      <c r="K99" s="210"/>
+      <c r="L99" s="209">
         <f>L23+L38+L47+L68+L78+L85+L93+L97</f>
         <v>10172692</v>
       </c>
-      <c r="M99" s="259"/>
-      <c r="N99" s="260"/>
-      <c r="O99" s="261"/>
+      <c r="M99" s="211"/>
+      <c r="N99" s="212"/>
     </row>
     <row r="100" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="E100" s="262"/>
-      <c r="F100" s="262"/>
-      <c r="G100" s="262"/>
-      <c r="H100" s="262"/>
-      <c r="I100" s="262"/>
-      <c r="Q100" s="202" t="s">
+      <c r="E100" s="213"/>
+      <c r="F100" s="213"/>
+      <c r="G100" s="213"/>
+      <c r="H100" s="213"/>
+      <c r="I100" s="213"/>
+      <c r="Q100" s="136" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="G101" s="229"/>
-      <c r="H101" s="229"/>
-      <c r="I101" s="229"/>
+      <c r="G101" s="150"/>
+      <c r="H101" s="150"/>
+      <c r="I101" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10714,53 +10677,53 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.109375" style="157" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="157" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="157" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="157" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="157" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" style="157" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="157" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="157" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="157"/>
+    <col min="1" max="1" width="21.109375" style="136" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="136" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="136" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="136" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" style="136" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" style="136" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="136" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="136" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="136"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="263" t="s">
+      <c r="A1" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="263"/>
-      <c r="C1" s="263"/>
-      <c r="D1" s="263"/>
-      <c r="E1" s="263"/>
-      <c r="F1" s="263"/>
-      <c r="G1" s="263"/>
-      <c r="H1" s="263"/>
+      <c r="B1" s="275"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="275"/>
+      <c r="F1" s="275"/>
+      <c r="G1" s="275"/>
+      <c r="H1" s="275"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="276" t="s">
         <v>581</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
+      <c r="B2" s="276"/>
+      <c r="C2" s="276"/>
+      <c r="D2" s="276"/>
+      <c r="E2" s="276"/>
+      <c r="F2" s="276"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="276"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="277" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="146" t="s">
+      <c r="C3" s="278"/>
+      <c r="D3" s="278"/>
+      <c r="E3" s="278"/>
+      <c r="F3" s="277" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="146"/>
+      <c r="G3" s="277"/>
       <c r="H3" s="36" t="s">
         <v>59</v>
       </c>
@@ -10967,7 +10930,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="172"/>
+      <c r="B11" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10995,33 +10958,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="264" t="s">
+      <c r="A1" s="281" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
+      <c r="B1" s="281"/>
+      <c r="C1" s="281"/>
+      <c r="D1" s="281"/>
       <c r="E1" s="10"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="280" t="s">
         <v>582</v>
       </c>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
+      <c r="B2" s="280"/>
+      <c r="C2" s="280"/>
+      <c r="D2" s="280"/>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="268" t="s">
+      <c r="A3" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="268" t="s">
+      <c r="B3" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="268" t="s">
+      <c r="C3" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="269" t="s">
+      <c r="D3" s="218" t="s">
         <v>53</v>
       </c>
     </row>
@@ -11035,7 +10998,7 @@
       <c r="C4" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D4" s="265">
+      <c r="D4" s="214">
         <v>8815</v>
       </c>
     </row>
@@ -11101,31 +11064,31 @@
       <c r="C9" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="270">
+      <c r="D9" s="219">
         <f>SUM(D4:D8)</f>
         <v>11805</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="280" t="s">
         <v>583</v>
       </c>
-      <c r="B12" s="149"/>
-      <c r="C12" s="149"/>
-      <c r="D12" s="149"/>
+      <c r="B12" s="280"/>
+      <c r="C12" s="280"/>
+      <c r="D12" s="280"/>
     </row>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="268" t="s">
+      <c r="A13" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="268" t="s">
+      <c r="B13" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="269" t="s">
+      <c r="D13" s="218" t="s">
         <v>53</v>
       </c>
     </row>
@@ -11139,7 +11102,7 @@
       <c r="C14" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="267">
+      <c r="D14" s="216">
         <v>10000</v>
       </c>
     </row>
@@ -11233,39 +11196,39 @@
       <c r="C21" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="270">
+      <c r="D21" s="219">
         <f>SUM(D14:D20)</f>
         <v>80000</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="149" t="s">
+      <c r="A24" s="280" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="149"/>
-      <c r="C24" s="149"/>
-      <c r="D24" s="149"/>
+      <c r="B24" s="280"/>
+      <c r="C24" s="280"/>
+      <c r="D24" s="280"/>
     </row>
     <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="149" t="s">
+      <c r="A25" s="280" t="s">
         <v>584</v>
       </c>
-      <c r="B25" s="149"/>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
+      <c r="B25" s="280"/>
+      <c r="C25" s="280"/>
+      <c r="D25" s="280"/>
     </row>
     <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="268" t="s">
+      <c r="A26" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="268" t="s">
+      <c r="B26" s="217" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="268" t="s">
+      <c r="C26" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="269" t="s">
+      <c r="D26" s="218" t="s">
         <v>53</v>
       </c>
     </row>
@@ -11331,31 +11294,31 @@
       <c r="C31" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="270">
+      <c r="D31" s="219">
         <f>SUM(D27:D30)</f>
         <v>31977</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="279" t="s">
         <v>585</v>
       </c>
-      <c r="B34" s="148"/>
-      <c r="C34" s="148"/>
-      <c r="D34" s="148"/>
+      <c r="B34" s="279"/>
+      <c r="C34" s="279"/>
+      <c r="D34" s="279"/>
     </row>
     <row r="35" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="268" t="s">
+      <c r="A35" s="217" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="268" t="s">
+      <c r="B35" s="217" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="268" t="s">
+      <c r="C35" s="217" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="269" t="s">
+      <c r="D35" s="218" t="s">
         <v>276</v>
       </c>
     </row>
@@ -11363,13 +11326,13 @@
       <c r="A36" s="8">
         <v>1</v>
       </c>
-      <c r="B36" s="266">
+      <c r="B36" s="215">
         <v>381</v>
       </c>
       <c r="C36" s="118" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="266">
+      <c r="D36" s="215">
         <f>742-126</f>
         <v>616</v>
       </c>
@@ -11378,13 +11341,13 @@
       <c r="A37" s="8">
         <v>2</v>
       </c>
-      <c r="B37" s="266">
+      <c r="B37" s="215">
         <v>2800</v>
       </c>
       <c r="C37" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="266">
+      <c r="D37" s="215">
         <v>2800</v>
       </c>
     </row>
@@ -11392,13 +11355,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="266">
+      <c r="B38" s="215">
         <v>12690</v>
       </c>
       <c r="C38" s="118" t="s">
         <v>171</v>
       </c>
-      <c r="D38" s="266">
+      <c r="D38" s="215">
         <v>10236</v>
       </c>
     </row>
@@ -11406,13 +11369,13 @@
       <c r="A39" s="8">
         <v>4</v>
       </c>
-      <c r="B39" s="266">
+      <c r="B39" s="215">
         <v>14590</v>
       </c>
       <c r="C39" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="266">
+      <c r="D39" s="215">
         <v>14149.52</v>
       </c>
     </row>
@@ -11420,13 +11383,13 @@
       <c r="A40" s="8">
         <v>5</v>
       </c>
-      <c r="B40" s="266">
+      <c r="B40" s="215">
         <v>18953</v>
       </c>
       <c r="C40" s="118" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="266">
+      <c r="D40" s="215">
         <v>4195</v>
       </c>
     </row>
@@ -11434,13 +11397,13 @@
       <c r="A41" s="8">
         <v>6</v>
       </c>
-      <c r="B41" s="266">
+      <c r="B41" s="215">
         <v>6270</v>
       </c>
       <c r="C41" s="118" t="s">
         <v>147</v>
       </c>
-      <c r="D41" s="266">
+      <c r="D41" s="215">
         <v>6270</v>
       </c>
     </row>
@@ -11448,13 +11411,13 @@
       <c r="A42" s="8">
         <v>7</v>
       </c>
-      <c r="B42" s="266">
+      <c r="B42" s="215">
         <v>0</v>
       </c>
       <c r="C42" s="118" t="s">
         <v>204</v>
       </c>
-      <c r="D42" s="266">
+      <c r="D42" s="215">
         <v>199</v>
       </c>
     </row>
@@ -11462,13 +11425,13 @@
       <c r="A43" s="8">
         <v>8</v>
       </c>
-      <c r="B43" s="266">
+      <c r="B43" s="215">
         <v>147</v>
       </c>
       <c r="C43" s="118" t="s">
         <v>301</v>
       </c>
-      <c r="D43" s="266">
+      <c r="D43" s="215">
         <v>0</v>
       </c>
     </row>
@@ -11476,13 +11439,13 @@
       <c r="A44" s="8">
         <v>9</v>
       </c>
-      <c r="B44" s="266">
+      <c r="B44" s="215">
         <v>1000</v>
       </c>
       <c r="C44" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="266">
+      <c r="D44" s="215">
         <v>1000</v>
       </c>
     </row>
@@ -11490,13 +11453,13 @@
       <c r="A45" s="8">
         <v>10</v>
       </c>
-      <c r="B45" s="266">
+      <c r="B45" s="215">
         <v>3500</v>
       </c>
       <c r="C45" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="266">
+      <c r="D45" s="215">
         <v>3800</v>
       </c>
     </row>
@@ -11504,13 +11467,13 @@
       <c r="A46" s="8">
         <v>11</v>
       </c>
-      <c r="B46" s="266">
+      <c r="B46" s="215">
         <v>1500</v>
       </c>
       <c r="C46" s="118" t="s">
         <v>201</v>
       </c>
-      <c r="D46" s="266">
+      <c r="D46" s="215">
         <v>1500</v>
       </c>
     </row>
@@ -11518,13 +11481,13 @@
       <c r="A47" s="8">
         <v>12</v>
       </c>
-      <c r="B47" s="266">
+      <c r="B47" s="215">
         <v>0</v>
       </c>
       <c r="C47" s="118" t="s">
         <v>597</v>
       </c>
-      <c r="D47" s="266">
+      <c r="D47" s="215">
         <v>826</v>
       </c>
     </row>
@@ -11536,7 +11499,7 @@
       <c r="C48" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="270">
+      <c r="D48" s="219">
         <f>SUM(D36:D47)</f>
         <v>45591.520000000004</v>
       </c>
@@ -11582,18 +11545,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="238" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="239" t="s">
         <v>604</v>
       </c>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3"/>
@@ -11759,18 +11722,18 @@
       <c r="E12" s="40"/>
     </row>
     <row r="14" spans="1:9" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="238" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
+      <c r="B14" s="238"/>
+      <c r="C14" s="238"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="133" t="s">
+      <c r="A15" s="239" t="s">
         <v>605</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
+      <c r="B15" s="239"/>
+      <c r="C15" s="239"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
@@ -11802,18 +11765,18 @@
       <c r="C20" s="121"/>
     </row>
     <row r="22" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="150" t="s">
+      <c r="A22" s="238" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="150"/>
-      <c r="C22" s="150"/>
+      <c r="B22" s="238"/>
+      <c r="C22" s="238"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="239" t="s">
         <v>606</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
+      <c r="B23" s="239"/>
+      <c r="C23" s="239"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
@@ -11845,18 +11808,18 @@
       <c r="C28" s="121"/>
     </row>
     <row r="30" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="150" t="s">
+      <c r="A30" s="238" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="150"/>
+      <c r="B30" s="238"/>
+      <c r="C30" s="238"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="239" t="s">
         <v>607</v>
       </c>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
+      <c r="B31" s="239"/>
+      <c r="C31" s="239"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
@@ -11920,12 +11883,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="282" t="s">
         <v>592</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
+      <c r="B1" s="282"/>
+      <c r="C1" s="282"/>
+      <c r="D1" s="282"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
@@ -11945,10 +11908,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="51"/>
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="283" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="152"/>
+      <c r="C4" s="283"/>
       <c r="D4" s="50" t="s">
         <v>114</v>
       </c>
@@ -12127,13 +12090,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="249" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="249"/>
+      <c r="C1" s="249"/>
+      <c r="D1" s="249"/>
+      <c r="E1" s="249"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="89" t="s">
